--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4602" documentId="13_ncr:1_{EE144245-9A81-46B4-BD16-CFA6097929DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F81369F7-5A45-46C0-AC91-D6D193C6AC4F}"/>
+  <xr:revisionPtr revIDLastSave="4605" documentId="13_ncr:1_{EE144245-9A81-46B4-BD16-CFA6097929DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68221C5E-04C2-457A-92C3-F57652493BFE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="292">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1791,6 +1791,44 @@
     <t>外食</t>
     <rPh sb="0" eb="2">
       <t>ガイショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>耳鼻科</t>
+    <rPh sb="0" eb="3">
+      <t>ジビカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生活費</t>
+    <rPh sb="0" eb="3">
+      <t>セイカツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外食</t>
+    <rPh sb="0" eb="2">
+      <t>ガイショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>実績</t>
+    <rPh sb="0" eb="2">
+      <t>ジッセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>南流山パン屋</t>
+    <rPh sb="0" eb="3">
+      <t>ミナミナガレヤマ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1981,6 +2019,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16527,36 +16569,60 @@
       </c>
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A528" s="7"/>
-      <c r="B528" s="5"/>
-      <c r="C528" s="5"/>
-      <c r="D528" s="5"/>
+      <c r="A528" s="7">
+        <v>46115</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C528" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D528" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E528" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F528" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G528" s="6"/>
-      <c r="H528" s="6"/>
+        <v>医療費-4実績</v>
+      </c>
+      <c r="G528" s="6">
+        <v>400</v>
+      </c>
+      <c r="H528" s="6" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A529" s="7"/>
-      <c r="B529" s="5"/>
-      <c r="C529" s="5"/>
-      <c r="D529" s="5"/>
+      <c r="A529" s="7">
+        <v>46117</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C529" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D529" s="5" t="s">
+        <v>290</v>
+      </c>
       <c r="E529" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F529" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G529" s="6"/>
-      <c r="H529" s="6"/>
+        <v>生活費外食4実績</v>
+      </c>
+      <c r="G529" s="6">
+        <v>1290</v>
+      </c>
+      <c r="H529" s="6" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A530" s="7"/>
@@ -18625,15 +18691,24 @@
   </sheetData>
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D530:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B530:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C530:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C529" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
+      <formula1>$L$3:$L$35</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B529" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
+      <formula1>$K$3:$K$20</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D529" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
+      <formula1>$M$3:$M$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4605" documentId="13_ncr:1_{EE144245-9A81-46B4-BD16-CFA6097929DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68221C5E-04C2-457A-92C3-F57652493BFE}"/>
+  <xr:revisionPtr revIDLastSave="4609" documentId="13_ncr:1_{EE144245-9A81-46B4-BD16-CFA6097929DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A57FDF9-E59A-4435-99E9-A189C36B1F49}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="301">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1829,6 +1829,81 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>習い事</t>
+    <rPh sb="0" eb="1">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バレエ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>発表会の写真</t>
+    <rPh sb="0" eb="3">
+      <t>ハッピョウカイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シャシン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>化粧品</t>
+    <rPh sb="0" eb="3">
+      <t>ケショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クレンジング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>学費</t>
+    <rPh sb="0" eb="2">
+      <t>ガクヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>小学校用品(黄色帽、体操服等)</t>
+    <rPh sb="0" eb="5">
+      <t>ショウガッコウヨウヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ボウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイソウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>乳液(アルビオン</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウエキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -16625,68 +16700,116 @@
       </c>
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A530" s="7"/>
-      <c r="B530" s="5"/>
-      <c r="C530" s="5"/>
-      <c r="D530" s="5"/>
+      <c r="A530" s="7">
+        <v>46117</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C530" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D530" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E530" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F530" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G530" s="6"/>
-      <c r="H530" s="6"/>
+        <v>習い事バレエ4実績</v>
+      </c>
+      <c r="G530" s="6">
+        <v>3961</v>
+      </c>
+      <c r="H530" s="6" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A531" s="7"/>
-      <c r="B531" s="5"/>
-      <c r="C531" s="5"/>
-      <c r="D531" s="5"/>
+      <c r="A531" s="7">
+        <v>46118</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C531" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D531" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E531" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F531" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G531" s="6"/>
-      <c r="H531" s="6"/>
+        <v>化粧品-4実績</v>
+      </c>
+      <c r="G531" s="6">
+        <v>1760</v>
+      </c>
+      <c r="H531" s="6" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A532" s="7"/>
-      <c r="B532" s="5"/>
-      <c r="C532" s="5"/>
-      <c r="D532" s="5"/>
+      <c r="A532" s="7">
+        <v>46118</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C532" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D532" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E532" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F532" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G532" s="6"/>
-      <c r="H532" s="6"/>
+        <v>学費ことは4実績</v>
+      </c>
+      <c r="G532" s="6">
+        <v>9345</v>
+      </c>
+      <c r="H532" s="6" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A533" s="7"/>
-      <c r="B533" s="5"/>
-      <c r="C533" s="5"/>
-      <c r="D533" s="5"/>
+      <c r="A533" s="7">
+        <v>46119</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C533" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D533" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E533" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F533" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G533" s="6"/>
-      <c r="H533" s="6"/>
+        <v>化粧品-4実績</v>
+      </c>
+      <c r="G533" s="6">
+        <v>5400</v>
+      </c>
+      <c r="H533" s="6" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A534" s="7"/>
@@ -18692,22 +18815,22 @@
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D530:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D534:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B530:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B534:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C530:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C534:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C529" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C533" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B529" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B533" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D529" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D533" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Desktop\Python_dir\money_managemant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4609" documentId="13_ncr:1_{EE144245-9A81-46B4-BD16-CFA6097929DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A57FDF9-E59A-4435-99E9-A189C36B1F49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="312">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1905,6 +1905,70 @@
     <rPh sb="0" eb="2">
       <t>ニュウエキ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>学費</t>
+    <rPh sb="0" eb="2">
+      <t>ガクヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>学校で使うショルダーバッグ</t>
+    <rPh sb="0" eb="2">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+  </si>
+  <si>
+    <t>りょう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ユニクロ　長袖Tシャツ</t>
+    <rPh sb="5" eb="7">
+      <t>ナガソデ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外食</t>
+    <rPh sb="0" eb="2">
+      <t>ガイショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>朝マック</t>
+    <rPh sb="0" eb="1">
+      <t>アサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mini one</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しまむら　パンツ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2094,10 +2158,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16812,100 +16872,170 @@
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A534" s="7"/>
-      <c r="B534" s="5"/>
-      <c r="C534" s="5"/>
-      <c r="D534" s="5"/>
+      <c r="A534" s="7">
+        <v>46120</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C534" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D534" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E534" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F534" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G534" s="6"/>
-      <c r="H534" s="6"/>
+        <v>学費ことは4実績</v>
+      </c>
+      <c r="G534" s="6">
+        <v>1419</v>
+      </c>
+      <c r="H534" s="6" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A535" s="7"/>
-      <c r="B535" s="5"/>
-      <c r="C535" s="5"/>
-      <c r="D535" s="5"/>
+      <c r="A535" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D535" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E535" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F535" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G535" s="6"/>
-      <c r="H535" s="6"/>
+        <v>服りょう4実績</v>
+      </c>
+      <c r="G535" s="6">
+        <v>1290</v>
+      </c>
+      <c r="H535" s="6" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A536" s="7"/>
-      <c r="B536" s="5"/>
-      <c r="C536" s="5"/>
-      <c r="D536" s="5"/>
+      <c r="A536" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C536" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D536" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E536" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F536" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G536" s="6"/>
-      <c r="H536" s="6"/>
+        <v>生活費外食4実績</v>
+      </c>
+      <c r="G536" s="6">
+        <v>2650</v>
+      </c>
+      <c r="H536" s="6" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A537" s="7"/>
-      <c r="B537" s="5"/>
-      <c r="C537" s="5"/>
-      <c r="D537" s="5"/>
+      <c r="A537" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B537" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C537" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D537" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E537" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F537" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G537" s="6"/>
-      <c r="H537" s="6"/>
+        <v>生活費外食4実績</v>
+      </c>
+      <c r="G537" s="6">
+        <v>829</v>
+      </c>
+      <c r="H537" s="6" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A538" s="7"/>
-      <c r="B538" s="5"/>
-      <c r="C538" s="5"/>
-      <c r="D538" s="5"/>
+      <c r="A538" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C538" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E538" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F538" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G538" s="6"/>
+        <v>服子供4実績</v>
+      </c>
+      <c r="G538" s="6">
+        <v>16479</v>
+      </c>
       <c r="H538" s="6"/>
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A539" s="7"/>
-      <c r="B539" s="5"/>
-      <c r="C539" s="5"/>
-      <c r="D539" s="5"/>
+      <c r="A539" s="7">
+        <v>46123</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C539" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D539" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E539" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F539" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G539" s="6"/>
-      <c r="H539" s="6"/>
+        <v>服ゆっこ4実績</v>
+      </c>
+      <c r="G539" s="6">
+        <v>1490</v>
+      </c>
+      <c r="H539" s="6" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A540" s="7"/>
@@ -18815,22 +18945,22 @@
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D534:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D542:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B534:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B542:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C534:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C542:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C533" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C541" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B533" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B541" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D533" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D541" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Desktop\Python_dir\money_managemant\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0241BCC-C540-426B-9AB9-2999748D2C94}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="332">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1969,6 +1969,121 @@
   </si>
   <si>
     <t>しまむら　パンツ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>491kWh</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>体操服、クオーターパンツ</t>
+    <rPh sb="0" eb="3">
+      <t>タイソウフク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>結婚記念日ケーキ</t>
+    <rPh sb="0" eb="2">
+      <t>ケッコン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>キネンビ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>315薬用美白クリーム</t>
+    <rPh sb="3" eb="7">
+      <t>ヤクヨウビハク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>315MJラインEXPB</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>医療費</t>
+    <rPh sb="0" eb="3">
+      <t>イリョウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう歯医者</t>
+    <rPh sb="3" eb="6">
+      <t>ハイシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>予備費</t>
+    <rPh sb="0" eb="3">
+      <t>ヨビヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フットレスト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クリーニング</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GUタンクトップx2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ショーツ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しゃぶしゃぶ宮崎霧峰</t>
+    <rPh sb="6" eb="8">
+      <t>ミヤザキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キリミネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生活費</t>
+    <rPh sb="0" eb="3">
+      <t>セイカツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ミスド</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -17038,260 +17153,442 @@
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A540" s="7"/>
-      <c r="B540" s="5"/>
-      <c r="C540" s="5"/>
-      <c r="D540" s="5"/>
+      <c r="A540" s="7">
+        <v>46124</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C540" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D540" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E540" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F540" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G540" s="6"/>
+        <v>光熱費水道4実績</v>
+      </c>
+      <c r="G540" s="6">
+        <v>14613</v>
+      </c>
       <c r="H540" s="6"/>
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A541" s="7"/>
-      <c r="B541" s="5"/>
-      <c r="C541" s="5"/>
-      <c r="D541" s="5"/>
+      <c r="A541" s="7">
+        <v>46143</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C541" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D541" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E541" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F541" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G541" s="6"/>
-      <c r="H541" s="6"/>
+        <v>光熱費電気5実績</v>
+      </c>
+      <c r="G541" s="6">
+        <v>17300</v>
+      </c>
+      <c r="H541" s="6" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="542" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A542" s="7"/>
-      <c r="B542" s="5"/>
-      <c r="C542" s="5"/>
-      <c r="D542" s="5"/>
+      <c r="A542" s="7">
+        <v>46124</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C542" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D542" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E542" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F542" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G542" s="6"/>
+        <v>美容室みなと4実績</v>
+      </c>
+      <c r="G542" s="6">
+        <v>1400</v>
+      </c>
       <c r="H542" s="6"/>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A543" s="7"/>
-      <c r="B543" s="5"/>
-      <c r="C543" s="5"/>
-      <c r="D543" s="5"/>
+      <c r="A543" s="7">
+        <v>46124</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D543" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E543" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F543" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G543" s="6"/>
+        <v>美容室りょう4実績</v>
+      </c>
+      <c r="G543" s="6">
+        <v>1400</v>
+      </c>
       <c r="H543" s="6"/>
     </row>
     <row r="544" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A544" s="7"/>
-      <c r="B544" s="5"/>
-      <c r="C544" s="5"/>
-      <c r="D544" s="5"/>
+      <c r="A544" s="7">
+        <v>46124</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C544" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D544" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E544" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F544" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G544" s="6"/>
+        <v>服子供4実績</v>
+      </c>
+      <c r="G544" s="6">
+        <v>5027</v>
+      </c>
       <c r="H544" s="6"/>
     </row>
     <row r="545" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A545" s="7"/>
-      <c r="B545" s="5"/>
-      <c r="C545" s="5"/>
-      <c r="D545" s="5"/>
+      <c r="A545" s="7">
+        <v>46125</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C545" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D545" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E545" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F545" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G545" s="6"/>
-      <c r="H545" s="6"/>
+        <v>学費みなと4実績</v>
+      </c>
+      <c r="G545" s="6">
+        <v>4919</v>
+      </c>
+      <c r="H545" s="6" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="546" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A546" s="7"/>
-      <c r="B546" s="5"/>
-      <c r="C546" s="5"/>
-      <c r="D546" s="5"/>
+      <c r="A546" s="7">
+        <v>46125</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C546" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D546" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E546" s="5">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F546" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G546" s="6"/>
-      <c r="H546" s="6"/>
+        <v>祝い事外食4実績</v>
+      </c>
+      <c r="G546" s="6">
+        <v>1880</v>
+      </c>
+      <c r="H546" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="547" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A547" s="7"/>
-      <c r="B547" s="5"/>
-      <c r="C547" s="5"/>
-      <c r="D547" s="5"/>
+      <c r="A547" s="7">
+        <v>46128</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C547" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D547" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E547" s="5">
-        <f t="shared" ref="E547:E610" si="43">MONTH(A547)</f>
-        <v>1</v>
+        <f t="shared" ref="E547:E555" si="43">MONTH(A547)</f>
+        <v>4</v>
       </c>
       <c r="F547" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G547" s="6"/>
-      <c r="H547" s="6"/>
+        <v>化粧品-4実績</v>
+      </c>
+      <c r="G547" s="6">
+        <v>2090</v>
+      </c>
+      <c r="H547" s="6" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="548" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A548" s="7"/>
-      <c r="B548" s="5"/>
-      <c r="C548" s="5"/>
-      <c r="D548" s="5"/>
+      <c r="A548" s="7">
+        <v>46128</v>
+      </c>
+      <c r="B548" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C548" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D548" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E548" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F548" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G548" s="6"/>
-      <c r="H548" s="6"/>
+        <v>化粧品-4実績</v>
+      </c>
+      <c r="G548" s="6">
+        <v>1045</v>
+      </c>
+      <c r="H548" s="6" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A549" s="7"/>
-      <c r="B549" s="5"/>
-      <c r="C549" s="5"/>
-      <c r="D549" s="5"/>
+      <c r="A549" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C549" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D549" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E549" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F549" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G549" s="6"/>
-      <c r="H549" s="6"/>
+        <v>医療費-4実績</v>
+      </c>
+      <c r="G549" s="6">
+        <v>4180</v>
+      </c>
+      <c r="H549" s="6" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A550" s="7"/>
-      <c r="B550" s="5"/>
-      <c r="C550" s="5"/>
-      <c r="D550" s="5"/>
+      <c r="A550" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C550" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D550" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E550" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F550" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G550" s="6"/>
-      <c r="H550" s="6"/>
+        <v>その他予備費4実績</v>
+      </c>
+      <c r="G550" s="6">
+        <v>3620</v>
+      </c>
+      <c r="H550" s="6" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A551" s="7"/>
-      <c r="B551" s="5"/>
-      <c r="C551" s="5"/>
-      <c r="D551" s="5"/>
+      <c r="A551" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C551" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D551" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E551" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F551" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G551" s="6"/>
+        <v>その他クリーニング4実績</v>
+      </c>
+      <c r="G551" s="6">
+        <v>9024</v>
+      </c>
       <c r="H551" s="6"/>
     </row>
     <row r="552" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A552" s="7"/>
-      <c r="B552" s="5"/>
-      <c r="C552" s="5"/>
-      <c r="D552" s="5"/>
+      <c r="A552" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C552" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D552" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E552" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F552" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G552" s="6"/>
-      <c r="H552" s="6"/>
+        <v>服ゆっこ4実績</v>
+      </c>
+      <c r="G552" s="6">
+        <v>2480</v>
+      </c>
+      <c r="H552" s="6" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A553" s="7"/>
-      <c r="B553" s="5"/>
-      <c r="C553" s="5"/>
-      <c r="D553" s="5"/>
+      <c r="A553" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B553" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C553" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D553" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E553" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F553" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G553" s="6"/>
-      <c r="H553" s="6"/>
+        <v>服ゆっこ4実績</v>
+      </c>
+      <c r="G553" s="6">
+        <v>1078</v>
+      </c>
+      <c r="H553" s="6" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A554" s="7"/>
-      <c r="B554" s="5"/>
-      <c r="C554" s="5"/>
-      <c r="D554" s="5"/>
+      <c r="A554" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C554" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D554" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E554" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F554" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G554" s="6"/>
-      <c r="H554" s="6"/>
+        <v>祝い事外食4実績</v>
+      </c>
+      <c r="G554" s="6">
+        <v>19701</v>
+      </c>
+      <c r="H554" s="6" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A555" s="7"/>
-      <c r="B555" s="5"/>
-      <c r="C555" s="5"/>
-      <c r="D555" s="5"/>
+      <c r="A555" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D555" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E555" s="5">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F555" s="5" t="str">
         <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-      <c r="G555" s="6"/>
-      <c r="H555" s="6"/>
+        <v>生活費外食4実績</v>
+      </c>
+      <c r="G555" s="6">
+        <v>1199</v>
+      </c>
+      <c r="H555" s="6" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A556" s="7"/>
@@ -17299,7 +17596,7 @@
       <c r="C556" s="5"/>
       <c r="D556" s="5"/>
       <c r="E556" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="E547:E610" si="44">MONTH(A556)</f>
         <v>1</v>
       </c>
       <c r="F556" s="5" t="str">
@@ -17315,7 +17612,7 @@
       <c r="C557" s="5"/>
       <c r="D557" s="5"/>
       <c r="E557" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F557" s="5" t="str">
@@ -17331,7 +17628,7 @@
       <c r="C558" s="5"/>
       <c r="D558" s="5"/>
       <c r="E558" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F558" s="5" t="str">
@@ -17347,7 +17644,7 @@
       <c r="C559" s="5"/>
       <c r="D559" s="5"/>
       <c r="E559" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F559" s="5" t="str">
@@ -17363,7 +17660,7 @@
       <c r="C560" s="5"/>
       <c r="D560" s="5"/>
       <c r="E560" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F560" s="5" t="str">
@@ -17379,7 +17676,7 @@
       <c r="C561" s="5"/>
       <c r="D561" s="5"/>
       <c r="E561" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F561" s="5" t="str">
@@ -17395,7 +17692,7 @@
       <c r="C562" s="5"/>
       <c r="D562" s="5"/>
       <c r="E562" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F562" s="5" t="str">
@@ -17411,7 +17708,7 @@
       <c r="C563" s="5"/>
       <c r="D563" s="5"/>
       <c r="E563" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F563" s="5" t="str">
@@ -17427,7 +17724,7 @@
       <c r="C564" s="5"/>
       <c r="D564" s="5"/>
       <c r="E564" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F564" s="5" t="str">
@@ -17443,7 +17740,7 @@
       <c r="C565" s="5"/>
       <c r="D565" s="5"/>
       <c r="E565" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F565" s="5" t="str">
@@ -17459,7 +17756,7 @@
       <c r="C566" s="5"/>
       <c r="D566" s="5"/>
       <c r="E566" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F566" s="5" t="str">
@@ -17475,7 +17772,7 @@
       <c r="C567" s="5"/>
       <c r="D567" s="5"/>
       <c r="E567" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F567" s="5" t="str">
@@ -17491,7 +17788,7 @@
       <c r="C568" s="5"/>
       <c r="D568" s="5"/>
       <c r="E568" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F568" s="5" t="str">
@@ -17507,7 +17804,7 @@
       <c r="C569" s="5"/>
       <c r="D569" s="5"/>
       <c r="E569" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F569" s="5" t="str">
@@ -17523,7 +17820,7 @@
       <c r="C570" s="5"/>
       <c r="D570" s="5"/>
       <c r="E570" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F570" s="5" t="str">
@@ -17539,7 +17836,7 @@
       <c r="C571" s="5"/>
       <c r="D571" s="5"/>
       <c r="E571" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F571" s="5" t="str">
@@ -17555,7 +17852,7 @@
       <c r="C572" s="5"/>
       <c r="D572" s="5"/>
       <c r="E572" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F572" s="5" t="str">
@@ -17571,7 +17868,7 @@
       <c r="C573" s="5"/>
       <c r="D573" s="5"/>
       <c r="E573" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F573" s="5" t="str">
@@ -17587,7 +17884,7 @@
       <c r="C574" s="5"/>
       <c r="D574" s="5"/>
       <c r="E574" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F574" s="5" t="str">
@@ -17603,7 +17900,7 @@
       <c r="C575" s="5"/>
       <c r="D575" s="5"/>
       <c r="E575" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F575" s="5" t="str">
@@ -17619,7 +17916,7 @@
       <c r="C576" s="5"/>
       <c r="D576" s="5"/>
       <c r="E576" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F576" s="5" t="str">
@@ -17635,7 +17932,7 @@
       <c r="C577" s="5"/>
       <c r="D577" s="5"/>
       <c r="E577" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F577" s="5" t="str">
@@ -17651,7 +17948,7 @@
       <c r="C578" s="5"/>
       <c r="D578" s="5"/>
       <c r="E578" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F578" s="5" t="str">
@@ -17667,7 +17964,7 @@
       <c r="C579" s="5"/>
       <c r="D579" s="5"/>
       <c r="E579" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F579" s="5" t="str">
@@ -17683,7 +17980,7 @@
       <c r="C580" s="5"/>
       <c r="D580" s="5"/>
       <c r="E580" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F580" s="5" t="str">
@@ -17699,7 +17996,7 @@
       <c r="C581" s="5"/>
       <c r="D581" s="5"/>
       <c r="E581" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F581" s="5" t="str">
@@ -17715,7 +18012,7 @@
       <c r="C582" s="5"/>
       <c r="D582" s="5"/>
       <c r="E582" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F582" s="5" t="str">
@@ -17731,7 +18028,7 @@
       <c r="C583" s="5"/>
       <c r="D583" s="5"/>
       <c r="E583" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F583" s="5" t="str">
@@ -17747,7 +18044,7 @@
       <c r="C584" s="5"/>
       <c r="D584" s="5"/>
       <c r="E584" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F584" s="5" t="str">
@@ -17763,7 +18060,7 @@
       <c r="C585" s="5"/>
       <c r="D585" s="5"/>
       <c r="E585" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F585" s="5" t="str">
@@ -17779,7 +18076,7 @@
       <c r="C586" s="5"/>
       <c r="D586" s="5"/>
       <c r="E586" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F586" s="5" t="str">
@@ -17795,7 +18092,7 @@
       <c r="C587" s="5"/>
       <c r="D587" s="5"/>
       <c r="E587" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F587" s="5" t="str">
@@ -17811,7 +18108,7 @@
       <c r="C588" s="5"/>
       <c r="D588" s="5"/>
       <c r="E588" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F588" s="5" t="str">
@@ -17827,7 +18124,7 @@
       <c r="C589" s="5"/>
       <c r="D589" s="5"/>
       <c r="E589" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F589" s="5" t="str">
@@ -17843,7 +18140,7 @@
       <c r="C590" s="5"/>
       <c r="D590" s="5"/>
       <c r="E590" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F590" s="5" t="str">
@@ -17859,7 +18156,7 @@
       <c r="C591" s="5"/>
       <c r="D591" s="5"/>
       <c r="E591" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F591" s="5" t="str">
@@ -17875,7 +18172,7 @@
       <c r="C592" s="5"/>
       <c r="D592" s="5"/>
       <c r="E592" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F592" s="5" t="str">
@@ -17891,7 +18188,7 @@
       <c r="C593" s="5"/>
       <c r="D593" s="5"/>
       <c r="E593" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F593" s="5" t="str">
@@ -17907,7 +18204,7 @@
       <c r="C594" s="5"/>
       <c r="D594" s="5"/>
       <c r="E594" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F594" s="5" t="str">
@@ -17923,7 +18220,7 @@
       <c r="C595" s="5"/>
       <c r="D595" s="5"/>
       <c r="E595" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F595" s="5" t="str">
@@ -17939,7 +18236,7 @@
       <c r="C596" s="5"/>
       <c r="D596" s="5"/>
       <c r="E596" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F596" s="5" t="str">
@@ -17955,7 +18252,7 @@
       <c r="C597" s="5"/>
       <c r="D597" s="5"/>
       <c r="E597" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F597" s="5" t="str">
@@ -17971,7 +18268,7 @@
       <c r="C598" s="5"/>
       <c r="D598" s="5"/>
       <c r="E598" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F598" s="5" t="str">
@@ -17987,7 +18284,7 @@
       <c r="C599" s="5"/>
       <c r="D599" s="5"/>
       <c r="E599" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F599" s="5" t="str">
@@ -18003,7 +18300,7 @@
       <c r="C600" s="5"/>
       <c r="D600" s="5"/>
       <c r="E600" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F600" s="5" t="str">
@@ -18019,7 +18316,7 @@
       <c r="C601" s="5"/>
       <c r="D601" s="5"/>
       <c r="E601" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F601" s="5" t="str">
@@ -18035,7 +18332,7 @@
       <c r="C602" s="5"/>
       <c r="D602" s="5"/>
       <c r="E602" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F602" s="5" t="str">
@@ -18051,7 +18348,7 @@
       <c r="C603" s="5"/>
       <c r="D603" s="5"/>
       <c r="E603" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F603" s="5" t="str">
@@ -18067,7 +18364,7 @@
       <c r="C604" s="5"/>
       <c r="D604" s="5"/>
       <c r="E604" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F604" s="5" t="str">
@@ -18083,7 +18380,7 @@
       <c r="C605" s="5"/>
       <c r="D605" s="5"/>
       <c r="E605" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F605" s="5" t="str">
@@ -18099,7 +18396,7 @@
       <c r="C606" s="5"/>
       <c r="D606" s="5"/>
       <c r="E606" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F606" s="5" t="str">
@@ -18115,7 +18412,7 @@
       <c r="C607" s="5"/>
       <c r="D607" s="5"/>
       <c r="E607" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F607" s="5" t="str">
@@ -18131,7 +18428,7 @@
       <c r="C608" s="5"/>
       <c r="D608" s="5"/>
       <c r="E608" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F608" s="5" t="str">
@@ -18147,7 +18444,7 @@
       <c r="C609" s="5"/>
       <c r="D609" s="5"/>
       <c r="E609" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F609" s="5" t="str">
@@ -18163,7 +18460,7 @@
       <c r="C610" s="5"/>
       <c r="D610" s="5"/>
       <c r="E610" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1</v>
       </c>
       <c r="F610" s="5" t="str">
@@ -18179,7 +18476,7 @@
       <c r="C611" s="5"/>
       <c r="D611" s="5"/>
       <c r="E611" s="5">
-        <f t="shared" ref="E611:E658" si="44">MONTH(A611)</f>
+        <f t="shared" ref="E611:E658" si="45">MONTH(A611)</f>
         <v>1</v>
       </c>
       <c r="F611" s="5" t="str">
@@ -18195,7 +18492,7 @@
       <c r="C612" s="5"/>
       <c r="D612" s="5"/>
       <c r="E612" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F612" s="5" t="str">
@@ -18211,7 +18508,7 @@
       <c r="C613" s="5"/>
       <c r="D613" s="5"/>
       <c r="E613" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F613" s="5" t="str">
@@ -18227,7 +18524,7 @@
       <c r="C614" s="5"/>
       <c r="D614" s="5"/>
       <c r="E614" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F614" s="5" t="str">
@@ -18243,7 +18540,7 @@
       <c r="C615" s="5"/>
       <c r="D615" s="5"/>
       <c r="E615" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F615" s="5" t="str">
@@ -18259,7 +18556,7 @@
       <c r="C616" s="5"/>
       <c r="D616" s="5"/>
       <c r="E616" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F616" s="5" t="str">
@@ -18275,7 +18572,7 @@
       <c r="C617" s="5"/>
       <c r="D617" s="5"/>
       <c r="E617" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F617" s="5" t="str">
@@ -18291,7 +18588,7 @@
       <c r="C618" s="5"/>
       <c r="D618" s="5"/>
       <c r="E618" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F618" s="5" t="str">
@@ -18307,7 +18604,7 @@
       <c r="C619" s="5"/>
       <c r="D619" s="5"/>
       <c r="E619" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F619" s="5" t="str">
@@ -18323,7 +18620,7 @@
       <c r="C620" s="5"/>
       <c r="D620" s="5"/>
       <c r="E620" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F620" s="5" t="str">
@@ -18339,7 +18636,7 @@
       <c r="C621" s="5"/>
       <c r="D621" s="5"/>
       <c r="E621" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F621" s="5" t="str">
@@ -18355,7 +18652,7 @@
       <c r="C622" s="5"/>
       <c r="D622" s="5"/>
       <c r="E622" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F622" s="5" t="str">
@@ -18371,7 +18668,7 @@
       <c r="C623" s="5"/>
       <c r="D623" s="5"/>
       <c r="E623" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F623" s="5" t="str">
@@ -18387,7 +18684,7 @@
       <c r="C624" s="5"/>
       <c r="D624" s="5"/>
       <c r="E624" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F624" s="5" t="str">
@@ -18403,7 +18700,7 @@
       <c r="C625" s="5"/>
       <c r="D625" s="5"/>
       <c r="E625" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F625" s="5" t="str">
@@ -18419,7 +18716,7 @@
       <c r="C626" s="5"/>
       <c r="D626" s="5"/>
       <c r="E626" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F626" s="5" t="str">
@@ -18435,7 +18732,7 @@
       <c r="C627" s="5"/>
       <c r="D627" s="5"/>
       <c r="E627" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F627" s="5" t="str">
@@ -18451,7 +18748,7 @@
       <c r="C628" s="5"/>
       <c r="D628" s="5"/>
       <c r="E628" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F628" s="5" t="str">
@@ -18467,7 +18764,7 @@
       <c r="C629" s="5"/>
       <c r="D629" s="5"/>
       <c r="E629" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F629" s="5" t="str">
@@ -18483,7 +18780,7 @@
       <c r="C630" s="5"/>
       <c r="D630" s="5"/>
       <c r="E630" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F630" s="5" t="str">
@@ -18499,7 +18796,7 @@
       <c r="C631" s="5"/>
       <c r="D631" s="5"/>
       <c r="E631" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F631" s="5" t="str">
@@ -18515,7 +18812,7 @@
       <c r="C632" s="5"/>
       <c r="D632" s="5"/>
       <c r="E632" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F632" s="5" t="str">
@@ -18531,7 +18828,7 @@
       <c r="C633" s="5"/>
       <c r="D633" s="5"/>
       <c r="E633" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F633" s="5" t="str">
@@ -18547,7 +18844,7 @@
       <c r="C634" s="5"/>
       <c r="D634" s="5"/>
       <c r="E634" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F634" s="5" t="str">
@@ -18563,7 +18860,7 @@
       <c r="C635" s="5"/>
       <c r="D635" s="5"/>
       <c r="E635" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F635" s="5" t="str">
@@ -18579,7 +18876,7 @@
       <c r="C636" s="5"/>
       <c r="D636" s="5"/>
       <c r="E636" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F636" s="5" t="str">
@@ -18595,7 +18892,7 @@
       <c r="C637" s="5"/>
       <c r="D637" s="5"/>
       <c r="E637" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F637" s="5" t="str">
@@ -18611,7 +18908,7 @@
       <c r="C638" s="5"/>
       <c r="D638" s="5"/>
       <c r="E638" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F638" s="5" t="str">
@@ -18627,7 +18924,7 @@
       <c r="C639" s="5"/>
       <c r="D639" s="5"/>
       <c r="E639" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F639" s="5" t="str">
@@ -18643,7 +18940,7 @@
       <c r="C640" s="5"/>
       <c r="D640" s="5"/>
       <c r="E640" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F640" s="5" t="str">
@@ -18659,7 +18956,7 @@
       <c r="C641" s="5"/>
       <c r="D641" s="5"/>
       <c r="E641" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F641" s="5" t="str">
@@ -18675,7 +18972,7 @@
       <c r="C642" s="5"/>
       <c r="D642" s="5"/>
       <c r="E642" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F642" s="5" t="str">
@@ -18691,7 +18988,7 @@
       <c r="C643" s="5"/>
       <c r="D643" s="5"/>
       <c r="E643" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F643" s="5" t="str">
@@ -18707,7 +19004,7 @@
       <c r="C644" s="5"/>
       <c r="D644" s="5"/>
       <c r="E644" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F644" s="5" t="str">
@@ -18723,7 +19020,7 @@
       <c r="C645" s="5"/>
       <c r="D645" s="5"/>
       <c r="E645" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F645" s="5" t="str">
@@ -18739,7 +19036,7 @@
       <c r="C646" s="5"/>
       <c r="D646" s="5"/>
       <c r="E646" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F646" s="5" t="str">
@@ -18755,7 +19052,7 @@
       <c r="C647" s="5"/>
       <c r="D647" s="5"/>
       <c r="E647" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F647" s="5" t="str">
@@ -18771,7 +19068,7 @@
       <c r="C648" s="5"/>
       <c r="D648" s="5"/>
       <c r="E648" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F648" s="5" t="str">
@@ -18787,7 +19084,7 @@
       <c r="C649" s="5"/>
       <c r="D649" s="5"/>
       <c r="E649" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F649" s="5" t="str">
@@ -18803,7 +19100,7 @@
       <c r="C650" s="5"/>
       <c r="D650" s="5"/>
       <c r="E650" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F650" s="5" t="str">
@@ -18819,7 +19116,7 @@
       <c r="C651" s="5"/>
       <c r="D651" s="5"/>
       <c r="E651" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F651" s="5" t="str">
@@ -18835,7 +19132,7 @@
       <c r="C652" s="5"/>
       <c r="D652" s="5"/>
       <c r="E652" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F652" s="5" t="str">
@@ -18851,7 +19148,7 @@
       <c r="C653" s="5"/>
       <c r="D653" s="5"/>
       <c r="E653" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F653" s="5" t="str">
@@ -18867,7 +19164,7 @@
       <c r="C654" s="5"/>
       <c r="D654" s="5"/>
       <c r="E654" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F654" s="5" t="str">
@@ -18883,7 +19180,7 @@
       <c r="C655" s="5"/>
       <c r="D655" s="5"/>
       <c r="E655" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F655" s="5" t="str">
@@ -18899,7 +19196,7 @@
       <c r="C656" s="5"/>
       <c r="D656" s="5"/>
       <c r="E656" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F656" s="5" t="str">
@@ -18915,7 +19212,7 @@
       <c r="C657" s="5"/>
       <c r="D657" s="5"/>
       <c r="E657" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F657" s="5" t="str">
@@ -18931,7 +19228,7 @@
       <c r="C658" s="5"/>
       <c r="D658" s="5"/>
       <c r="E658" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="F658" s="5" t="str">
@@ -18945,22 +19242,22 @@
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D542:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D527 D556:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B542:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B527 B556:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C542:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C527 C556:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C541" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C528:C555" xr:uid="{548560BC-83A7-43D7-A592-816C2E9E4594}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B541" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B528:B555" xr:uid="{6BCDE0D2-546F-46B0-966F-58798CFE2786}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D541" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D528:D555" xr:uid="{C138CEA5-A90B-4094-95F2-FC921D916CE0}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A6EE0EB-04BE-437B-A237-060DD9B87E63}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{830265E3-8CB7-4D00-8585-749A542A8C10}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="224">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1388,6 +1388,20 @@
     </rPh>
     <rPh sb="8" eb="10">
       <t>キリミネ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ポーチ、帽子</t>
+    <rPh sb="4" eb="6">
+      <t>ボウシ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1418,12 +1432,18 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1458,7 +1478,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1487,6 +1507,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1578,6 +1601,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10812,7 +10839,7 @@
         <v>9</v>
       </c>
       <c r="F332" s="5" t="str">
-        <f t="shared" ref="F332:F394" si="11">B332&amp;C332&amp;E332&amp;D332</f>
+        <f t="shared" ref="F332:F385" si="11">B332&amp;C332&amp;E332&amp;D332</f>
         <v>ふるさと納税-9予算</v>
       </c>
       <c r="G332" s="6">
@@ -15704,7 +15731,7 @@
         <v>3</v>
       </c>
       <c r="F512" s="5" t="str">
-        <f t="shared" ref="F512:F555" si="16">B512&amp;C512&amp;E512&amp;D512</f>
+        <f t="shared" ref="F512:F574" si="16">B512&amp;C512&amp;E512&amp;D512</f>
         <v>こずかいりょう3実績</v>
       </c>
       <c r="G512" s="6">
@@ -15914,7 +15941,7 @@
         <v>19</v>
       </c>
       <c r="E520" s="5">
-        <f t="shared" ref="E520:E555" si="17">MONTH(A520)</f>
+        <f t="shared" ref="E520:E574" si="17">MONTH(A520)</f>
         <v>3</v>
       </c>
       <c r="F520" s="5" t="str">
@@ -16895,308 +16922,514 @@
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A556" s="7"/>
-      <c r="B556" s="5"/>
-      <c r="C556" s="5"/>
-      <c r="D556" s="5"/>
+      <c r="A556" s="7">
+        <v>46133</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C556" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D556" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E556" s="5">
-        <f t="shared" ref="E556:E610" si="18">MONTH(A556)</f>
-        <v>1</v>
+        <f t="shared" si="17"/>
+        <v>4</v>
       </c>
       <c r="F556" s="5" t="str">
-        <f t="shared" ref="F453:F658" si="19">B556&amp;C556&amp;E556&amp;D556</f>
-        <v>1</v>
-      </c>
-      <c r="G556" s="6"/>
-      <c r="H556" s="6"/>
+        <f t="shared" si="16"/>
+        <v>服子供4実績</v>
+      </c>
+      <c r="G556" s="6">
+        <v>888</v>
+      </c>
+      <c r="H556" s="6" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A557" s="7"/>
-      <c r="B557" s="5"/>
-      <c r="C557" s="5"/>
-      <c r="D557" s="5"/>
+      <c r="A557" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B557" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C557" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D557" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E557" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F557" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>家賃-4実績</v>
+      </c>
+      <c r="G557" s="6">
+        <v>120829</v>
+      </c>
+      <c r="H557" s="6"/>
+    </row>
+    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A558" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D558" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E558" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F558" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>生活費-4実績</v>
+      </c>
+      <c r="G558" s="10">
+        <v>116000</v>
+      </c>
+      <c r="H558" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A559" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C559" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D559" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E559" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F559" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>光熱費ガス4実績</v>
+      </c>
+      <c r="G559" s="10">
+        <v>9000</v>
+      </c>
+      <c r="H559" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A560" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D560" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E560" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F560" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>通信料GPS4実績</v>
+      </c>
+      <c r="G560" s="6">
+        <v>0</v>
+      </c>
+      <c r="H560" s="6"/>
+    </row>
+    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A561" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D561" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E561" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F561" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>通信料ゆっこ4実績</v>
+      </c>
+      <c r="G561" s="10">
+        <v>3500</v>
+      </c>
+      <c r="H561" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A562" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D562" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E562" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F562" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>通信料りょう4実績</v>
+      </c>
+      <c r="G562" s="6">
+        <v>2931</v>
+      </c>
+      <c r="H562" s="6"/>
+    </row>
+    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A563" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C563" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E563" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F563" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>サブスクiCloud4実績</v>
+      </c>
+      <c r="G563" s="6">
+        <v>450</v>
+      </c>
+      <c r="H563" s="6"/>
+    </row>
+    <row r="564" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A564" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C564" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D564" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E564" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F564" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>習い事バレエ4実績</v>
+      </c>
+      <c r="G564" s="10">
+        <v>9020</v>
+      </c>
+      <c r="H564" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A565" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D565" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E565" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F565" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>習い事英会話4実績</v>
+      </c>
+      <c r="G565" s="6">
+        <v>2980</v>
+      </c>
+      <c r="H565" s="6"/>
+    </row>
+    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A566" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C566" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D566" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E566" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F566" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>習い事公文4実績</v>
+      </c>
+      <c r="G566" s="10">
+        <v>14960</v>
+      </c>
+      <c r="H566" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A567" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B567" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C567" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D567" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E567" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F567" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>保険ゆっこ医療4実績</v>
+      </c>
+      <c r="G567" s="6">
+        <v>2924</v>
+      </c>
+      <c r="H567" s="6"/>
+    </row>
+    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A568" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C568" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D568" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E568" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F568" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>保険りょう死亡4実績</v>
+      </c>
+      <c r="G568" s="6">
+        <v>1780</v>
+      </c>
+      <c r="H568" s="6"/>
+    </row>
+    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A569" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B569" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D569" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E569" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F569" s="5" t="str">
+        <f t="shared" si="16"/>
+        <v>保険りょう医療4実績</v>
+      </c>
+      <c r="G569" s="6">
+        <v>2572</v>
+      </c>
+      <c r="H569" s="6"/>
+    </row>
+    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A570" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B570" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C570" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D570" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E570" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F570" s="5" t="str">
+        <f>B570&amp;C570&amp;E570&amp;D570</f>
+        <v>こずかいゆっこ4実績</v>
+      </c>
+      <c r="G570" s="6">
+        <v>25000</v>
+      </c>
+      <c r="H570" s="6"/>
+    </row>
+    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A571" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B571" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D571" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E571" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F571" s="5" t="str">
+        <f t="shared" ref="F571:F572" si="18">B571&amp;C571&amp;E571&amp;D571</f>
+        <v>こずかいりょう4実績</v>
+      </c>
+      <c r="G571" s="6">
+        <v>25000</v>
+      </c>
+      <c r="H571" s="6"/>
+    </row>
+    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A572" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D572" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E572" s="5">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
+      <c r="F572" s="5" t="str">
         <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F557" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G557" s="6"/>
-      <c r="H557" s="6"/>
-    </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A558" s="7"/>
-      <c r="B558" s="5"/>
-      <c r="C558" s="5"/>
-      <c r="D558" s="5"/>
-      <c r="E558" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F558" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G558" s="6"/>
-      <c r="H558" s="6"/>
-    </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A559" s="7"/>
-      <c r="B559" s="5"/>
-      <c r="C559" s="5"/>
-      <c r="D559" s="5"/>
-      <c r="E559" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F559" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G559" s="6"/>
-      <c r="H559" s="6"/>
-    </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A560" s="7"/>
-      <c r="B560" s="5"/>
-      <c r="C560" s="5"/>
-      <c r="D560" s="5"/>
-      <c r="E560" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F560" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G560" s="6"/>
-      <c r="H560" s="6"/>
-    </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A561" s="7"/>
-      <c r="B561" s="5"/>
-      <c r="C561" s="5"/>
-      <c r="D561" s="5"/>
-      <c r="E561" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F561" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G561" s="6"/>
-      <c r="H561" s="6"/>
-    </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A562" s="7"/>
-      <c r="B562" s="5"/>
-      <c r="C562" s="5"/>
-      <c r="D562" s="5"/>
-      <c r="E562" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F562" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G562" s="6"/>
-      <c r="H562" s="6"/>
-    </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A563" s="7"/>
-      <c r="B563" s="5"/>
-      <c r="C563" s="5"/>
-      <c r="D563" s="5"/>
-      <c r="E563" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F563" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G563" s="6"/>
-      <c r="H563" s="6"/>
-    </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A564" s="7"/>
-      <c r="B564" s="5"/>
-      <c r="C564" s="5"/>
-      <c r="D564" s="5"/>
-      <c r="E564" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F564" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G564" s="6"/>
-      <c r="H564" s="6"/>
-    </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A565" s="7"/>
-      <c r="B565" s="5"/>
-      <c r="C565" s="5"/>
-      <c r="D565" s="5"/>
-      <c r="E565" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F565" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G565" s="6"/>
-      <c r="H565" s="6"/>
-    </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A566" s="7"/>
-      <c r="B566" s="5"/>
-      <c r="C566" s="5"/>
-      <c r="D566" s="5"/>
-      <c r="E566" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F566" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G566" s="6"/>
-      <c r="H566" s="6"/>
-    </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A567" s="7"/>
-      <c r="B567" s="5"/>
-      <c r="C567" s="5"/>
-      <c r="D567" s="5"/>
-      <c r="E567" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F567" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G567" s="6"/>
-      <c r="H567" s="6"/>
-    </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A568" s="7"/>
-      <c r="B568" s="5"/>
-      <c r="C568" s="5"/>
-      <c r="D568" s="5"/>
-      <c r="E568" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F568" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G568" s="6"/>
-      <c r="H568" s="6"/>
-    </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A569" s="7"/>
-      <c r="B569" s="5"/>
-      <c r="C569" s="5"/>
-      <c r="D569" s="5"/>
-      <c r="E569" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F569" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G569" s="6"/>
-      <c r="H569" s="6"/>
-    </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A570" s="7"/>
-      <c r="B570" s="5"/>
-      <c r="C570" s="5"/>
-      <c r="D570" s="5"/>
-      <c r="E570" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F570" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G570" s="6"/>
-      <c r="H570" s="6"/>
-    </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A571" s="7"/>
-      <c r="B571" s="5"/>
-      <c r="C571" s="5"/>
-      <c r="D571" s="5"/>
-      <c r="E571" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F571" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G571" s="6"/>
-      <c r="H571" s="6"/>
-    </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A572" s="7"/>
-      <c r="B572" s="5"/>
-      <c r="C572" s="5"/>
-      <c r="D572" s="5"/>
-      <c r="E572" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="F572" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G572" s="6"/>
+        <v>奨学金-4実績</v>
+      </c>
+      <c r="G572" s="6">
+        <v>10125</v>
+      </c>
       <c r="H572" s="6"/>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A573" s="7"/>
-      <c r="B573" s="5"/>
-      <c r="C573" s="5"/>
-      <c r="D573" s="5"/>
+      <c r="A573" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B573" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E573" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
+        <f t="shared" si="17"/>
+        <v>4</v>
       </c>
       <c r="F573" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G573" s="6"/>
-      <c r="H573" s="6"/>
+        <f t="shared" si="16"/>
+        <v>その他クリーニング4実績</v>
+      </c>
+      <c r="G573" s="10">
+        <v>5500</v>
+      </c>
+      <c r="H573" s="6" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A574" s="7"/>
-      <c r="B574" s="5"/>
-      <c r="C574" s="5"/>
-      <c r="D574" s="5"/>
+      <c r="A574" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B574" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C574" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D574" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E574" s="5">
-        <f t="shared" si="18"/>
-        <v>1</v>
+        <f t="shared" si="17"/>
+        <v>4</v>
       </c>
       <c r="F574" s="5" t="str">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G574" s="6"/>
-      <c r="H574" s="6"/>
+        <f t="shared" si="16"/>
+        <v>服子供4実績</v>
+      </c>
+      <c r="G574" s="6">
+        <v>2498</v>
+      </c>
+      <c r="H574" s="6" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A575" s="7"/>
@@ -17204,11 +17437,11 @@
       <c r="C575" s="5"/>
       <c r="D575" s="5"/>
       <c r="E575" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="E556:E610" si="19">MONTH(A575)</f>
         <v>1</v>
       </c>
       <c r="F575" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F556:F658" si="20">B575&amp;C575&amp;E575&amp;D575</f>
         <v>1</v>
       </c>
       <c r="G575" s="6"/>
@@ -17220,11 +17453,11 @@
       <c r="C576" s="5"/>
       <c r="D576" s="5"/>
       <c r="E576" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F576" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G576" s="6"/>
@@ -17236,11 +17469,11 @@
       <c r="C577" s="5"/>
       <c r="D577" s="5"/>
       <c r="E577" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F577" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G577" s="6"/>
@@ -17252,11 +17485,11 @@
       <c r="C578" s="5"/>
       <c r="D578" s="5"/>
       <c r="E578" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F578" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G578" s="6"/>
@@ -17268,11 +17501,11 @@
       <c r="C579" s="5"/>
       <c r="D579" s="5"/>
       <c r="E579" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F579" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G579" s="6"/>
@@ -17284,11 +17517,11 @@
       <c r="C580" s="5"/>
       <c r="D580" s="5"/>
       <c r="E580" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F580" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G580" s="6"/>
@@ -17300,11 +17533,11 @@
       <c r="C581" s="5"/>
       <c r="D581" s="5"/>
       <c r="E581" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F581" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G581" s="6"/>
@@ -17316,11 +17549,11 @@
       <c r="C582" s="5"/>
       <c r="D582" s="5"/>
       <c r="E582" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F582" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G582" s="6"/>
@@ -17332,11 +17565,11 @@
       <c r="C583" s="5"/>
       <c r="D583" s="5"/>
       <c r="E583" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F583" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G583" s="6"/>
@@ -17348,11 +17581,11 @@
       <c r="C584" s="5"/>
       <c r="D584" s="5"/>
       <c r="E584" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F584" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G584" s="6"/>
@@ -17364,11 +17597,11 @@
       <c r="C585" s="5"/>
       <c r="D585" s="5"/>
       <c r="E585" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F585" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G585" s="6"/>
@@ -17380,11 +17613,11 @@
       <c r="C586" s="5"/>
       <c r="D586" s="5"/>
       <c r="E586" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F586" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G586" s="6"/>
@@ -17396,11 +17629,11 @@
       <c r="C587" s="5"/>
       <c r="D587" s="5"/>
       <c r="E587" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F587" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G587" s="6"/>
@@ -17412,11 +17645,11 @@
       <c r="C588" s="5"/>
       <c r="D588" s="5"/>
       <c r="E588" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F588" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G588" s="6"/>
@@ -17428,11 +17661,11 @@
       <c r="C589" s="5"/>
       <c r="D589" s="5"/>
       <c r="E589" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F589" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G589" s="6"/>
@@ -17444,11 +17677,11 @@
       <c r="C590" s="5"/>
       <c r="D590" s="5"/>
       <c r="E590" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F590" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G590" s="6"/>
@@ -17460,11 +17693,11 @@
       <c r="C591" s="5"/>
       <c r="D591" s="5"/>
       <c r="E591" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F591" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G591" s="6"/>
@@ -17476,11 +17709,11 @@
       <c r="C592" s="5"/>
       <c r="D592" s="5"/>
       <c r="E592" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F592" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G592" s="6"/>
@@ -17492,11 +17725,11 @@
       <c r="C593" s="5"/>
       <c r="D593" s="5"/>
       <c r="E593" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F593" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G593" s="6"/>
@@ -17508,11 +17741,11 @@
       <c r="C594" s="5"/>
       <c r="D594" s="5"/>
       <c r="E594" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F594" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G594" s="6"/>
@@ -17524,11 +17757,11 @@
       <c r="C595" s="5"/>
       <c r="D595" s="5"/>
       <c r="E595" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F595" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G595" s="6"/>
@@ -17540,11 +17773,11 @@
       <c r="C596" s="5"/>
       <c r="D596" s="5"/>
       <c r="E596" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F596" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G596" s="6"/>
@@ -17556,11 +17789,11 @@
       <c r="C597" s="5"/>
       <c r="D597" s="5"/>
       <c r="E597" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F597" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G597" s="6"/>
@@ -17572,11 +17805,11 @@
       <c r="C598" s="5"/>
       <c r="D598" s="5"/>
       <c r="E598" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F598" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G598" s="6"/>
@@ -17588,11 +17821,11 @@
       <c r="C599" s="5"/>
       <c r="D599" s="5"/>
       <c r="E599" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F599" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G599" s="6"/>
@@ -17604,11 +17837,11 @@
       <c r="C600" s="5"/>
       <c r="D600" s="5"/>
       <c r="E600" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F600" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G600" s="6"/>
@@ -17620,11 +17853,11 @@
       <c r="C601" s="5"/>
       <c r="D601" s="5"/>
       <c r="E601" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F601" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G601" s="6"/>
@@ -17636,11 +17869,11 @@
       <c r="C602" s="5"/>
       <c r="D602" s="5"/>
       <c r="E602" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F602" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G602" s="6"/>
@@ -17652,11 +17885,11 @@
       <c r="C603" s="5"/>
       <c r="D603" s="5"/>
       <c r="E603" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F603" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G603" s="6"/>
@@ -17668,11 +17901,11 @@
       <c r="C604" s="5"/>
       <c r="D604" s="5"/>
       <c r="E604" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F604" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G604" s="6"/>
@@ -17684,11 +17917,11 @@
       <c r="C605" s="5"/>
       <c r="D605" s="5"/>
       <c r="E605" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F605" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G605" s="6"/>
@@ -17700,11 +17933,11 @@
       <c r="C606" s="5"/>
       <c r="D606" s="5"/>
       <c r="E606" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F606" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G606" s="6"/>
@@ -17716,11 +17949,11 @@
       <c r="C607" s="5"/>
       <c r="D607" s="5"/>
       <c r="E607" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F607" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G607" s="6"/>
@@ -17732,11 +17965,11 @@
       <c r="C608" s="5"/>
       <c r="D608" s="5"/>
       <c r="E608" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F608" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G608" s="6"/>
@@ -17748,11 +17981,11 @@
       <c r="C609" s="5"/>
       <c r="D609" s="5"/>
       <c r="E609" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F609" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G609" s="6"/>
@@ -17764,11 +17997,11 @@
       <c r="C610" s="5"/>
       <c r="D610" s="5"/>
       <c r="E610" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="F610" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G610" s="6"/>
@@ -17780,11 +18013,11 @@
       <c r="C611" s="5"/>
       <c r="D611" s="5"/>
       <c r="E611" s="5">
-        <f t="shared" ref="E611:E658" si="20">MONTH(A611)</f>
+        <f t="shared" ref="E611:E658" si="21">MONTH(A611)</f>
         <v>1</v>
       </c>
       <c r="F611" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="G611" s="6"/>
@@ -17796,11 +18029,11 @@
       <c r="C612" s="5"/>
       <c r="D612" s="5"/>
       <c r="E612" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F612" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F612" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G612" s="6"/>
@@ -17812,11 +18045,11 @@
       <c r="C613" s="5"/>
       <c r="D613" s="5"/>
       <c r="E613" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F613" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F613" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G613" s="6"/>
@@ -17828,11 +18061,11 @@
       <c r="C614" s="5"/>
       <c r="D614" s="5"/>
       <c r="E614" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F614" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F614" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G614" s="6"/>
@@ -17844,11 +18077,11 @@
       <c r="C615" s="5"/>
       <c r="D615" s="5"/>
       <c r="E615" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F615" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F615" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G615" s="6"/>
@@ -17860,11 +18093,11 @@
       <c r="C616" s="5"/>
       <c r="D616" s="5"/>
       <c r="E616" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F616" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F616" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G616" s="6"/>
@@ -17876,11 +18109,11 @@
       <c r="C617" s="5"/>
       <c r="D617" s="5"/>
       <c r="E617" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F617" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F617" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G617" s="6"/>
@@ -17892,11 +18125,11 @@
       <c r="C618" s="5"/>
       <c r="D618" s="5"/>
       <c r="E618" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F618" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F618" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G618" s="6"/>
@@ -17908,11 +18141,11 @@
       <c r="C619" s="5"/>
       <c r="D619" s="5"/>
       <c r="E619" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F619" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F619" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G619" s="6"/>
@@ -17924,11 +18157,11 @@
       <c r="C620" s="5"/>
       <c r="D620" s="5"/>
       <c r="E620" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F620" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F620" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G620" s="6"/>
@@ -17940,11 +18173,11 @@
       <c r="C621" s="5"/>
       <c r="D621" s="5"/>
       <c r="E621" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F621" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F621" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G621" s="6"/>
@@ -17956,11 +18189,11 @@
       <c r="C622" s="5"/>
       <c r="D622" s="5"/>
       <c r="E622" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F622" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F622" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G622" s="6"/>
@@ -17972,11 +18205,11 @@
       <c r="C623" s="5"/>
       <c r="D623" s="5"/>
       <c r="E623" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F623" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F623" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G623" s="6"/>
@@ -17988,11 +18221,11 @@
       <c r="C624" s="5"/>
       <c r="D624" s="5"/>
       <c r="E624" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F624" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F624" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G624" s="6"/>
@@ -18004,11 +18237,11 @@
       <c r="C625" s="5"/>
       <c r="D625" s="5"/>
       <c r="E625" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F625" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F625" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G625" s="6"/>
@@ -18020,11 +18253,11 @@
       <c r="C626" s="5"/>
       <c r="D626" s="5"/>
       <c r="E626" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F626" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F626" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G626" s="6"/>
@@ -18036,11 +18269,11 @@
       <c r="C627" s="5"/>
       <c r="D627" s="5"/>
       <c r="E627" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F627" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F627" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G627" s="6"/>
@@ -18052,11 +18285,11 @@
       <c r="C628" s="5"/>
       <c r="D628" s="5"/>
       <c r="E628" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F628" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F628" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G628" s="6"/>
@@ -18068,11 +18301,11 @@
       <c r="C629" s="5"/>
       <c r="D629" s="5"/>
       <c r="E629" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F629" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F629" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G629" s="6"/>
@@ -18084,11 +18317,11 @@
       <c r="C630" s="5"/>
       <c r="D630" s="5"/>
       <c r="E630" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F630" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F630" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G630" s="6"/>
@@ -18100,11 +18333,11 @@
       <c r="C631" s="5"/>
       <c r="D631" s="5"/>
       <c r="E631" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F631" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F631" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G631" s="6"/>
@@ -18116,11 +18349,11 @@
       <c r="C632" s="5"/>
       <c r="D632" s="5"/>
       <c r="E632" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F632" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G632" s="6"/>
@@ -18132,11 +18365,11 @@
       <c r="C633" s="5"/>
       <c r="D633" s="5"/>
       <c r="E633" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F633" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F633" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G633" s="6"/>
@@ -18148,11 +18381,11 @@
       <c r="C634" s="5"/>
       <c r="D634" s="5"/>
       <c r="E634" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F634" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F634" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G634" s="6"/>
@@ -18164,11 +18397,11 @@
       <c r="C635" s="5"/>
       <c r="D635" s="5"/>
       <c r="E635" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F635" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F635" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G635" s="6"/>
@@ -18180,11 +18413,11 @@
       <c r="C636" s="5"/>
       <c r="D636" s="5"/>
       <c r="E636" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F636" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F636" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G636" s="6"/>
@@ -18196,11 +18429,11 @@
       <c r="C637" s="5"/>
       <c r="D637" s="5"/>
       <c r="E637" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F637" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F637" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G637" s="6"/>
@@ -18212,11 +18445,11 @@
       <c r="C638" s="5"/>
       <c r="D638" s="5"/>
       <c r="E638" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F638" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F638" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G638" s="6"/>
@@ -18228,11 +18461,11 @@
       <c r="C639" s="5"/>
       <c r="D639" s="5"/>
       <c r="E639" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F639" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F639" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G639" s="6"/>
@@ -18244,11 +18477,11 @@
       <c r="C640" s="5"/>
       <c r="D640" s="5"/>
       <c r="E640" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F640" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F640" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G640" s="6"/>
@@ -18260,11 +18493,11 @@
       <c r="C641" s="5"/>
       <c r="D641" s="5"/>
       <c r="E641" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F641" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F641" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G641" s="6"/>
@@ -18276,11 +18509,11 @@
       <c r="C642" s="5"/>
       <c r="D642" s="5"/>
       <c r="E642" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F642" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F642" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G642" s="6"/>
@@ -18292,11 +18525,11 @@
       <c r="C643" s="5"/>
       <c r="D643" s="5"/>
       <c r="E643" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F643" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F643" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G643" s="6"/>
@@ -18308,11 +18541,11 @@
       <c r="C644" s="5"/>
       <c r="D644" s="5"/>
       <c r="E644" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F644" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F644" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G644" s="6"/>
@@ -18324,11 +18557,11 @@
       <c r="C645" s="5"/>
       <c r="D645" s="5"/>
       <c r="E645" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F645" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F645" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G645" s="6"/>
@@ -18340,11 +18573,11 @@
       <c r="C646" s="5"/>
       <c r="D646" s="5"/>
       <c r="E646" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F646" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F646" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G646" s="6"/>
@@ -18356,11 +18589,11 @@
       <c r="C647" s="5"/>
       <c r="D647" s="5"/>
       <c r="E647" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F647" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F647" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G647" s="6"/>
@@ -18372,11 +18605,11 @@
       <c r="C648" s="5"/>
       <c r="D648" s="5"/>
       <c r="E648" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F648" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F648" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G648" s="6"/>
@@ -18388,11 +18621,11 @@
       <c r="C649" s="5"/>
       <c r="D649" s="5"/>
       <c r="E649" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F649" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F649" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G649" s="6"/>
@@ -18404,11 +18637,11 @@
       <c r="C650" s="5"/>
       <c r="D650" s="5"/>
       <c r="E650" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F650" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F650" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G650" s="6"/>
@@ -18420,11 +18653,11 @@
       <c r="C651" s="5"/>
       <c r="D651" s="5"/>
       <c r="E651" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F651" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F651" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G651" s="6"/>
@@ -18436,11 +18669,11 @@
       <c r="C652" s="5"/>
       <c r="D652" s="5"/>
       <c r="E652" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F652" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F652" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G652" s="6"/>
@@ -18452,11 +18685,11 @@
       <c r="C653" s="5"/>
       <c r="D653" s="5"/>
       <c r="E653" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F653" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F653" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G653" s="6"/>
@@ -18468,11 +18701,11 @@
       <c r="C654" s="5"/>
       <c r="D654" s="5"/>
       <c r="E654" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F654" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F654" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G654" s="6"/>
@@ -18484,11 +18717,11 @@
       <c r="C655" s="5"/>
       <c r="D655" s="5"/>
       <c r="E655" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F655" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F655" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G655" s="6"/>
@@ -18500,11 +18733,11 @@
       <c r="C656" s="5"/>
       <c r="D656" s="5"/>
       <c r="E656" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F656" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F656" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G656" s="6"/>
@@ -18516,11 +18749,11 @@
       <c r="C657" s="5"/>
       <c r="D657" s="5"/>
       <c r="E657" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G657" s="6"/>
@@ -18532,11 +18765,11 @@
       <c r="C658" s="5"/>
       <c r="D658" s="5"/>
       <c r="E658" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="str">
         <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="str">
-        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="G658" s="6"/>
@@ -18546,22 +18779,22 @@
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D556:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D575:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
       <formula1>$L$2:$L$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B556:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B575:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C556:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C575:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C555" xr:uid="{30EEE32F-3918-4BA6-9B63-CADE7424ABCD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C574" xr:uid="{30EEE32F-3918-4BA6-9B63-CADE7424ABCD}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B555" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B574" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D555" xr:uid="{3680D5DC-B9FE-4A63-B348-9CF9D298C4AB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D574" xr:uid="{3680D5DC-B9FE-4A63-B348-9CF9D298C4AB}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F65A1CBA-2155-4572-82CC-0E9BBB9F4591}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F2B9FB9-DE21-4EA7-8DB8-4294F526308A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="249">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1464,6 +1464,126 @@
     <rPh sb="3" eb="4">
       <t>フクロ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仕事机横のサイドテーブル</t>
+    <rPh sb="0" eb="2">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツクエ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水着</t>
+    <rPh sb="0" eb="2">
+      <t>ミズギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マリオ映画</t>
+    <rPh sb="3" eb="5">
+      <t>エイガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>珪藻土バスマット</t>
+    <rPh sb="0" eb="3">
+      <t>ケイソウド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>資さんうどん</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>親不知抜歯</t>
+    <rPh sb="0" eb="3">
+      <t>オヤシラズ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バッシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サングラス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KEYUCA収納</t>
+    <rPh sb="6" eb="8">
+      <t>シュウノウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>キャップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>みなくん、こっちゃん耳鼻科</t>
+    <rPh sb="10" eb="13">
+      <t>ジビカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しいか靴</t>
+    <rPh sb="3" eb="4">
+      <t>クツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生活費</t>
+    <rPh sb="0" eb="3">
+      <t>セイカツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外食</t>
+    <rPh sb="0" eb="2">
+      <t>ガイショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モスバーガー</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10926,7 +11046,7 @@
         <v>9</v>
       </c>
       <c r="F333" s="5" t="str">
-        <f t="shared" ref="F333:F395" si="11">B333&amp;C333&amp;E333&amp;D333</f>
+        <f t="shared" ref="F333:F386" si="11">B333&amp;C333&amp;E333&amp;D333</f>
         <v>ふるさと納税-9予算</v>
       </c>
       <c r="G333" s="6">
@@ -18881,228 +19001,394 @@
       <c r="H626" s="6"/>
     </row>
     <row r="627" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A627" s="7"/>
-      <c r="B627" s="5"/>
-      <c r="C627" s="5"/>
-      <c r="D627" s="5"/>
+      <c r="A627" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B627" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C627" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D627" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E627" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F627" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G627" s="6">
+        <v>2788</v>
+      </c>
+      <c r="H627" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A628" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B628" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G627" s="6"/>
-      <c r="H627" s="6"/>
-    </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A628" s="7"/>
-      <c r="B628" s="5"/>
-      <c r="C628" s="5"/>
-      <c r="D628" s="5"/>
+      <c r="C628" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D628" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E628" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F628" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G628" s="6"/>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G628" s="6">
+        <v>1121</v>
+      </c>
       <c r="H628" s="6"/>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A629" s="7"/>
-      <c r="B629" s="5"/>
-      <c r="C629" s="5"/>
-      <c r="D629" s="5"/>
+      <c r="A629" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B629" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C629" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D629" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E629" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F629" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G629" s="6"/>
-      <c r="H629" s="6"/>
+        <v>学費ことは5実績</v>
+      </c>
+      <c r="G629" s="6">
+        <v>5681</v>
+      </c>
+      <c r="H629" s="6" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="630" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A630" s="7"/>
-      <c r="B630" s="5"/>
-      <c r="C630" s="5"/>
-      <c r="D630" s="5"/>
+      <c r="A630" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B630" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C630" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D630" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E630" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F630" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G630" s="6"/>
-      <c r="H630" s="6"/>
+        <v>学費みなと5実績</v>
+      </c>
+      <c r="G630" s="6">
+        <v>0</v>
+      </c>
+      <c r="H630" s="6" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="631" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A631" s="7"/>
-      <c r="B631" s="5"/>
-      <c r="C631" s="5"/>
-      <c r="D631" s="5"/>
+      <c r="A631" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B631" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D631" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E631" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F631" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G631" s="6"/>
-      <c r="H631" s="6"/>
+        <v>娯楽費その他5実績</v>
+      </c>
+      <c r="G631" s="6">
+        <v>3790</v>
+      </c>
+      <c r="H631" s="6" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="632" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A632" s="7"/>
-      <c r="B632" s="5"/>
-      <c r="C632" s="5"/>
-      <c r="D632" s="5"/>
+      <c r="A632" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B632" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C632" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D632" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E632" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F632" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G632" s="6"/>
-      <c r="H632" s="6"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G632" s="6">
+        <v>1990</v>
+      </c>
+      <c r="H632" s="6" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="633" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A633" s="7"/>
-      <c r="B633" s="5"/>
-      <c r="C633" s="5"/>
-      <c r="D633" s="5"/>
+      <c r="A633" s="7">
+        <v>46149</v>
+      </c>
+      <c r="B633" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C633" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D633" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E633" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F633" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G633" s="6"/>
-      <c r="H633" s="6"/>
+        <v>生活費外食5実績</v>
+      </c>
+      <c r="G633" s="6">
+        <v>2498</v>
+      </c>
+      <c r="H633" s="6" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="634" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A634" s="7"/>
-      <c r="B634" s="5"/>
-      <c r="C634" s="5"/>
-      <c r="D634" s="5"/>
+      <c r="A634" s="7">
+        <v>46150</v>
+      </c>
+      <c r="B634" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C634" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D634" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E634" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F634" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G634" s="6"/>
-      <c r="H634" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G634" s="6">
+        <v>2500</v>
+      </c>
+      <c r="H634" s="6" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="635" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A635" s="7"/>
-      <c r="B635" s="5"/>
-      <c r="C635" s="5"/>
-      <c r="D635" s="5"/>
+      <c r="A635" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B635" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D635" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E635" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F635" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G635" s="6"/>
-      <c r="H635" s="6"/>
+        <v>服りょう5実績</v>
+      </c>
+      <c r="G635" s="6">
+        <v>2490</v>
+      </c>
+      <c r="H635" s="6" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="636" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A636" s="7"/>
-      <c r="B636" s="5"/>
-      <c r="C636" s="5"/>
-      <c r="D636" s="5"/>
+      <c r="A636" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B636" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C636" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D636" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E636" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F636" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G636" s="6"/>
-      <c r="H636" s="6"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G636" s="6">
+        <v>1738</v>
+      </c>
+      <c r="H636" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="637" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A637" s="7"/>
-      <c r="B637" s="5"/>
-      <c r="C637" s="5"/>
-      <c r="D637" s="5"/>
+      <c r="A637" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B637" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D637" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E637" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F637" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G637" s="6"/>
-      <c r="H637" s="6"/>
+        <v>服ゆっこ5実績</v>
+      </c>
+      <c r="G637" s="6">
+        <v>2420</v>
+      </c>
+      <c r="H637" s="6" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="638" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A638" s="7"/>
-      <c r="B638" s="5"/>
-      <c r="C638" s="5"/>
-      <c r="D638" s="5"/>
+      <c r="A638" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B638" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C638" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D638" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E638" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F638" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G638" s="6"/>
-      <c r="H638" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G638" s="6">
+        <v>400</v>
+      </c>
+      <c r="H638" s="6" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A639" s="7"/>
-      <c r="B639" s="5"/>
-      <c r="C639" s="5"/>
-      <c r="D639" s="5"/>
+      <c r="A639" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B639" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D639" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E639" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F639" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G639" s="6"/>
-      <c r="H639" s="6"/>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G639" s="6">
+        <v>824</v>
+      </c>
+      <c r="H639" s="6" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="640" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A640" s="7"/>
-      <c r="B640" s="5"/>
-      <c r="C640" s="5"/>
-      <c r="D640" s="5"/>
+      <c r="A640" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B640" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C640" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D640" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E640" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F640" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G640" s="6"/>
-      <c r="H640" s="6"/>
+        <v>生活費外食5実績</v>
+      </c>
+      <c r="G640" s="6">
+        <v>1710</v>
+      </c>
+      <c r="H640" s="6" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A641" s="7"/>
@@ -19286,11 +19572,11 @@
       <c r="C652" s="5"/>
       <c r="D652" s="5"/>
       <c r="E652" s="5">
-        <f t="shared" ref="E611:E658" si="24">MONTH(A652)</f>
+        <f t="shared" ref="E652:E658" si="24">MONTH(A652)</f>
         <v>1</v>
       </c>
       <c r="F652" s="5" t="str">
-        <f t="shared" ref="F575:F658" si="25">B652&amp;C652&amp;E652&amp;D652</f>
+        <f t="shared" ref="F652:F658" si="25">B652&amp;C652&amp;E652&amp;D652</f>
         <v>1</v>
       </c>
       <c r="G652" s="6"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F2B9FB9-DE21-4EA7-8DB8-4294F526308A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD0E7933-3EC4-4885-A657-FAB766A8249D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="258">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1584,6 +1584,63 @@
   </si>
   <si>
     <t>モスバーガー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>書道セット</t>
+    <rPh sb="0" eb="2">
+      <t>ショドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう歯医者クリーニング</t>
+    <rPh sb="3" eb="6">
+      <t>ハイシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セントラルパークのパン屋</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ検査</t>
+    <rPh sb="3" eb="5">
+      <t>ケンサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう鼻うがい薬</t>
+    <rPh sb="3" eb="4">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -19391,131 +19448,221 @@
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A641" s="7"/>
-      <c r="B641" s="5"/>
-      <c r="C641" s="5"/>
-      <c r="D641" s="5"/>
+      <c r="A641" s="7">
+        <v>46152</v>
+      </c>
+      <c r="B641" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D641" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E641" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F641" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G641" s="6"/>
-      <c r="H641" s="6"/>
+        <v>学費みなと5実績</v>
+      </c>
+      <c r="G641" s="6">
+        <v>2529</v>
+      </c>
+      <c r="H641" s="5" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="642" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A642" s="7"/>
-      <c r="B642" s="5"/>
-      <c r="C642" s="5"/>
-      <c r="D642" s="5"/>
+      <c r="A642" s="7">
+        <v>46154</v>
+      </c>
+      <c r="B642" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C642" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D642" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E642" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F642" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G642" s="6">
+        <v>3590</v>
+      </c>
+      <c r="H642" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A643" s="7">
+        <v>46153</v>
+      </c>
+      <c r="B643" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G642" s="6"/>
-      <c r="H642" s="6"/>
-    </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A643" s="7"/>
-      <c r="B643" s="5"/>
-      <c r="C643" s="5"/>
-      <c r="D643" s="5"/>
+      <c r="C643" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D643" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E643" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F643" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G643" s="6"/>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G643" s="6">
+        <v>5874</v>
+      </c>
       <c r="H643" s="6"/>
     </row>
     <row r="644" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A644" s="7"/>
-      <c r="B644" s="5"/>
-      <c r="C644" s="5"/>
-      <c r="D644" s="5"/>
+      <c r="A644" s="7">
+        <v>46157</v>
+      </c>
+      <c r="B644" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C644" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D644" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E644" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F644" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G644" s="6"/>
-      <c r="H644" s="6"/>
+        <v>生活費外食5実績</v>
+      </c>
+      <c r="G644" s="6">
+        <v>2420</v>
+      </c>
+      <c r="H644" s="6" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="645" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A645" s="7"/>
-      <c r="B645" s="5"/>
-      <c r="C645" s="5"/>
-      <c r="D645" s="5"/>
+      <c r="A645" s="7">
+        <v>46157</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D645" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E645" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F645" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G645" s="6"/>
-      <c r="H645" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G645" s="6">
+        <v>1550</v>
+      </c>
+      <c r="H645" s="6" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A646" s="7"/>
-      <c r="B646" s="5"/>
-      <c r="C646" s="5"/>
-      <c r="D646" s="5"/>
+      <c r="A646" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B646" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C646" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D646" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E646" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F646" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G646" s="6"/>
-      <c r="H646" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G646" s="6">
+        <v>1100</v>
+      </c>
+      <c r="H646" s="6" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A647" s="7"/>
-      <c r="B647" s="5"/>
-      <c r="C647" s="5"/>
-      <c r="D647" s="5"/>
+      <c r="A647" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B647" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D647" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E647" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F647" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G647" s="6"/>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G647" s="6">
+        <v>1518</v>
+      </c>
       <c r="H647" s="6"/>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A648" s="7"/>
-      <c r="B648" s="5"/>
-      <c r="C648" s="5"/>
-      <c r="D648" s="5"/>
+      <c r="A648" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B648" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C648" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D648" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E648" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F648" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G648" s="6"/>
+        <v>服ゆっこ5実績</v>
+      </c>
+      <c r="G648" s="6">
+        <v>4697</v>
+      </c>
       <c r="H648" s="6"/>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.35">

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD0E7933-3EC4-4885-A657-FAB766A8249D}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88EC539B-3A1B-4D18-81FF-158B60FE0608}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="285">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1641,6 +1641,195 @@
   </si>
   <si>
     <t>ゆっこ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう耳鼻科</t>
+    <rPh sb="3" eb="6">
+      <t>ジビカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>データガバナンス書籍</t>
+    <rPh sb="8" eb="10">
+      <t>ショセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>みなくんバッグ、サンダル、こっちゃん浴衣</t>
+    <rPh sb="18" eb="20">
+      <t>ユカタ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>携帯ケース</t>
+    <rPh sb="0" eb="2">
+      <t>ケイタイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>歯医者クリーニング</t>
+    <rPh sb="0" eb="3">
+      <t>ハイシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>うがい薬</t>
+    <rPh sb="3" eb="4">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>こどもこづかい</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セブン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>交通費</t>
+    <rPh sb="0" eb="3">
+      <t>コウツウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>UNIQLO Tシャツx2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソフィーナIP ハリ弾力注入美容液 レフィル40g</t>
+    <rPh sb="10" eb="12">
+      <t>ダンリョク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チュウニュウ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ビヨウエキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ALBION 乳液 + コットン</t>
+    <rPh sb="7" eb="9">
+      <t>ニュウエキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ランドセルの背中部分につける冷たいやつ</t>
+    <rPh sb="6" eb="10">
+      <t>セナカブブン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツメ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あじくま</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>NISA積み立て</t>
+    <rPh sb="4" eb="5">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ドライヤー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこボラギノール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>りょう　歯医者</t>
+    <rPh sb="4" eb="7">
+      <t>ハイシャ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ことは　眼科</t>
+    <rPh sb="4" eb="6">
+      <t>ガンカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゆっこ　大腸内視鏡検査</t>
+    <rPh sb="4" eb="6">
+      <t>ダイチョウ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ナイシキョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンサ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鎌倉パスタ</t>
+    <rPh sb="0" eb="2">
+      <t>カマクラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mr.Olive アウター</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほっけ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5月校外学習</t>
+    <rPh sb="1" eb="2">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>コウガイガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>しいか天使組</t>
+    <rPh sb="3" eb="5">
+      <t>テンシ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>グミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>靴下</t>
+    <rPh sb="0" eb="2">
+      <t>クツシタ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1648,7 +1837,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1669,6 +1858,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1684,7 +1880,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1707,6 +1903,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1716,7 +1927,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1748,6 +1959,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1839,10 +2053,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2162,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA17BBB-6113-46DB-848C-A2EFD616B277}">
-  <dimension ref="A1:W658"/>
+  <dimension ref="A1:W708"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.640625" bestFit="1" customWidth="1"/>
@@ -19666,186 +19876,1602 @@
       <c r="H648" s="6"/>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A649" s="7"/>
-      <c r="B649" s="5"/>
-      <c r="C649" s="5"/>
-      <c r="D649" s="5"/>
+      <c r="A649" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B649" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D649" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E649" s="5">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F649" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G649" s="6"/>
-      <c r="H649" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G649" s="6">
+        <v>1550</v>
+      </c>
+      <c r="H649" s="6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A650" s="7"/>
-      <c r="B650" s="5"/>
-      <c r="C650" s="5"/>
-      <c r="D650" s="5"/>
+      <c r="A650" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B650" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C650" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D650" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E650" s="5">
-        <f t="shared" ref="E650:E651" si="23">MONTH(A650)</f>
-        <v>1</v>
+        <f t="shared" ref="E650:E708" si="23">MONTH(A650)</f>
+        <v>5</v>
       </c>
       <c r="F650" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G650" s="6"/>
-      <c r="H650" s="6"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G650" s="6">
+        <v>4690</v>
+      </c>
+      <c r="H650" s="6" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A651" s="7"/>
-      <c r="B651" s="5"/>
-      <c r="C651" s="5"/>
-      <c r="D651" s="5"/>
+      <c r="A651" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B651" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D651" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E651" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F651" s="5" t="str">
         <f t="shared" si="19"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G651" s="6">
+        <v>2996</v>
+      </c>
+      <c r="H651" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A652" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B652" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G651" s="6"/>
-      <c r="H651" s="6"/>
-    </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A652" s="7"/>
-      <c r="B652" s="5"/>
-      <c r="C652" s="5"/>
-      <c r="D652" s="5"/>
+      <c r="C652" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D652" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E652" s="5">
-        <f t="shared" ref="E652:E658" si="24">MONTH(A652)</f>
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F652" s="5" t="str">
+        <f t="shared" ref="F652:F708" si="24">B652&amp;C652&amp;E652&amp;D652</f>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G652" s="6">
+        <v>5499</v>
+      </c>
+      <c r="H652" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="653" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A653" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B653" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E653" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F653" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G653" s="6">
+        <v>2200</v>
+      </c>
+      <c r="H653" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="654" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A654" s="7">
+        <v>46164</v>
+      </c>
+      <c r="B654" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C654" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D654" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E654" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F654" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G654" s="6">
+        <v>1978</v>
+      </c>
+      <c r="H654" s="6"/>
+    </row>
+    <row r="655" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A655" s="7">
+        <v>46168</v>
+      </c>
+      <c r="B655" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D655" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E655" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F655" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G655" s="6">
+        <f>2110+610</f>
+        <v>2720</v>
+      </c>
+      <c r="H655" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A656" s="7">
+        <v>46168</v>
+      </c>
+      <c r="B656" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C656" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D656" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E656" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F656" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G656" s="6">
+        <v>1550</v>
+      </c>
+      <c r="H656" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A657" s="7">
+        <v>46166</v>
+      </c>
+      <c r="B657" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E657" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F657" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G657" s="6">
+        <v>1078</v>
+      </c>
+      <c r="H657" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A658" s="7">
+        <v>46166</v>
+      </c>
+      <c r="B658" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C658" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D658" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E658" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F658" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G658" s="6">
+        <v>1700</v>
+      </c>
+      <c r="H658" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A659" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B659" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D659" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E659" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F659" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>生活費外食5実績</v>
+      </c>
+      <c r="G659" s="6">
+        <v>1078</v>
+      </c>
+      <c r="H659" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A660" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B660" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C660" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D660" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E660" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F660" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>娯楽費その他5実績</v>
+      </c>
+      <c r="G660" s="6">
+        <v>4000</v>
+      </c>
+      <c r="H660" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A661" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B661" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D661" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E661" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F661" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他父の日/母の日/誕生日5実績</v>
+      </c>
+      <c r="G661" s="6">
+        <v>3112</v>
+      </c>
+      <c r="H661" s="6"/>
+    </row>
+    <row r="662" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A662" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B662" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F652" s="5" t="str">
-        <f t="shared" ref="F652:F658" si="25">B652&amp;C652&amp;E652&amp;D652</f>
+      <c r="C662" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D662" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E662" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F662" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服子供5実績</v>
+      </c>
+      <c r="G662" s="6">
+        <v>2580</v>
+      </c>
+      <c r="H662" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A663" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B663" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D663" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E663" s="5">
+        <f>MONTH(A663)</f>
+        <v>5</v>
+      </c>
+      <c r="F663" s="5" t="str">
+        <f>B663&amp;C663&amp;E663&amp;D663</f>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G663" s="6">
+        <v>2304</v>
+      </c>
+      <c r="H663" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A664" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B664" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C664" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D664" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E664" s="5">
+        <f>MONTH(A664)</f>
+        <v>5</v>
+      </c>
+      <c r="F664" s="5" t="str">
+        <f>B664&amp;C664&amp;E664&amp;D664</f>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G664" s="6">
+        <v>3840</v>
+      </c>
+      <c r="H664" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A665" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B665" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D665" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E665" s="5">
+        <f>MONTH(A665)</f>
+        <v>5</v>
+      </c>
+      <c r="F665" s="5" t="str">
+        <f>B665&amp;C665&amp;E665&amp;D665</f>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G665" s="6">
+        <v>6565</v>
+      </c>
+      <c r="H665" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A666" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B666" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C666" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D666" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E666" s="5">
+        <f>MONTH(A666)</f>
+        <v>5</v>
+      </c>
+      <c r="F666" s="5" t="str">
+        <f>B666&amp;C666&amp;E666&amp;D666</f>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G666" s="6">
+        <v>5918</v>
+      </c>
+      <c r="H666" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A667" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B667" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D667" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E667" s="5">
+        <f t="shared" ref="E667:E668" si="25">MONTH(A667)</f>
+        <v>5</v>
+      </c>
+      <c r="F667" s="5" t="str">
+        <f t="shared" ref="F667:F668" si="26">B667&amp;C667&amp;E667&amp;D667</f>
+        <v>学費みなと5実績</v>
+      </c>
+      <c r="G667" s="6">
+        <v>550</v>
+      </c>
+      <c r="H667" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A668" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B668" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C668" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D668" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E668" s="5">
+        <f t="shared" si="25"/>
+        <v>5</v>
+      </c>
+      <c r="F668" s="5" t="str">
+        <f t="shared" si="26"/>
+        <v>学費ことは5実績</v>
+      </c>
+      <c r="G668" s="6">
+        <v>550</v>
+      </c>
+      <c r="H668" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A669" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B669" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D669" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E669" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F669" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>学費みなと5実績</v>
+      </c>
+      <c r="G669" s="6">
+        <v>7380</v>
+      </c>
+      <c r="H669" s="6"/>
+    </row>
+    <row r="670" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A670" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B670" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C670" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D670" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E670" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F670" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>学費ことは5実績</v>
+      </c>
+      <c r="G670" s="6">
+        <v>9420</v>
+      </c>
+      <c r="H670" s="6"/>
+    </row>
+    <row r="671" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A671" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B671" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D671" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E671" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F671" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>生活費外食5実績</v>
+      </c>
+      <c r="G671" s="6">
+        <v>2750</v>
+      </c>
+      <c r="H671" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A672" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B672" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C672" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D672" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E672" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F672" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他NISA積み立て5実績</v>
+      </c>
+      <c r="G672" s="6">
+        <v>40000</v>
+      </c>
+      <c r="H672" s="6"/>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A673" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B673" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D673" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E673" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F673" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他予備費5実績</v>
+      </c>
+      <c r="G673" s="6">
+        <v>28000</v>
+      </c>
+      <c r="H673" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A674" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B674" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C674" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D674" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E674" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F674" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>化粧品-5実績</v>
+      </c>
+      <c r="G674" s="6">
+        <v>1650</v>
+      </c>
+      <c r="H674" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A675" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B675" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D675" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E675" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F675" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-5実績</v>
+      </c>
+      <c r="G675" s="6">
+        <v>2167</v>
+      </c>
+      <c r="H675" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A676" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C676" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D676" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E676" s="5">
+        <f t="shared" si="23"/>
+        <v>5</v>
+      </c>
+      <c r="F676" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>美容室りょう5実績</v>
+      </c>
+      <c r="G676" s="6">
+        <v>1300</v>
+      </c>
+      <c r="H676" s="6"/>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A677" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D677" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E677" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F677" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>生活費外食6実績</v>
+      </c>
+      <c r="G677" s="10">
+        <v>11000</v>
+      </c>
+      <c r="H677" s="6"/>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A678" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D678" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E678" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F678" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>学費みなと6実績</v>
+      </c>
+      <c r="G678" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H678" s="6"/>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A679" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D679" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E679" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F679" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>学費ことは6実績</v>
+      </c>
+      <c r="G679" s="10">
+        <v>1000</v>
+      </c>
+      <c r="H679" s="6"/>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A680" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B680" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G652" s="6"/>
-      <c r="H652" s="6"/>
-    </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A653" s="7"/>
-      <c r="B653" s="5"/>
-      <c r="C653" s="5"/>
-      <c r="D653" s="5"/>
-      <c r="E653" s="5">
+      <c r="C680" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D680" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E680" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F680" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服ゆっこ6実績</v>
+      </c>
+      <c r="G680" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H680" s="6"/>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A681" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D681" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E681" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F681" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服りょう6実績</v>
+      </c>
+      <c r="G681" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H681" s="6"/>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A682" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C682" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D682" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E682" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F682" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服子供6実績</v>
+      </c>
+      <c r="G682" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H682" s="6"/>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A683" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D683" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E683" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F683" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>美容室ゆっこ6実績</v>
+      </c>
+      <c r="G683" s="10">
+        <v>20000</v>
+      </c>
+      <c r="H683" s="6"/>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A684" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C684" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D684" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E684" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F684" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>美容室みなと6実績</v>
+      </c>
+      <c r="G684" s="10">
+        <v>1400</v>
+      </c>
+      <c r="H684" s="6"/>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A685" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D685" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E685" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F685" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>化粧品-6実績</v>
+      </c>
+      <c r="G685" s="10">
+        <v>8000</v>
+      </c>
+      <c r="H685" s="6"/>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A686" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B686" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C686" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D686" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E686" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F686" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G686" s="10">
+        <v>7600</v>
+      </c>
+      <c r="H686" s="6"/>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A687" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D687" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E687" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F687" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>ふるさと納税-6実績</v>
+      </c>
+      <c r="G687" s="10">
+        <v>16000</v>
+      </c>
+      <c r="H687" s="6"/>
+    </row>
+    <row r="688" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A688" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B688" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C688" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D688" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E688" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F688" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他NHK6実績</v>
+      </c>
+      <c r="G688" s="6">
+        <v>6309</v>
+      </c>
+      <c r="H688" s="6"/>
+    </row>
+    <row r="689" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A689" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D689" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E689" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F689" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他父の日/母の日/誕生日6実績</v>
+      </c>
+      <c r="G689" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H689" s="6"/>
+    </row>
+    <row r="690" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A690" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B690" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C690" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D690" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E690" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F690" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他予備費6実績</v>
+      </c>
+      <c r="G690" s="10">
+        <v>5000</v>
+      </c>
+      <c r="H690" s="6"/>
+    </row>
+    <row r="691" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A691" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D691" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E691" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F691" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他NISA積み立て6実績</v>
+      </c>
+      <c r="G691" s="10">
+        <v>40000</v>
+      </c>
+      <c r="H691" s="6"/>
+    </row>
+    <row r="692" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A692" s="7">
+        <v>46175</v>
+      </c>
+      <c r="B692" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C692" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D692" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E692" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F692" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G692" s="6">
+        <v>2080</v>
+      </c>
+      <c r="H692" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A693" s="7">
+        <v>46178</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D693" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E693" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F693" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G693" s="6">
+        <v>200</v>
+      </c>
+      <c r="H693" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A694" s="7">
+        <v>46178</v>
+      </c>
+      <c r="B694" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C694" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D694" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E694" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F694" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G694" s="6">
+        <v>5250</v>
+      </c>
+      <c r="H694" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A695" s="7">
+        <v>46179</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D695" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E695" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F695" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>生活費外食6実績</v>
+      </c>
+      <c r="G695" s="6">
+        <v>5962</v>
+      </c>
+      <c r="H695" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A696" s="7">
+        <v>46180</v>
+      </c>
+      <c r="B696" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C696" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D696" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E696" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F696" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服りょう6実績</v>
+      </c>
+      <c r="G696" s="6">
+        <v>6000</v>
+      </c>
+      <c r="H696" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A697" s="7">
+        <v>46180</v>
+      </c>
+      <c r="B697" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D697" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E697" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F697" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>ふるさと納税-6実績</v>
+      </c>
+      <c r="G697" s="6">
+        <v>12000</v>
+      </c>
+      <c r="H697" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A698" s="7">
+        <v>46180</v>
+      </c>
+      <c r="B698" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C698" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D698" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E698" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F698" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>ふるさと納税-6実績</v>
+      </c>
+      <c r="G698" s="6">
+        <v>12000</v>
+      </c>
+      <c r="H698" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A699" s="7">
+        <v>46192</v>
+      </c>
+      <c r="B699" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D699" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E699" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F699" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>学費みなと6実績</v>
+      </c>
+      <c r="G699" s="6">
+        <v>5035</v>
+      </c>
+      <c r="H699" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A700" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B700" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D700" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E700" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F700" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>その他予備費6実績</v>
+      </c>
+      <c r="G700" s="6">
+        <v>7000</v>
+      </c>
+      <c r="H700" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A701" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B701" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D701" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E701" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F701" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G701" s="6">
+        <v>400</v>
+      </c>
+      <c r="H701" s="6"/>
+    </row>
+    <row r="702" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A702" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B702" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D702" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E702" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F702" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服ゆっこ6実績</v>
+      </c>
+      <c r="G702" s="11">
+        <v>1419</v>
+      </c>
+      <c r="H702" s="6"/>
+    </row>
+    <row r="703" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A703" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B703" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D703" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E703" s="5">
+        <f t="shared" si="23"/>
+        <v>6</v>
+      </c>
+      <c r="F703" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>服子供6実績</v>
+      </c>
+      <c r="G703" s="11">
+        <f>1966-G702</f>
+        <v>547</v>
+      </c>
+      <c r="H703" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A704" s="7"/>
+      <c r="B704" s="5"/>
+      <c r="C704" s="5"/>
+      <c r="D704" s="5"/>
+      <c r="E704" s="5">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="F704" s="5" t="str">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="F653" s="5" t="str">
-        <f t="shared" si="25"/>
+      <c r="G704" s="6"/>
+      <c r="H704" s="6"/>
+    </row>
+    <row r="705" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A705" s="7"/>
+      <c r="B705" s="5"/>
+      <c r="C705" s="5"/>
+      <c r="D705" s="5"/>
+      <c r="E705" s="5">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="G653" s="6"/>
-      <c r="H653" s="6"/>
-    </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A654" s="7"/>
-      <c r="B654" s="5"/>
-      <c r="C654" s="5"/>
-      <c r="D654" s="5"/>
-      <c r="E654" s="5">
+      <c r="F705" s="5" t="str">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="F654" s="5" t="str">
-        <f t="shared" si="25"/>
+      <c r="G705" s="6"/>
+      <c r="H705" s="6"/>
+    </row>
+    <row r="706" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A706" s="7"/>
+      <c r="B706" s="5"/>
+      <c r="C706" s="5"/>
+      <c r="D706" s="5"/>
+      <c r="E706" s="5">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="G654" s="6"/>
-      <c r="H654" s="6"/>
-    </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A655" s="7"/>
-      <c r="B655" s="5"/>
-      <c r="C655" s="5"/>
-      <c r="D655" s="5"/>
-      <c r="E655" s="5">
+      <c r="F706" s="5" t="str">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="F655" s="5" t="str">
-        <f t="shared" si="25"/>
+      <c r="G706" s="6"/>
+      <c r="H706" s="6"/>
+    </row>
+    <row r="707" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A707" s="7"/>
+      <c r="B707" s="5"/>
+      <c r="C707" s="5"/>
+      <c r="D707" s="5"/>
+      <c r="E707" s="5">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="G655" s="6"/>
-      <c r="H655" s="6"/>
-    </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A656" s="7"/>
-      <c r="B656" s="5"/>
-      <c r="C656" s="5"/>
-      <c r="D656" s="5"/>
-      <c r="E656" s="5">
+      <c r="F707" s="5" t="str">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="F656" s="5" t="str">
-        <f t="shared" si="25"/>
+      <c r="G707" s="6"/>
+      <c r="H707" s="6"/>
+    </row>
+    <row r="708" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A708" s="7"/>
+      <c r="B708" s="5"/>
+      <c r="C708" s="5"/>
+      <c r="D708" s="5"/>
+      <c r="E708" s="5">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="G656" s="6"/>
-      <c r="H656" s="6"/>
-    </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A657" s="7"/>
-      <c r="B657" s="5"/>
-      <c r="C657" s="5"/>
-      <c r="D657" s="5"/>
-      <c r="E657" s="5">
+      <c r="F708" s="5" t="str">
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
-      <c r="F657" s="5" t="str">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="G657" s="6"/>
-      <c r="H657" s="6"/>
-    </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A658" s="7"/>
-      <c r="B658" s="5"/>
-      <c r="C658" s="5"/>
-      <c r="D658" s="5"/>
-      <c r="E658" s="5">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="str">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="G658" s="6"/>
-      <c r="H658" s="6"/>
+      <c r="G708" s="6"/>
+      <c r="H708" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D652:D658" xr:uid="{5B67F85E-9D17-4307-BDC6-AE83260D11C7}">
-      <formula1>$L$2:$L$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B652:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B709:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C652:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C709:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C651" xr:uid="{30EEE32F-3918-4BA6-9B63-CADE7424ABCD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C648" xr:uid="{30EEE32F-3918-4BA6-9B63-CADE7424ABCD}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B651" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B708" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D651" xr:uid="{9F307D87-AAFB-4A79-BE24-527506E91BA8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D708" xr:uid="{9F307D87-AAFB-4A79-BE24-527506E91BA8}">
       <formula1>$M$3:$M$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C649:C708" xr:uid="{8BC1415C-B08C-4069-82FD-0A974E4FEA99}">
+      <formula1>$L$3:$L$36</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88EC539B-3A1B-4D18-81FF-158B60FE0608}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121BA632-4A14-4A62-AA18-48B20DB33AE2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -20669,9 +20669,7 @@
         <f t="shared" si="24"/>
         <v>生活費外食6実績</v>
       </c>
-      <c r="G677" s="10">
-        <v>11000</v>
-      </c>
+      <c r="G677" s="10"/>
       <c r="H677" s="6"/>
     </row>
     <row r="678" spans="1:8" x14ac:dyDescent="0.35">
@@ -20695,9 +20693,7 @@
         <f t="shared" si="24"/>
         <v>学費みなと6実績</v>
       </c>
-      <c r="G678" s="10">
-        <v>1000</v>
-      </c>
+      <c r="G678" s="10"/>
       <c r="H678" s="6"/>
     </row>
     <row r="679" spans="1:8" x14ac:dyDescent="0.35">
@@ -20721,9 +20717,7 @@
         <f t="shared" si="24"/>
         <v>学費ことは6実績</v>
       </c>
-      <c r="G679" s="10">
-        <v>1000</v>
-      </c>
+      <c r="G679" s="10"/>
       <c r="H679" s="6"/>
     </row>
     <row r="680" spans="1:8" x14ac:dyDescent="0.35">
@@ -20747,9 +20741,7 @@
         <f t="shared" si="24"/>
         <v>服ゆっこ6実績</v>
       </c>
-      <c r="G680" s="10">
-        <v>15000</v>
-      </c>
+      <c r="G680" s="10"/>
       <c r="H680" s="6"/>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.35">
@@ -20773,9 +20765,7 @@
         <f t="shared" si="24"/>
         <v>服りょう6実績</v>
       </c>
-      <c r="G681" s="10">
-        <v>5000</v>
-      </c>
+      <c r="G681" s="10"/>
       <c r="H681" s="6"/>
     </row>
     <row r="682" spans="1:8" x14ac:dyDescent="0.35">
@@ -20799,9 +20789,7 @@
         <f t="shared" si="24"/>
         <v>服子供6実績</v>
       </c>
-      <c r="G682" s="10">
-        <v>15000</v>
-      </c>
+      <c r="G682" s="10"/>
       <c r="H682" s="6"/>
     </row>
     <row r="683" spans="1:8" x14ac:dyDescent="0.35">
@@ -20825,9 +20813,7 @@
         <f t="shared" si="24"/>
         <v>美容室ゆっこ6実績</v>
       </c>
-      <c r="G683" s="10">
-        <v>20000</v>
-      </c>
+      <c r="G683" s="10"/>
       <c r="H683" s="6"/>
     </row>
     <row r="684" spans="1:8" x14ac:dyDescent="0.35">
@@ -20851,9 +20837,7 @@
         <f t="shared" si="24"/>
         <v>美容室みなと6実績</v>
       </c>
-      <c r="G684" s="10">
-        <v>1400</v>
-      </c>
+      <c r="G684" s="10"/>
       <c r="H684" s="6"/>
     </row>
     <row r="685" spans="1:8" x14ac:dyDescent="0.35">
@@ -20877,9 +20861,7 @@
         <f t="shared" si="24"/>
         <v>化粧品-6実績</v>
       </c>
-      <c r="G685" s="10">
-        <v>8000</v>
-      </c>
+      <c r="G685" s="10"/>
       <c r="H685" s="6"/>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.35">
@@ -20903,9 +20885,7 @@
         <f t="shared" si="24"/>
         <v>医療費-6実績</v>
       </c>
-      <c r="G686" s="10">
-        <v>7600</v>
-      </c>
+      <c r="G686" s="10"/>
       <c r="H686" s="6"/>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.35">
@@ -20929,9 +20909,7 @@
         <f t="shared" si="24"/>
         <v>ふるさと納税-6実績</v>
       </c>
-      <c r="G687" s="10">
-        <v>16000</v>
-      </c>
+      <c r="G687" s="10"/>
       <c r="H687" s="6"/>
     </row>
     <row r="688" spans="1:8" x14ac:dyDescent="0.35">
@@ -20981,9 +20959,7 @@
         <f t="shared" si="24"/>
         <v>その他父の日/母の日/誕生日6実績</v>
       </c>
-      <c r="G689" s="10">
-        <v>5000</v>
-      </c>
+      <c r="G689" s="10"/>
       <c r="H689" s="6"/>
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.35">
@@ -21007,9 +20983,7 @@
         <f t="shared" si="24"/>
         <v>その他予備費6実績</v>
       </c>
-      <c r="G690" s="10">
-        <v>5000</v>
-      </c>
+      <c r="G690" s="10"/>
       <c r="H690" s="6"/>
     </row>
     <row r="691" spans="1:8" x14ac:dyDescent="0.35">
@@ -21033,9 +21007,7 @@
         <f t="shared" si="24"/>
         <v>その他NISA積み立て6実績</v>
       </c>
-      <c r="G691" s="10">
-        <v>40000</v>
-      </c>
+      <c r="G691" s="10"/>
       <c r="H691" s="6"/>
     </row>
     <row r="692" spans="1:8" x14ac:dyDescent="0.35">

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121BA632-4A14-4A62-AA18-48B20DB33AE2}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E9B4A46-E93B-492B-B3C3-FE4831384BE8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2392" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="287">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1819,17 +1819,22 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>子供</t>
+    <t>マック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一蘭</t>
     <rPh sb="0" eb="2">
-      <t>コドモ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>靴下</t>
-    <rPh sb="0" eb="2">
-      <t>クツシタ</t>
-    </rPh>
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アローズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フリークスstore　バッグ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1837,7 +1842,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1858,13 +1863,6 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1880,7 +1878,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1903,21 +1901,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1927,7 +1910,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1959,9 +1942,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2053,6 +2033,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2372,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA17BBB-6113-46DB-848C-A2EFD616B277}">
-  <dimension ref="A1:W708"/>
+  <dimension ref="A1:W715"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.640625" bestFit="1" customWidth="1"/>
@@ -19917,7 +19901,7 @@
         <v>19</v>
       </c>
       <c r="E650" s="5">
-        <f t="shared" ref="E650:E708" si="23">MONTH(A650)</f>
+        <f t="shared" ref="E650:E713" si="23">MONTH(A650)</f>
         <v>5</v>
       </c>
       <c r="F650" s="5" t="str">
@@ -19977,7 +19961,7 @@
         <v>5</v>
       </c>
       <c r="F652" s="5" t="str">
-        <f t="shared" ref="F652:F708" si="24">B652&amp;C652&amp;E652&amp;D652</f>
+        <f t="shared" ref="F652:F715" si="24">B652&amp;C652&amp;E652&amp;D652</f>
         <v>服子供5実績</v>
       </c>
       <c r="G652" s="6">
@@ -21309,7 +21293,7 @@
         <f t="shared" si="24"/>
         <v>服ゆっこ6実績</v>
       </c>
-      <c r="G702" s="11">
+      <c r="G702" s="6">
         <v>1419</v>
       </c>
       <c r="H702" s="6"/>
@@ -21322,7 +21306,7 @@
         <v>1</v>
       </c>
       <c r="C703" s="5" t="s">
-        <v>283</v>
+        <v>73</v>
       </c>
       <c r="D703" s="5" t="s">
         <v>19</v>
@@ -21335,114 +21319,284 @@
         <f t="shared" si="24"/>
         <v>服子供6実績</v>
       </c>
-      <c r="G703" s="11">
+      <c r="G703" s="6">
         <f>1966-G702</f>
         <v>547</v>
       </c>
       <c r="H703" s="6" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
     </row>
     <row r="704" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A704" s="7"/>
-      <c r="B704" s="5"/>
-      <c r="C704" s="5"/>
-      <c r="D704" s="5"/>
+      <c r="A704" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B704" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C704" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D704" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E704" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F704" s="5" t="str">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="G704" s="6"/>
+        <v>医療費-6実績</v>
+      </c>
+      <c r="G704" s="6">
+        <v>400</v>
+      </c>
       <c r="H704" s="6"/>
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A705" s="7"/>
-      <c r="B705" s="5"/>
-      <c r="C705" s="5"/>
-      <c r="D705" s="5"/>
+      <c r="A705" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D705" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E705" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F705" s="5" t="str">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="G705" s="6"/>
-      <c r="H705" s="6"/>
+        <v>生活費外食6実績</v>
+      </c>
+      <c r="G705" s="6">
+        <v>2300</v>
+      </c>
+      <c r="H705" s="6" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A706" s="7"/>
-      <c r="B706" s="5"/>
-      <c r="C706" s="5"/>
-      <c r="D706" s="5"/>
+      <c r="A706" s="7">
+        <v>46187</v>
+      </c>
+      <c r="B706" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D706" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E706" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F706" s="5" t="str">
         <f t="shared" si="24"/>
+        <v>生活費外食6実績</v>
+      </c>
+      <c r="G706" s="6">
+        <v>2380</v>
+      </c>
+      <c r="H706" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="707" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A707" s="7">
+        <v>46187</v>
+      </c>
+      <c r="B707" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G706" s="6"/>
-      <c r="H706" s="6"/>
-    </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A707" s="7"/>
-      <c r="B707" s="5"/>
-      <c r="C707" s="5"/>
-      <c r="D707" s="5"/>
+      <c r="C707" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D707" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E707" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F707" s="5" t="str">
         <f t="shared" si="24"/>
+        <v>服ゆっこ6実績</v>
+      </c>
+      <c r="G707" s="6">
+        <v>6490</v>
+      </c>
+      <c r="H707" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="708" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A708" s="7">
+        <v>46187</v>
+      </c>
+      <c r="B708" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G707" s="6"/>
-      <c r="H707" s="6"/>
-    </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A708" s="7"/>
-      <c r="B708" s="5"/>
-      <c r="C708" s="5"/>
-      <c r="D708" s="5"/>
+      <c r="C708" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D708" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E708" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F708" s="5" t="str">
         <f t="shared" si="24"/>
+        <v>服ゆっこ6実績</v>
+      </c>
+      <c r="G708" s="6">
+        <v>3998</v>
+      </c>
+      <c r="H708" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A709" s="7"/>
+      <c r="B709" s="5"/>
+      <c r="C709" s="5"/>
+      <c r="D709" s="5"/>
+      <c r="E709" s="5">
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="G708" s="6"/>
-      <c r="H708" s="6"/>
+      <c r="F709" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G709" s="6"/>
+      <c r="H709" s="6"/>
+    </row>
+    <row r="710" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A710" s="7"/>
+      <c r="B710" s="5"/>
+      <c r="C710" s="5"/>
+      <c r="D710" s="5"/>
+      <c r="E710" s="5">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G710" s="6"/>
+      <c r="H710" s="6"/>
+    </row>
+    <row r="711" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A711" s="7"/>
+      <c r="B711" s="5"/>
+      <c r="C711" s="5"/>
+      <c r="D711" s="5"/>
+      <c r="E711" s="5">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="F711" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G711" s="6"/>
+      <c r="H711" s="6"/>
+    </row>
+    <row r="712" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A712" s="7"/>
+      <c r="B712" s="5"/>
+      <c r="C712" s="5"/>
+      <c r="D712" s="5"/>
+      <c r="E712" s="5">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="F712" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G712" s="6"/>
+      <c r="H712" s="6"/>
+    </row>
+    <row r="713" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A713" s="7"/>
+      <c r="B713" s="5"/>
+      <c r="C713" s="5"/>
+      <c r="D713" s="5"/>
+      <c r="E713" s="5">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="F713" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G713" s="6"/>
+      <c r="H713" s="6"/>
+    </row>
+    <row r="714" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A714" s="7"/>
+      <c r="B714" s="5"/>
+      <c r="C714" s="5"/>
+      <c r="D714" s="5"/>
+      <c r="E714" s="5">
+        <f t="shared" ref="E714:E715" si="27">MONTH(A714)</f>
+        <v>1</v>
+      </c>
+      <c r="F714" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G714" s="6"/>
+      <c r="H714" s="6"/>
+    </row>
+    <row r="715" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A715" s="7"/>
+      <c r="B715" s="5"/>
+      <c r="C715" s="5"/>
+      <c r="D715" s="5"/>
+      <c r="E715" s="5">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="F715" s="5" t="str">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="G715" s="6"/>
+      <c r="H715" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B709:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B716:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C709:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C716:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C648" xr:uid="{30EEE32F-3918-4BA6-9B63-CADE7424ABCD}">
       <formula1>$L$3:$L$35</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B708" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B715" xr:uid="{6F660A3A-19A7-4B4F-83F5-0346813C75F4}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D708" xr:uid="{9F307D87-AAFB-4A79-BE24-527506E91BA8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D715" xr:uid="{9F307D87-AAFB-4A79-BE24-527506E91BA8}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C649:C708" xr:uid="{8BC1415C-B08C-4069-82FD-0A974E4FEA99}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C649:C715" xr:uid="{8BC1415C-B08C-4069-82FD-0A974E4FEA99}">
       <formula1>$L$3:$L$36</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4286AAB-C89F-4536-98F1-B3F08923DDE7}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E960F7-461E-4810-BF01-CE1CCC61A19A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="313">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1936,6 +1936,110 @@
     <t>ソフィーナ ip 300ml 化粧水</t>
     <rPh sb="15" eb="18">
       <t>ケショウスイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>娯楽費</t>
+    <rPh sb="0" eb="3">
+      <t>ゴラクヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プリキュア映画チケ</t>
+    <rPh sb="5" eb="7">
+      <t>エイガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>服</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>子供</t>
+    <rPh sb="0" eb="2">
+      <t>コドモ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>医療費</t>
+    <rPh sb="0" eb="3">
+      <t>イリョウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>みなくん耳鼻科</t>
+    <rPh sb="4" eb="7">
+      <t>ジビカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生活費</t>
+    <rPh sb="0" eb="3">
+      <t>セイカツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ココス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>肌着</t>
+    <rPh sb="0" eb="2">
+      <t>ハダギ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイシャドウ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ファンデーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マスカラ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光熱費</t>
+    <rPh sb="0" eb="3">
+      <t>コウネツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>電気</t>
+    <rPh sb="0" eb="2">
+      <t>デンキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>実績</t>
+    <rPh sb="0" eb="2">
+      <t>ジッセキ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1966,18 +2070,12 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2012,7 +2110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2041,9 +2139,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -2138,6 +2233,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2457,7 +2556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA17BBB-6113-46DB-848C-A2EFD616B277}">
-  <dimension ref="A1:W728"/>
+  <dimension ref="A1:W940"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.640625" bestFit="1" customWidth="1"/>
@@ -17876,7 +17975,7 @@
       <c r="G571" s="6">
         <v>2931</v>
       </c>
-      <c r="H571" s="11" t="s">
+      <c r="H571" s="10" t="s">
         <v>278</v>
       </c>
     </row>
@@ -18240,7 +18339,7 @@
         <v>4</v>
       </c>
       <c r="F585" s="5" t="str">
-        <f t="shared" ref="F585:F728" si="19">B585&amp;C585&amp;E585&amp;D585</f>
+        <f t="shared" ref="F585:F723" si="19">B585&amp;C585&amp;E585&amp;D585</f>
         <v>服りょう4実績</v>
       </c>
       <c r="G585" s="6">
@@ -18712,7 +18811,7 @@
       <c r="G602" s="6">
         <v>3065</v>
       </c>
-      <c r="H602" s="11" t="s">
+      <c r="H602" s="10" t="s">
         <v>281</v>
       </c>
     </row>
@@ -19024,12 +19123,10 @@
         <f t="shared" si="21"/>
         <v>生活費-6実績</v>
       </c>
-      <c r="G614" s="10">
-        <v>115000</v>
-      </c>
-      <c r="H614" s="6" t="s">
-        <v>192</v>
-      </c>
+      <c r="G614" s="6">
+        <v>114000</v>
+      </c>
+      <c r="H614" s="6"/>
     </row>
     <row r="615" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A615" s="7">
@@ -19189,7 +19286,7 @@
       <c r="G620" s="6">
         <v>2931</v>
       </c>
-      <c r="H620" s="11" t="s">
+      <c r="H620" s="10" t="s">
         <v>283</v>
       </c>
     </row>
@@ -20161,7 +20258,7 @@
         <v>19</v>
       </c>
       <c r="E656" s="5">
-        <f t="shared" ref="E656:E728" si="23">MONTH(A656)</f>
+        <f t="shared" ref="E656:E723" si="23">MONTH(A656)</f>
         <v>5</v>
       </c>
       <c r="F656" s="5" t="str">
@@ -21750,163 +21847,278 @@
       </c>
     </row>
     <row r="714" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A714" s="7"/>
-      <c r="B714" s="5"/>
-      <c r="C714" s="5"/>
-      <c r="D714" s="5"/>
+      <c r="A714" s="7">
+        <v>46204</v>
+      </c>
+      <c r="B714" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D714" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E714" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F714" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G714" s="6"/>
-      <c r="H714" s="6"/>
+        <v>娯楽費その他7実績</v>
+      </c>
+      <c r="G714" s="6">
+        <v>2500</v>
+      </c>
+      <c r="H714" s="6" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A715" s="7"/>
-      <c r="B715" s="5"/>
-      <c r="C715" s="5"/>
-      <c r="D715" s="5"/>
+      <c r="A715" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B715" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D715" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E715" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F715" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G715" s="6"/>
+        <v>服子供7実績</v>
+      </c>
+      <c r="G715" s="6">
+        <v>1408</v>
+      </c>
       <c r="H715" s="6"/>
     </row>
     <row r="716" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A716" s="7"/>
-      <c r="B716" s="5"/>
-      <c r="C716" s="5"/>
-      <c r="D716" s="5"/>
+      <c r="A716" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B716" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C716" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D716" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E716" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F716" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G716" s="6"/>
-      <c r="H716" s="6"/>
+        <v>医療費-7実績</v>
+      </c>
+      <c r="G716" s="6">
+        <v>200</v>
+      </c>
+      <c r="H716" s="6" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A717" s="7"/>
-      <c r="B717" s="5"/>
-      <c r="C717" s="5"/>
-      <c r="D717" s="5"/>
+      <c r="A717" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B717" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D717" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E717" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F717" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G717" s="6"/>
-      <c r="H717" s="6"/>
+        <v>生活費外食7実績</v>
+      </c>
+      <c r="G717" s="6">
+        <v>6017</v>
+      </c>
+      <c r="H717" s="6" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A718" s="7"/>
-      <c r="B718" s="5"/>
-      <c r="C718" s="5"/>
-      <c r="D718" s="5"/>
+      <c r="A718" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B718" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D718" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E718" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F718" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G718" s="6"/>
-      <c r="H718" s="6"/>
+        <v>服子供7実績</v>
+      </c>
+      <c r="G718" s="6">
+        <v>966</v>
+      </c>
+      <c r="H718" s="6" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A719" s="7"/>
-      <c r="B719" s="5"/>
-      <c r="C719" s="5"/>
-      <c r="D719" s="5"/>
+      <c r="A719" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B719" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D719" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E719" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F719" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G719" s="6"/>
-      <c r="H719" s="6"/>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G719" s="6">
+        <v>7700</v>
+      </c>
+      <c r="H719" s="6" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A720" s="7"/>
-      <c r="B720" s="5"/>
-      <c r="C720" s="5"/>
-      <c r="D720" s="5"/>
+      <c r="A720" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B720" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D720" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E720" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F720" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G720" s="6"/>
-      <c r="H720" s="6"/>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G720" s="6">
+        <v>7700</v>
+      </c>
+      <c r="H720" s="6" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A721" s="7"/>
-      <c r="B721" s="5"/>
-      <c r="C721" s="5"/>
-      <c r="D721" s="5"/>
+      <c r="A721" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B721" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D721" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E721" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F721" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G721" s="6"/>
-      <c r="H721" s="6"/>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G721" s="6">
+        <v>1870</v>
+      </c>
+      <c r="H721" s="6" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A722" s="7"/>
-      <c r="B722" s="5"/>
-      <c r="C722" s="5"/>
-      <c r="D722" s="5"/>
+      <c r="A722" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B722" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D722" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E722" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F722" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G722" s="6"/>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G722" s="6">
+        <f>3554-1870+1100</f>
+        <v>2784</v>
+      </c>
       <c r="H722" s="6"/>
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A723" s="7"/>
-      <c r="B723" s="5"/>
-      <c r="C723" s="5"/>
-      <c r="D723" s="5"/>
+      <c r="A723" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B723" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D723" s="5" t="s">
+        <v>312</v>
+      </c>
       <c r="E723" s="5">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F723" s="5" t="str">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="G723" s="6"/>
+        <v>光熱費電気7実績</v>
+      </c>
+      <c r="G723" s="6">
+        <v>11883</v>
+      </c>
       <c r="H723" s="6"/>
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.35">
@@ -21915,11 +22127,11 @@
       <c r="C724" s="5"/>
       <c r="D724" s="5"/>
       <c r="E724" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="E656:E728" si="26">MONTH(A724)</f>
         <v>1</v>
       </c>
       <c r="F724" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F585:F728" si="27">B724&amp;C724&amp;E724&amp;D724</f>
         <v>1</v>
       </c>
       <c r="G724" s="6"/>
@@ -21931,11 +22143,11 @@
       <c r="C725" s="5"/>
       <c r="D725" s="5"/>
       <c r="E725" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F725" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G725" s="6"/>
@@ -21947,11 +22159,11 @@
       <c r="C726" s="5"/>
       <c r="D726" s="5"/>
       <c r="E726" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F726" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G726" s="6"/>
@@ -21963,11 +22175,11 @@
       <c r="C727" s="5"/>
       <c r="D727" s="5"/>
       <c r="E727" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F727" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G727" s="6"/>
@@ -21979,33 +22191,3425 @@
       <c r="C728" s="5"/>
       <c r="D728" s="5"/>
       <c r="E728" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="E728:E791" si="28">MONTH(A728)</f>
         <v>1</v>
       </c>
       <c r="F728" s="5" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F728:F791" si="29">B728&amp;C728&amp;E728&amp;D728</f>
         <v>1</v>
       </c>
       <c r="G728" s="6"/>
       <c r="H728" s="6"/>
+    </row>
+    <row r="729" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A729" s="7"/>
+      <c r="B729" s="5"/>
+      <c r="C729" s="5"/>
+      <c r="D729" s="5"/>
+      <c r="E729" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F729" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G729" s="6"/>
+      <c r="H729" s="6"/>
+    </row>
+    <row r="730" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A730" s="7"/>
+      <c r="B730" s="5"/>
+      <c r="C730" s="5"/>
+      <c r="D730" s="5"/>
+      <c r="E730" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F730" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G730" s="6"/>
+      <c r="H730" s="6"/>
+    </row>
+    <row r="731" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A731" s="7"/>
+      <c r="B731" s="5"/>
+      <c r="C731" s="5"/>
+      <c r="D731" s="5"/>
+      <c r="E731" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F731" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G731" s="6"/>
+      <c r="H731" s="6"/>
+    </row>
+    <row r="732" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A732" s="7"/>
+      <c r="B732" s="5"/>
+      <c r="C732" s="5"/>
+      <c r="D732" s="5"/>
+      <c r="E732" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F732" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G732" s="6"/>
+      <c r="H732" s="6"/>
+    </row>
+    <row r="733" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A733" s="7"/>
+      <c r="B733" s="5"/>
+      <c r="C733" s="5"/>
+      <c r="D733" s="5"/>
+      <c r="E733" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F733" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G733" s="6"/>
+      <c r="H733" s="6"/>
+    </row>
+    <row r="734" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A734" s="7"/>
+      <c r="B734" s="5"/>
+      <c r="C734" s="5"/>
+      <c r="D734" s="5"/>
+      <c r="E734" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F734" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G734" s="6"/>
+      <c r="H734" s="6"/>
+    </row>
+    <row r="735" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A735" s="7"/>
+      <c r="B735" s="5"/>
+      <c r="C735" s="5"/>
+      <c r="D735" s="5"/>
+      <c r="E735" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G735" s="6"/>
+      <c r="H735" s="6"/>
+    </row>
+    <row r="736" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A736" s="7"/>
+      <c r="B736" s="5"/>
+      <c r="C736" s="5"/>
+      <c r="D736" s="5"/>
+      <c r="E736" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G736" s="6"/>
+      <c r="H736" s="6"/>
+    </row>
+    <row r="737" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A737" s="7"/>
+      <c r="B737" s="5"/>
+      <c r="C737" s="5"/>
+      <c r="D737" s="5"/>
+      <c r="E737" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F737" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G737" s="6"/>
+      <c r="H737" s="6"/>
+    </row>
+    <row r="738" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A738" s="7"/>
+      <c r="B738" s="5"/>
+      <c r="C738" s="5"/>
+      <c r="D738" s="5"/>
+      <c r="E738" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F738" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G738" s="6"/>
+      <c r="H738" s="6"/>
+    </row>
+    <row r="739" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A739" s="7"/>
+      <c r="B739" s="5"/>
+      <c r="C739" s="5"/>
+      <c r="D739" s="5"/>
+      <c r="E739" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F739" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G739" s="6"/>
+      <c r="H739" s="6"/>
+    </row>
+    <row r="740" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A740" s="7"/>
+      <c r="B740" s="5"/>
+      <c r="C740" s="5"/>
+      <c r="D740" s="5"/>
+      <c r="E740" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F740" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G740" s="6"/>
+      <c r="H740" s="6"/>
+    </row>
+    <row r="741" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A741" s="7"/>
+      <c r="B741" s="5"/>
+      <c r="C741" s="5"/>
+      <c r="D741" s="5"/>
+      <c r="E741" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F741" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G741" s="6"/>
+      <c r="H741" s="6"/>
+    </row>
+    <row r="742" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A742" s="7"/>
+      <c r="B742" s="5"/>
+      <c r="C742" s="5"/>
+      <c r="D742" s="5"/>
+      <c r="E742" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F742" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G742" s="6"/>
+      <c r="H742" s="6"/>
+    </row>
+    <row r="743" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A743" s="7"/>
+      <c r="B743" s="5"/>
+      <c r="C743" s="5"/>
+      <c r="D743" s="5"/>
+      <c r="E743" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F743" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G743" s="6"/>
+      <c r="H743" s="6"/>
+    </row>
+    <row r="744" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A744" s="7"/>
+      <c r="B744" s="5"/>
+      <c r="C744" s="5"/>
+      <c r="D744" s="5"/>
+      <c r="E744" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F744" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G744" s="6"/>
+      <c r="H744" s="6"/>
+    </row>
+    <row r="745" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A745" s="7"/>
+      <c r="B745" s="5"/>
+      <c r="C745" s="5"/>
+      <c r="D745" s="5"/>
+      <c r="E745" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F745" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G745" s="6"/>
+      <c r="H745" s="6"/>
+    </row>
+    <row r="746" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A746" s="7"/>
+      <c r="B746" s="5"/>
+      <c r="C746" s="5"/>
+      <c r="D746" s="5"/>
+      <c r="E746" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F746" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G746" s="6"/>
+      <c r="H746" s="6"/>
+    </row>
+    <row r="747" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A747" s="7"/>
+      <c r="B747" s="5"/>
+      <c r="C747" s="5"/>
+      <c r="D747" s="5"/>
+      <c r="E747" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F747" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G747" s="6"/>
+      <c r="H747" s="6"/>
+    </row>
+    <row r="748" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A748" s="7"/>
+      <c r="B748" s="5"/>
+      <c r="C748" s="5"/>
+      <c r="D748" s="5"/>
+      <c r="E748" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F748" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G748" s="6"/>
+      <c r="H748" s="6"/>
+    </row>
+    <row r="749" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A749" s="7"/>
+      <c r="B749" s="5"/>
+      <c r="C749" s="5"/>
+      <c r="D749" s="5"/>
+      <c r="E749" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F749" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G749" s="6"/>
+      <c r="H749" s="6"/>
+    </row>
+    <row r="750" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A750" s="7"/>
+      <c r="B750" s="5"/>
+      <c r="C750" s="5"/>
+      <c r="D750" s="5"/>
+      <c r="E750" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F750" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G750" s="6"/>
+      <c r="H750" s="6"/>
+    </row>
+    <row r="751" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A751" s="7"/>
+      <c r="B751" s="5"/>
+      <c r="C751" s="5"/>
+      <c r="D751" s="5"/>
+      <c r="E751" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F751" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G751" s="6"/>
+      <c r="H751" s="6"/>
+    </row>
+    <row r="752" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A752" s="7"/>
+      <c r="B752" s="5"/>
+      <c r="C752" s="5"/>
+      <c r="D752" s="5"/>
+      <c r="E752" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F752" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G752" s="6"/>
+      <c r="H752" s="6"/>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A753" s="7"/>
+      <c r="B753" s="5"/>
+      <c r="C753" s="5"/>
+      <c r="D753" s="5"/>
+      <c r="E753" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F753" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G753" s="6"/>
+      <c r="H753" s="6"/>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A754" s="7"/>
+      <c r="B754" s="5"/>
+      <c r="C754" s="5"/>
+      <c r="D754" s="5"/>
+      <c r="E754" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F754" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G754" s="6"/>
+      <c r="H754" s="6"/>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A755" s="7"/>
+      <c r="B755" s="5"/>
+      <c r="C755" s="5"/>
+      <c r="D755" s="5"/>
+      <c r="E755" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F755" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G755" s="6"/>
+      <c r="H755" s="6"/>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A756" s="7"/>
+      <c r="B756" s="5"/>
+      <c r="C756" s="5"/>
+      <c r="D756" s="5"/>
+      <c r="E756" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F756" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G756" s="6"/>
+      <c r="H756" s="6"/>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A757" s="7"/>
+      <c r="B757" s="5"/>
+      <c r="C757" s="5"/>
+      <c r="D757" s="5"/>
+      <c r="E757" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F757" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G757" s="6"/>
+      <c r="H757" s="6"/>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A758" s="7"/>
+      <c r="B758" s="5"/>
+      <c r="C758" s="5"/>
+      <c r="D758" s="5"/>
+      <c r="E758" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F758" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G758" s="6"/>
+      <c r="H758" s="6"/>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A759" s="7"/>
+      <c r="B759" s="5"/>
+      <c r="C759" s="5"/>
+      <c r="D759" s="5"/>
+      <c r="E759" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F759" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G759" s="6"/>
+      <c r="H759" s="6"/>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A760" s="7"/>
+      <c r="B760" s="5"/>
+      <c r="C760" s="5"/>
+      <c r="D760" s="5"/>
+      <c r="E760" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F760" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G760" s="6"/>
+      <c r="H760" s="6"/>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A761" s="7"/>
+      <c r="B761" s="5"/>
+      <c r="C761" s="5"/>
+      <c r="D761" s="5"/>
+      <c r="E761" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G761" s="6"/>
+      <c r="H761" s="6"/>
+    </row>
+    <row r="762" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A762" s="7"/>
+      <c r="B762" s="5"/>
+      <c r="C762" s="5"/>
+      <c r="D762" s="5"/>
+      <c r="E762" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G762" s="6"/>
+      <c r="H762" s="6"/>
+    </row>
+    <row r="763" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A763" s="7"/>
+      <c r="B763" s="5"/>
+      <c r="C763" s="5"/>
+      <c r="D763" s="5"/>
+      <c r="E763" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F763" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G763" s="6"/>
+      <c r="H763" s="6"/>
+    </row>
+    <row r="764" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A764" s="7"/>
+      <c r="B764" s="5"/>
+      <c r="C764" s="5"/>
+      <c r="D764" s="5"/>
+      <c r="E764" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F764" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G764" s="6"/>
+      <c r="H764" s="6"/>
+    </row>
+    <row r="765" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A765" s="7"/>
+      <c r="B765" s="5"/>
+      <c r="C765" s="5"/>
+      <c r="D765" s="5"/>
+      <c r="E765" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F765" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G765" s="6"/>
+      <c r="H765" s="6"/>
+    </row>
+    <row r="766" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A766" s="7"/>
+      <c r="B766" s="5"/>
+      <c r="C766" s="5"/>
+      <c r="D766" s="5"/>
+      <c r="E766" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F766" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G766" s="6"/>
+      <c r="H766" s="6"/>
+    </row>
+    <row r="767" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A767" s="7"/>
+      <c r="B767" s="5"/>
+      <c r="C767" s="5"/>
+      <c r="D767" s="5"/>
+      <c r="E767" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F767" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G767" s="6"/>
+      <c r="H767" s="6"/>
+    </row>
+    <row r="768" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A768" s="7"/>
+      <c r="B768" s="5"/>
+      <c r="C768" s="5"/>
+      <c r="D768" s="5"/>
+      <c r="E768" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F768" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G768" s="6"/>
+      <c r="H768" s="6"/>
+    </row>
+    <row r="769" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A769" s="7"/>
+      <c r="B769" s="5"/>
+      <c r="C769" s="5"/>
+      <c r="D769" s="5"/>
+      <c r="E769" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F769" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G769" s="6"/>
+      <c r="H769" s="6"/>
+    </row>
+    <row r="770" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A770" s="7"/>
+      <c r="B770" s="5"/>
+      <c r="C770" s="5"/>
+      <c r="D770" s="5"/>
+      <c r="E770" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F770" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G770" s="6"/>
+      <c r="H770" s="6"/>
+    </row>
+    <row r="771" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A771" s="7"/>
+      <c r="B771" s="5"/>
+      <c r="C771" s="5"/>
+      <c r="D771" s="5"/>
+      <c r="E771" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F771" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G771" s="6"/>
+      <c r="H771" s="6"/>
+    </row>
+    <row r="772" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A772" s="7"/>
+      <c r="B772" s="5"/>
+      <c r="C772" s="5"/>
+      <c r="D772" s="5"/>
+      <c r="E772" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F772" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G772" s="6"/>
+      <c r="H772" s="6"/>
+    </row>
+    <row r="773" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A773" s="7"/>
+      <c r="B773" s="5"/>
+      <c r="C773" s="5"/>
+      <c r="D773" s="5"/>
+      <c r="E773" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F773" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G773" s="6"/>
+      <c r="H773" s="6"/>
+    </row>
+    <row r="774" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A774" s="7"/>
+      <c r="B774" s="5"/>
+      <c r="C774" s="5"/>
+      <c r="D774" s="5"/>
+      <c r="E774" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F774" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G774" s="6"/>
+      <c r="H774" s="6"/>
+    </row>
+    <row r="775" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A775" s="7"/>
+      <c r="B775" s="5"/>
+      <c r="C775" s="5"/>
+      <c r="D775" s="5"/>
+      <c r="E775" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F775" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G775" s="6"/>
+      <c r="H775" s="6"/>
+    </row>
+    <row r="776" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A776" s="7"/>
+      <c r="B776" s="5"/>
+      <c r="C776" s="5"/>
+      <c r="D776" s="5"/>
+      <c r="E776" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F776" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G776" s="6"/>
+      <c r="H776" s="6"/>
+    </row>
+    <row r="777" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A777" s="7"/>
+      <c r="B777" s="5"/>
+      <c r="C777" s="5"/>
+      <c r="D777" s="5"/>
+      <c r="E777" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F777" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G777" s="6"/>
+      <c r="H777" s="6"/>
+    </row>
+    <row r="778" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A778" s="7"/>
+      <c r="B778" s="5"/>
+      <c r="C778" s="5"/>
+      <c r="D778" s="5"/>
+      <c r="E778" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F778" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G778" s="6"/>
+      <c r="H778" s="6"/>
+    </row>
+    <row r="779" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A779" s="7"/>
+      <c r="B779" s="5"/>
+      <c r="C779" s="5"/>
+      <c r="D779" s="5"/>
+      <c r="E779" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F779" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G779" s="6"/>
+      <c r="H779" s="6"/>
+    </row>
+    <row r="780" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A780" s="7"/>
+      <c r="B780" s="5"/>
+      <c r="C780" s="5"/>
+      <c r="D780" s="5"/>
+      <c r="E780" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F780" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G780" s="6"/>
+      <c r="H780" s="6"/>
+    </row>
+    <row r="781" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A781" s="7"/>
+      <c r="B781" s="5"/>
+      <c r="C781" s="5"/>
+      <c r="D781" s="5"/>
+      <c r="E781" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F781" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G781" s="6"/>
+      <c r="H781" s="6"/>
+    </row>
+    <row r="782" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A782" s="7"/>
+      <c r="B782" s="5"/>
+      <c r="C782" s="5"/>
+      <c r="D782" s="5"/>
+      <c r="E782" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F782" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G782" s="6"/>
+      <c r="H782" s="6"/>
+    </row>
+    <row r="783" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A783" s="7"/>
+      <c r="B783" s="5"/>
+      <c r="C783" s="5"/>
+      <c r="D783" s="5"/>
+      <c r="E783" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F783" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G783" s="6"/>
+      <c r="H783" s="6"/>
+    </row>
+    <row r="784" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A784" s="7"/>
+      <c r="B784" s="5"/>
+      <c r="C784" s="5"/>
+      <c r="D784" s="5"/>
+      <c r="E784" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F784" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G784" s="6"/>
+      <c r="H784" s="6"/>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A785" s="7"/>
+      <c r="B785" s="5"/>
+      <c r="C785" s="5"/>
+      <c r="D785" s="5"/>
+      <c r="E785" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F785" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G785" s="6"/>
+      <c r="H785" s="6"/>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A786" s="7"/>
+      <c r="B786" s="5"/>
+      <c r="C786" s="5"/>
+      <c r="D786" s="5"/>
+      <c r="E786" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F786" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G786" s="6"/>
+      <c r="H786" s="6"/>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A787" s="7"/>
+      <c r="B787" s="5"/>
+      <c r="C787" s="5"/>
+      <c r="D787" s="5"/>
+      <c r="E787" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F787" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G787" s="6"/>
+      <c r="H787" s="6"/>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A788" s="7"/>
+      <c r="B788" s="5"/>
+      <c r="C788" s="5"/>
+      <c r="D788" s="5"/>
+      <c r="E788" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F788" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G788" s="6"/>
+      <c r="H788" s="6"/>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A789" s="7"/>
+      <c r="B789" s="5"/>
+      <c r="C789" s="5"/>
+      <c r="D789" s="5"/>
+      <c r="E789" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F789" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G789" s="6"/>
+      <c r="H789" s="6"/>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A790" s="7"/>
+      <c r="B790" s="5"/>
+      <c r="C790" s="5"/>
+      <c r="D790" s="5"/>
+      <c r="E790" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F790" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G790" s="6"/>
+      <c r="H790" s="6"/>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A791" s="7"/>
+      <c r="B791" s="5"/>
+      <c r="C791" s="5"/>
+      <c r="D791" s="5"/>
+      <c r="E791" s="5">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="F791" s="5" t="str">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="G791" s="6"/>
+      <c r="H791" s="6"/>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A792" s="7"/>
+      <c r="B792" s="5"/>
+      <c r="C792" s="5"/>
+      <c r="D792" s="5"/>
+      <c r="E792" s="5">
+        <f t="shared" ref="E792:E855" si="30">MONTH(A792)</f>
+        <v>1</v>
+      </c>
+      <c r="F792" s="5" t="str">
+        <f t="shared" ref="F792:F855" si="31">B792&amp;C792&amp;E792&amp;D792</f>
+        <v>1</v>
+      </c>
+      <c r="G792" s="6"/>
+      <c r="H792" s="6"/>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A793" s="7"/>
+      <c r="B793" s="5"/>
+      <c r="C793" s="5"/>
+      <c r="D793" s="5"/>
+      <c r="E793" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F793" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G793" s="6"/>
+      <c r="H793" s="6"/>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A794" s="7"/>
+      <c r="B794" s="5"/>
+      <c r="C794" s="5"/>
+      <c r="D794" s="5"/>
+      <c r="E794" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F794" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G794" s="6"/>
+      <c r="H794" s="6"/>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A795" s="7"/>
+      <c r="B795" s="5"/>
+      <c r="C795" s="5"/>
+      <c r="D795" s="5"/>
+      <c r="E795" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F795" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G795" s="6"/>
+      <c r="H795" s="6"/>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A796" s="7"/>
+      <c r="B796" s="5"/>
+      <c r="C796" s="5"/>
+      <c r="D796" s="5"/>
+      <c r="E796" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F796" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G796" s="6"/>
+      <c r="H796" s="6"/>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A797" s="7"/>
+      <c r="B797" s="5"/>
+      <c r="C797" s="5"/>
+      <c r="D797" s="5"/>
+      <c r="E797" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F797" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G797" s="6"/>
+      <c r="H797" s="6"/>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A798" s="7"/>
+      <c r="B798" s="5"/>
+      <c r="C798" s="5"/>
+      <c r="D798" s="5"/>
+      <c r="E798" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F798" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G798" s="6"/>
+      <c r="H798" s="6"/>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A799" s="7"/>
+      <c r="B799" s="5"/>
+      <c r="C799" s="5"/>
+      <c r="D799" s="5"/>
+      <c r="E799" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F799" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G799" s="6"/>
+      <c r="H799" s="6"/>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A800" s="7"/>
+      <c r="B800" s="5"/>
+      <c r="C800" s="5"/>
+      <c r="D800" s="5"/>
+      <c r="E800" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F800" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G800" s="6"/>
+      <c r="H800" s="6"/>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A801" s="7"/>
+      <c r="B801" s="5"/>
+      <c r="C801" s="5"/>
+      <c r="D801" s="5"/>
+      <c r="E801" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F801" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G801" s="6"/>
+      <c r="H801" s="6"/>
+    </row>
+    <row r="802" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A802" s="7"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="5"/>
+      <c r="D802" s="5"/>
+      <c r="E802" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F802" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G802" s="6"/>
+      <c r="H802" s="6"/>
+    </row>
+    <row r="803" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A803" s="7"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="5"/>
+      <c r="D803" s="5"/>
+      <c r="E803" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F803" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G803" s="6"/>
+      <c r="H803" s="6"/>
+    </row>
+    <row r="804" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A804" s="7"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="5"/>
+      <c r="D804" s="5"/>
+      <c r="E804" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F804" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G804" s="6"/>
+      <c r="H804" s="6"/>
+    </row>
+    <row r="805" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A805" s="7"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="5"/>
+      <c r="D805" s="5"/>
+      <c r="E805" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F805" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G805" s="6"/>
+      <c r="H805" s="6"/>
+    </row>
+    <row r="806" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A806" s="7"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="5"/>
+      <c r="D806" s="5"/>
+      <c r="E806" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F806" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G806" s="6"/>
+      <c r="H806" s="6"/>
+    </row>
+    <row r="807" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A807" s="7"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="5"/>
+      <c r="D807" s="5"/>
+      <c r="E807" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F807" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G807" s="6"/>
+      <c r="H807" s="6"/>
+    </row>
+    <row r="808" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A808" s="7"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="5"/>
+      <c r="D808" s="5"/>
+      <c r="E808" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F808" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G808" s="6"/>
+      <c r="H808" s="6"/>
+    </row>
+    <row r="809" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A809" s="7"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="5"/>
+      <c r="D809" s="5"/>
+      <c r="E809" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F809" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G809" s="6"/>
+      <c r="H809" s="6"/>
+    </row>
+    <row r="810" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A810" s="7"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="5"/>
+      <c r="D810" s="5"/>
+      <c r="E810" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F810" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G810" s="6"/>
+      <c r="H810" s="6"/>
+    </row>
+    <row r="811" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A811" s="7"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="5"/>
+      <c r="D811" s="5"/>
+      <c r="E811" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F811" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G811" s="6"/>
+      <c r="H811" s="6"/>
+    </row>
+    <row r="812" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A812" s="7"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="5"/>
+      <c r="D812" s="5"/>
+      <c r="E812" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F812" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G812" s="6"/>
+      <c r="H812" s="6"/>
+    </row>
+    <row r="813" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A813" s="7"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="5"/>
+      <c r="D813" s="5"/>
+      <c r="E813" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F813" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G813" s="6"/>
+      <c r="H813" s="6"/>
+    </row>
+    <row r="814" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A814" s="7"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="5"/>
+      <c r="D814" s="5"/>
+      <c r="E814" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F814" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G814" s="6"/>
+      <c r="H814" s="6"/>
+    </row>
+    <row r="815" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A815" s="7"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="5"/>
+      <c r="D815" s="5"/>
+      <c r="E815" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F815" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G815" s="6"/>
+      <c r="H815" s="6"/>
+    </row>
+    <row r="816" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A816" s="7"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="5"/>
+      <c r="D816" s="5"/>
+      <c r="E816" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F816" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G816" s="6"/>
+      <c r="H816" s="6"/>
+    </row>
+    <row r="817" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A817" s="7"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="5"/>
+      <c r="D817" s="5"/>
+      <c r="E817" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F817" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G817" s="6"/>
+      <c r="H817" s="6"/>
+    </row>
+    <row r="818" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A818" s="7"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="5"/>
+      <c r="D818" s="5"/>
+      <c r="E818" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F818" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G818" s="6"/>
+      <c r="H818" s="6"/>
+    </row>
+    <row r="819" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A819" s="7"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="5"/>
+      <c r="D819" s="5"/>
+      <c r="E819" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F819" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G819" s="6"/>
+      <c r="H819" s="6"/>
+    </row>
+    <row r="820" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A820" s="7"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="5"/>
+      <c r="D820" s="5"/>
+      <c r="E820" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F820" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G820" s="6"/>
+      <c r="H820" s="6"/>
+    </row>
+    <row r="821" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A821" s="7"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="5"/>
+      <c r="D821" s="5"/>
+      <c r="E821" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F821" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G821" s="6"/>
+      <c r="H821" s="6"/>
+    </row>
+    <row r="822" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A822" s="7"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="5"/>
+      <c r="D822" s="5"/>
+      <c r="E822" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F822" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G822" s="6"/>
+      <c r="H822" s="6"/>
+    </row>
+    <row r="823" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A823" s="7"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="5"/>
+      <c r="D823" s="5"/>
+      <c r="E823" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F823" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G823" s="6"/>
+      <c r="H823" s="6"/>
+    </row>
+    <row r="824" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A824" s="7"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="5"/>
+      <c r="D824" s="5"/>
+      <c r="E824" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F824" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G824" s="6"/>
+      <c r="H824" s="6"/>
+    </row>
+    <row r="825" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A825" s="7"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="5"/>
+      <c r="D825" s="5"/>
+      <c r="E825" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F825" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G825" s="6"/>
+      <c r="H825" s="6"/>
+    </row>
+    <row r="826" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A826" s="7"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="5"/>
+      <c r="D826" s="5"/>
+      <c r="E826" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F826" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G826" s="6"/>
+      <c r="H826" s="6"/>
+    </row>
+    <row r="827" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A827" s="7"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="5"/>
+      <c r="D827" s="5"/>
+      <c r="E827" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F827" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G827" s="6"/>
+      <c r="H827" s="6"/>
+    </row>
+    <row r="828" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A828" s="7"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="5"/>
+      <c r="D828" s="5"/>
+      <c r="E828" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F828" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G828" s="6"/>
+      <c r="H828" s="6"/>
+    </row>
+    <row r="829" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A829" s="7"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="5"/>
+      <c r="D829" s="5"/>
+      <c r="E829" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F829" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G829" s="6"/>
+      <c r="H829" s="6"/>
+    </row>
+    <row r="830" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A830" s="7"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="5"/>
+      <c r="D830" s="5"/>
+      <c r="E830" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F830" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G830" s="6"/>
+      <c r="H830" s="6"/>
+    </row>
+    <row r="831" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A831" s="7"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="5"/>
+      <c r="D831" s="5"/>
+      <c r="E831" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F831" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G831" s="6"/>
+      <c r="H831" s="6"/>
+    </row>
+    <row r="832" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A832" s="7"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="5"/>
+      <c r="D832" s="5"/>
+      <c r="E832" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F832" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G832" s="6"/>
+      <c r="H832" s="6"/>
+    </row>
+    <row r="833" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A833" s="7"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="5"/>
+      <c r="D833" s="5"/>
+      <c r="E833" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F833" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G833" s="6"/>
+      <c r="H833" s="6"/>
+    </row>
+    <row r="834" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A834" s="7"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="5"/>
+      <c r="D834" s="5"/>
+      <c r="E834" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F834" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G834" s="6"/>
+      <c r="H834" s="6"/>
+    </row>
+    <row r="835" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A835" s="7"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="5"/>
+      <c r="D835" s="5"/>
+      <c r="E835" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F835" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G835" s="6"/>
+      <c r="H835" s="6"/>
+    </row>
+    <row r="836" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A836" s="7"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="5"/>
+      <c r="D836" s="5"/>
+      <c r="E836" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F836" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G836" s="6"/>
+      <c r="H836" s="6"/>
+    </row>
+    <row r="837" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A837" s="7"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="5"/>
+      <c r="D837" s="5"/>
+      <c r="E837" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F837" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G837" s="6"/>
+      <c r="H837" s="6"/>
+    </row>
+    <row r="838" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A838" s="7"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="5"/>
+      <c r="D838" s="5"/>
+      <c r="E838" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F838" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G838" s="6"/>
+      <c r="H838" s="6"/>
+    </row>
+    <row r="839" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A839" s="7"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="5"/>
+      <c r="D839" s="5"/>
+      <c r="E839" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F839" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G839" s="6"/>
+      <c r="H839" s="6"/>
+    </row>
+    <row r="840" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A840" s="7"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="5"/>
+      <c r="D840" s="5"/>
+      <c r="E840" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F840" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G840" s="6"/>
+      <c r="H840" s="6"/>
+    </row>
+    <row r="841" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A841" s="7"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="5"/>
+      <c r="D841" s="5"/>
+      <c r="E841" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F841" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G841" s="6"/>
+      <c r="H841" s="6"/>
+    </row>
+    <row r="842" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A842" s="7"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="5"/>
+      <c r="D842" s="5"/>
+      <c r="E842" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F842" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G842" s="6"/>
+      <c r="H842" s="6"/>
+    </row>
+    <row r="843" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A843" s="7"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="5"/>
+      <c r="D843" s="5"/>
+      <c r="E843" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F843" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G843" s="6"/>
+      <c r="H843" s="6"/>
+    </row>
+    <row r="844" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A844" s="7"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="5"/>
+      <c r="D844" s="5"/>
+      <c r="E844" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F844" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G844" s="6"/>
+      <c r="H844" s="6"/>
+    </row>
+    <row r="845" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A845" s="7"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="5"/>
+      <c r="D845" s="5"/>
+      <c r="E845" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F845" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G845" s="6"/>
+      <c r="H845" s="6"/>
+    </row>
+    <row r="846" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A846" s="7"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="5"/>
+      <c r="D846" s="5"/>
+      <c r="E846" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F846" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G846" s="6"/>
+      <c r="H846" s="6"/>
+    </row>
+    <row r="847" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A847" s="7"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="5"/>
+      <c r="D847" s="5"/>
+      <c r="E847" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F847" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G847" s="6"/>
+      <c r="H847" s="6"/>
+    </row>
+    <row r="848" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A848" s="7"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="5"/>
+      <c r="D848" s="5"/>
+      <c r="E848" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F848" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G848" s="6"/>
+      <c r="H848" s="6"/>
+    </row>
+    <row r="849" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A849" s="7"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="5"/>
+      <c r="D849" s="5"/>
+      <c r="E849" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F849" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G849" s="6"/>
+      <c r="H849" s="6"/>
+    </row>
+    <row r="850" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A850" s="7"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="5"/>
+      <c r="D850" s="5"/>
+      <c r="E850" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F850" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G850" s="6"/>
+      <c r="H850" s="6"/>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A851" s="7"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="5"/>
+      <c r="D851" s="5"/>
+      <c r="E851" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F851" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G851" s="6"/>
+      <c r="H851" s="6"/>
+    </row>
+    <row r="852" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A852" s="7"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="5"/>
+      <c r="D852" s="5"/>
+      <c r="E852" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F852" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G852" s="6"/>
+      <c r="H852" s="6"/>
+    </row>
+    <row r="853" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A853" s="7"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="5"/>
+      <c r="D853" s="5"/>
+      <c r="E853" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F853" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G853" s="6"/>
+      <c r="H853" s="6"/>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A854" s="7"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="5"/>
+      <c r="D854" s="5"/>
+      <c r="E854" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F854" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G854" s="6"/>
+      <c r="H854" s="6"/>
+    </row>
+    <row r="855" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A855" s="7"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="5"/>
+      <c r="D855" s="5"/>
+      <c r="E855" s="5">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="F855" s="5" t="str">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="G855" s="6"/>
+      <c r="H855" s="6"/>
+    </row>
+    <row r="856" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A856" s="7"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="5"/>
+      <c r="D856" s="5"/>
+      <c r="E856" s="5">
+        <f t="shared" ref="E856:E919" si="32">MONTH(A856)</f>
+        <v>1</v>
+      </c>
+      <c r="F856" s="5" t="str">
+        <f t="shared" ref="F856:F919" si="33">B856&amp;C856&amp;E856&amp;D856</f>
+        <v>1</v>
+      </c>
+      <c r="G856" s="6"/>
+      <c r="H856" s="6"/>
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A857" s="7"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="5"/>
+      <c r="D857" s="5"/>
+      <c r="E857" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F857" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G857" s="6"/>
+      <c r="H857" s="6"/>
+    </row>
+    <row r="858" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A858" s="7"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="5"/>
+      <c r="D858" s="5"/>
+      <c r="E858" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F858" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G858" s="6"/>
+      <c r="H858" s="6"/>
+    </row>
+    <row r="859" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A859" s="7"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="5"/>
+      <c r="D859" s="5"/>
+      <c r="E859" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F859" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G859" s="6"/>
+      <c r="H859" s="6"/>
+    </row>
+    <row r="860" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A860" s="7"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="5"/>
+      <c r="D860" s="5"/>
+      <c r="E860" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F860" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G860" s="6"/>
+      <c r="H860" s="6"/>
+    </row>
+    <row r="861" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A861" s="7"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="5"/>
+      <c r="D861" s="5"/>
+      <c r="E861" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F861" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G861" s="6"/>
+      <c r="H861" s="6"/>
+    </row>
+    <row r="862" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A862" s="7"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="5"/>
+      <c r="D862" s="5"/>
+      <c r="E862" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F862" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G862" s="6"/>
+      <c r="H862" s="6"/>
+    </row>
+    <row r="863" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A863" s="7"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="5"/>
+      <c r="D863" s="5"/>
+      <c r="E863" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F863" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G863" s="6"/>
+      <c r="H863" s="6"/>
+    </row>
+    <row r="864" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A864" s="7"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="5"/>
+      <c r="D864" s="5"/>
+      <c r="E864" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F864" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G864" s="6"/>
+      <c r="H864" s="6"/>
+    </row>
+    <row r="865" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A865" s="7"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="5"/>
+      <c r="D865" s="5"/>
+      <c r="E865" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F865" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G865" s="6"/>
+      <c r="H865" s="6"/>
+    </row>
+    <row r="866" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A866" s="7"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="5"/>
+      <c r="D866" s="5"/>
+      <c r="E866" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F866" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G866" s="6"/>
+      <c r="H866" s="6"/>
+    </row>
+    <row r="867" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A867" s="7"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="5"/>
+      <c r="D867" s="5"/>
+      <c r="E867" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F867" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G867" s="6"/>
+      <c r="H867" s="6"/>
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A868" s="7"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="5"/>
+      <c r="D868" s="5"/>
+      <c r="E868" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F868" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G868" s="6"/>
+      <c r="H868" s="6"/>
+    </row>
+    <row r="869" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A869" s="7"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="5"/>
+      <c r="D869" s="5"/>
+      <c r="E869" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F869" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G869" s="6"/>
+      <c r="H869" s="6"/>
+    </row>
+    <row r="870" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A870" s="7"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="5"/>
+      <c r="D870" s="5"/>
+      <c r="E870" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F870" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G870" s="6"/>
+      <c r="H870" s="6"/>
+    </row>
+    <row r="871" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A871" s="7"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="5"/>
+      <c r="D871" s="5"/>
+      <c r="E871" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F871" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G871" s="6"/>
+      <c r="H871" s="6"/>
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A872" s="7"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="5"/>
+      <c r="D872" s="5"/>
+      <c r="E872" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F872" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G872" s="6"/>
+      <c r="H872" s="6"/>
+    </row>
+    <row r="873" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A873" s="7"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="5"/>
+      <c r="D873" s="5"/>
+      <c r="E873" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F873" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G873" s="6"/>
+      <c r="H873" s="6"/>
+    </row>
+    <row r="874" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A874" s="7"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="5"/>
+      <c r="D874" s="5"/>
+      <c r="E874" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F874" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G874" s="6"/>
+      <c r="H874" s="6"/>
+    </row>
+    <row r="875" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A875" s="7"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="5"/>
+      <c r="D875" s="5"/>
+      <c r="E875" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F875" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G875" s="6"/>
+      <c r="H875" s="6"/>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A876" s="7"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="5"/>
+      <c r="D876" s="5"/>
+      <c r="E876" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F876" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G876" s="6"/>
+      <c r="H876" s="6"/>
+    </row>
+    <row r="877" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A877" s="7"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="5"/>
+      <c r="D877" s="5"/>
+      <c r="E877" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F877" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G877" s="6"/>
+      <c r="H877" s="6"/>
+    </row>
+    <row r="878" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A878" s="7"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="5"/>
+      <c r="D878" s="5"/>
+      <c r="E878" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F878" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G878" s="6"/>
+      <c r="H878" s="6"/>
+    </row>
+    <row r="879" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A879" s="7"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="5"/>
+      <c r="D879" s="5"/>
+      <c r="E879" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F879" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G879" s="6"/>
+      <c r="H879" s="6"/>
+    </row>
+    <row r="880" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A880" s="7"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="5"/>
+      <c r="D880" s="5"/>
+      <c r="E880" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F880" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G880" s="6"/>
+      <c r="H880" s="6"/>
+    </row>
+    <row r="881" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A881" s="7"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="5"/>
+      <c r="D881" s="5"/>
+      <c r="E881" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F881" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G881" s="6"/>
+      <c r="H881" s="6"/>
+    </row>
+    <row r="882" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A882" s="7"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="5"/>
+      <c r="D882" s="5"/>
+      <c r="E882" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F882" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G882" s="6"/>
+      <c r="H882" s="6"/>
+    </row>
+    <row r="883" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A883" s="7"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="5"/>
+      <c r="D883" s="5"/>
+      <c r="E883" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F883" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G883" s="6"/>
+      <c r="H883" s="6"/>
+    </row>
+    <row r="884" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A884" s="7"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="5"/>
+      <c r="D884" s="5"/>
+      <c r="E884" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F884" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G884" s="6"/>
+      <c r="H884" s="6"/>
+    </row>
+    <row r="885" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A885" s="7"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="5"/>
+      <c r="D885" s="5"/>
+      <c r="E885" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F885" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G885" s="6"/>
+      <c r="H885" s="6"/>
+    </row>
+    <row r="886" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A886" s="7"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="5"/>
+      <c r="D886" s="5"/>
+      <c r="E886" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F886" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G886" s="6"/>
+      <c r="H886" s="6"/>
+    </row>
+    <row r="887" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A887" s="7"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="5"/>
+      <c r="D887" s="5"/>
+      <c r="E887" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F887" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G887" s="6"/>
+      <c r="H887" s="6"/>
+    </row>
+    <row r="888" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A888" s="7"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="5"/>
+      <c r="D888" s="5"/>
+      <c r="E888" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F888" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G888" s="6"/>
+      <c r="H888" s="6"/>
+    </row>
+    <row r="889" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A889" s="7"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="5"/>
+      <c r="D889" s="5"/>
+      <c r="E889" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F889" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G889" s="6"/>
+      <c r="H889" s="6"/>
+    </row>
+    <row r="890" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A890" s="7"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="5"/>
+      <c r="D890" s="5"/>
+      <c r="E890" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F890" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G890" s="6"/>
+      <c r="H890" s="6"/>
+    </row>
+    <row r="891" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A891" s="7"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="5"/>
+      <c r="D891" s="5"/>
+      <c r="E891" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F891" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G891" s="6"/>
+      <c r="H891" s="6"/>
+    </row>
+    <row r="892" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A892" s="7"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="5"/>
+      <c r="D892" s="5"/>
+      <c r="E892" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F892" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G892" s="6"/>
+      <c r="H892" s="6"/>
+    </row>
+    <row r="893" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A893" s="7"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="5"/>
+      <c r="D893" s="5"/>
+      <c r="E893" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F893" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G893" s="6"/>
+      <c r="H893" s="6"/>
+    </row>
+    <row r="894" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A894" s="7"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="5"/>
+      <c r="D894" s="5"/>
+      <c r="E894" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F894" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G894" s="6"/>
+      <c r="H894" s="6"/>
+    </row>
+    <row r="895" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A895" s="7"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="5"/>
+      <c r="D895" s="5"/>
+      <c r="E895" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F895" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G895" s="6"/>
+      <c r="H895" s="6"/>
+    </row>
+    <row r="896" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A896" s="7"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="5"/>
+      <c r="D896" s="5"/>
+      <c r="E896" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F896" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G896" s="6"/>
+      <c r="H896" s="6"/>
+    </row>
+    <row r="897" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A897" s="7"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="5"/>
+      <c r="D897" s="5"/>
+      <c r="E897" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F897" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G897" s="6"/>
+      <c r="H897" s="6"/>
+    </row>
+    <row r="898" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A898" s="7"/>
+      <c r="B898" s="5"/>
+      <c r="C898" s="5"/>
+      <c r="D898" s="5"/>
+      <c r="E898" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F898" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G898" s="6"/>
+      <c r="H898" s="6"/>
+    </row>
+    <row r="899" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A899" s="7"/>
+      <c r="B899" s="5"/>
+      <c r="C899" s="5"/>
+      <c r="D899" s="5"/>
+      <c r="E899" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F899" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G899" s="6"/>
+      <c r="H899" s="6"/>
+    </row>
+    <row r="900" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A900" s="7"/>
+      <c r="B900" s="5"/>
+      <c r="C900" s="5"/>
+      <c r="D900" s="5"/>
+      <c r="E900" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F900" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G900" s="6"/>
+      <c r="H900" s="6"/>
+    </row>
+    <row r="901" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A901" s="7"/>
+      <c r="B901" s="5"/>
+      <c r="C901" s="5"/>
+      <c r="D901" s="5"/>
+      <c r="E901" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F901" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G901" s="6"/>
+      <c r="H901" s="6"/>
+    </row>
+    <row r="902" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A902" s="7"/>
+      <c r="B902" s="5"/>
+      <c r="C902" s="5"/>
+      <c r="D902" s="5"/>
+      <c r="E902" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F902" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G902" s="6"/>
+      <c r="H902" s="6"/>
+    </row>
+    <row r="903" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A903" s="7"/>
+      <c r="B903" s="5"/>
+      <c r="C903" s="5"/>
+      <c r="D903" s="5"/>
+      <c r="E903" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F903" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G903" s="6"/>
+      <c r="H903" s="6"/>
+    </row>
+    <row r="904" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A904" s="7"/>
+      <c r="B904" s="5"/>
+      <c r="C904" s="5"/>
+      <c r="D904" s="5"/>
+      <c r="E904" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F904" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G904" s="6"/>
+      <c r="H904" s="6"/>
+    </row>
+    <row r="905" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A905" s="7"/>
+      <c r="B905" s="5"/>
+      <c r="C905" s="5"/>
+      <c r="D905" s="5"/>
+      <c r="E905" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F905" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G905" s="6"/>
+      <c r="H905" s="6"/>
+    </row>
+    <row r="906" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A906" s="7"/>
+      <c r="B906" s="5"/>
+      <c r="C906" s="5"/>
+      <c r="D906" s="5"/>
+      <c r="E906" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F906" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G906" s="6"/>
+      <c r="H906" s="6"/>
+    </row>
+    <row r="907" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A907" s="7"/>
+      <c r="B907" s="5"/>
+      <c r="C907" s="5"/>
+      <c r="D907" s="5"/>
+      <c r="E907" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F907" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G907" s="6"/>
+      <c r="H907" s="6"/>
+    </row>
+    <row r="908" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A908" s="7"/>
+      <c r="B908" s="5"/>
+      <c r="C908" s="5"/>
+      <c r="D908" s="5"/>
+      <c r="E908" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F908" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G908" s="6"/>
+      <c r="H908" s="6"/>
+    </row>
+    <row r="909" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A909" s="7"/>
+      <c r="B909" s="5"/>
+      <c r="C909" s="5"/>
+      <c r="D909" s="5"/>
+      <c r="E909" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F909" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G909" s="6"/>
+      <c r="H909" s="6"/>
+    </row>
+    <row r="910" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A910" s="7"/>
+      <c r="B910" s="5"/>
+      <c r="C910" s="5"/>
+      <c r="D910" s="5"/>
+      <c r="E910" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F910" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G910" s="6"/>
+      <c r="H910" s="6"/>
+    </row>
+    <row r="911" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A911" s="7"/>
+      <c r="B911" s="5"/>
+      <c r="C911" s="5"/>
+      <c r="D911" s="5"/>
+      <c r="E911" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F911" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G911" s="6"/>
+      <c r="H911" s="6"/>
+    </row>
+    <row r="912" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A912" s="7"/>
+      <c r="B912" s="5"/>
+      <c r="C912" s="5"/>
+      <c r="D912" s="5"/>
+      <c r="E912" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F912" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G912" s="6"/>
+      <c r="H912" s="6"/>
+    </row>
+    <row r="913" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A913" s="7"/>
+      <c r="B913" s="5"/>
+      <c r="C913" s="5"/>
+      <c r="D913" s="5"/>
+      <c r="E913" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F913" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G913" s="6"/>
+      <c r="H913" s="6"/>
+    </row>
+    <row r="914" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A914" s="7"/>
+      <c r="B914" s="5"/>
+      <c r="C914" s="5"/>
+      <c r="D914" s="5"/>
+      <c r="E914" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F914" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G914" s="6"/>
+      <c r="H914" s="6"/>
+    </row>
+    <row r="915" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A915" s="7"/>
+      <c r="B915" s="5"/>
+      <c r="C915" s="5"/>
+      <c r="D915" s="5"/>
+      <c r="E915" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F915" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G915" s="6"/>
+      <c r="H915" s="6"/>
+    </row>
+    <row r="916" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A916" s="7"/>
+      <c r="B916" s="5"/>
+      <c r="C916" s="5"/>
+      <c r="D916" s="5"/>
+      <c r="E916" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F916" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G916" s="6"/>
+      <c r="H916" s="6"/>
+    </row>
+    <row r="917" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A917" s="7"/>
+      <c r="B917" s="5"/>
+      <c r="C917" s="5"/>
+      <c r="D917" s="5"/>
+      <c r="E917" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F917" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G917" s="6"/>
+      <c r="H917" s="6"/>
+    </row>
+    <row r="918" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A918" s="7"/>
+      <c r="B918" s="5"/>
+      <c r="C918" s="5"/>
+      <c r="D918" s="5"/>
+      <c r="E918" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F918" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G918" s="6"/>
+      <c r="H918" s="6"/>
+    </row>
+    <row r="919" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A919" s="7"/>
+      <c r="B919" s="5"/>
+      <c r="C919" s="5"/>
+      <c r="D919" s="5"/>
+      <c r="E919" s="5">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="F919" s="5" t="str">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+      <c r="G919" s="6"/>
+      <c r="H919" s="6"/>
+    </row>
+    <row r="920" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A920" s="7"/>
+      <c r="B920" s="5"/>
+      <c r="C920" s="5"/>
+      <c r="D920" s="5"/>
+      <c r="E920" s="5">
+        <f t="shared" ref="E920:E940" si="34">MONTH(A920)</f>
+        <v>1</v>
+      </c>
+      <c r="F920" s="5" t="str">
+        <f t="shared" ref="F920:F940" si="35">B920&amp;C920&amp;E920&amp;D920</f>
+        <v>1</v>
+      </c>
+      <c r="G920" s="6"/>
+      <c r="H920" s="6"/>
+    </row>
+    <row r="921" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A921" s="7"/>
+      <c r="B921" s="5"/>
+      <c r="C921" s="5"/>
+      <c r="D921" s="5"/>
+      <c r="E921" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F921" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G921" s="6"/>
+      <c r="H921" s="6"/>
+    </row>
+    <row r="922" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A922" s="7"/>
+      <c r="B922" s="5"/>
+      <c r="C922" s="5"/>
+      <c r="D922" s="5"/>
+      <c r="E922" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F922" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G922" s="6"/>
+      <c r="H922" s="6"/>
+    </row>
+    <row r="923" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A923" s="7"/>
+      <c r="B923" s="5"/>
+      <c r="C923" s="5"/>
+      <c r="D923" s="5"/>
+      <c r="E923" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F923" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G923" s="6"/>
+      <c r="H923" s="6"/>
+    </row>
+    <row r="924" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A924" s="7"/>
+      <c r="B924" s="5"/>
+      <c r="C924" s="5"/>
+      <c r="D924" s="5"/>
+      <c r="E924" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F924" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G924" s="6"/>
+      <c r="H924" s="6"/>
+    </row>
+    <row r="925" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A925" s="7"/>
+      <c r="B925" s="5"/>
+      <c r="C925" s="5"/>
+      <c r="D925" s="5"/>
+      <c r="E925" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F925" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G925" s="6"/>
+      <c r="H925" s="6"/>
+    </row>
+    <row r="926" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A926" s="7"/>
+      <c r="B926" s="5"/>
+      <c r="C926" s="5"/>
+      <c r="D926" s="5"/>
+      <c r="E926" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F926" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G926" s="6"/>
+      <c r="H926" s="6"/>
+    </row>
+    <row r="927" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A927" s="7"/>
+      <c r="B927" s="5"/>
+      <c r="C927" s="5"/>
+      <c r="D927" s="5"/>
+      <c r="E927" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F927" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G927" s="6"/>
+      <c r="H927" s="6"/>
+    </row>
+    <row r="928" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A928" s="7"/>
+      <c r="B928" s="5"/>
+      <c r="C928" s="5"/>
+      <c r="D928" s="5"/>
+      <c r="E928" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F928" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G928" s="6"/>
+      <c r="H928" s="6"/>
+    </row>
+    <row r="929" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A929" s="7"/>
+      <c r="B929" s="5"/>
+      <c r="C929" s="5"/>
+      <c r="D929" s="5"/>
+      <c r="E929" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F929" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G929" s="6"/>
+      <c r="H929" s="6"/>
+    </row>
+    <row r="930" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A930" s="7"/>
+      <c r="B930" s="5"/>
+      <c r="C930" s="5"/>
+      <c r="D930" s="5"/>
+      <c r="E930" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F930" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G930" s="6"/>
+      <c r="H930" s="6"/>
+    </row>
+    <row r="931" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A931" s="7"/>
+      <c r="B931" s="5"/>
+      <c r="C931" s="5"/>
+      <c r="D931" s="5"/>
+      <c r="E931" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F931" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G931" s="6"/>
+      <c r="H931" s="6"/>
+    </row>
+    <row r="932" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A932" s="7"/>
+      <c r="B932" s="5"/>
+      <c r="C932" s="5"/>
+      <c r="D932" s="5"/>
+      <c r="E932" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F932" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G932" s="6"/>
+      <c r="H932" s="6"/>
+    </row>
+    <row r="933" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A933" s="7"/>
+      <c r="B933" s="5"/>
+      <c r="C933" s="5"/>
+      <c r="D933" s="5"/>
+      <c r="E933" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F933" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G933" s="6"/>
+      <c r="H933" s="6"/>
+    </row>
+    <row r="934" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A934" s="7"/>
+      <c r="B934" s="5"/>
+      <c r="C934" s="5"/>
+      <c r="D934" s="5"/>
+      <c r="E934" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F934" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G934" s="6"/>
+      <c r="H934" s="6"/>
+    </row>
+    <row r="935" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A935" s="7"/>
+      <c r="B935" s="5"/>
+      <c r="C935" s="5"/>
+      <c r="D935" s="5"/>
+      <c r="E935" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F935" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G935" s="6"/>
+      <c r="H935" s="6"/>
+    </row>
+    <row r="936" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A936" s="7"/>
+      <c r="B936" s="5"/>
+      <c r="C936" s="5"/>
+      <c r="D936" s="5"/>
+      <c r="E936" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F936" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G936" s="6"/>
+      <c r="H936" s="6"/>
+    </row>
+    <row r="937" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A937" s="7"/>
+      <c r="B937" s="5"/>
+      <c r="C937" s="5"/>
+      <c r="D937" s="5"/>
+      <c r="E937" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F937" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G937" s="6"/>
+      <c r="H937" s="6"/>
+    </row>
+    <row r="938" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A938" s="7"/>
+      <c r="B938" s="5"/>
+      <c r="C938" s="5"/>
+      <c r="D938" s="5"/>
+      <c r="E938" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F938" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G938" s="6"/>
+      <c r="H938" s="6"/>
+    </row>
+    <row r="939" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A939" s="7"/>
+      <c r="B939" s="5"/>
+      <c r="C939" s="5"/>
+      <c r="D939" s="5"/>
+      <c r="E939" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F939" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G939" s="6"/>
+      <c r="H939" s="6"/>
+    </row>
+    <row r="940" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A940" s="7"/>
+      <c r="B940" s="5"/>
+      <c r="C940" s="5"/>
+      <c r="D940" s="5"/>
+      <c r="E940" s="5">
+        <f t="shared" si="34"/>
+        <v>1</v>
+      </c>
+      <c r="F940" s="5" t="str">
+        <f t="shared" si="35"/>
+        <v>1</v>
+      </c>
+      <c r="G940" s="6"/>
+      <c r="H940" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H658" xr:uid="{CD0DB41C-1229-4A2D-AB76-57C35A8F00D8}"/>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B729:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B941:B1048576" xr:uid="{2E3ACDB5-6551-4396-A88E-14FEB151CED4}">
       <formula1>$J$2:$J$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C729:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C941:C1048576" xr:uid="{910F4386-FD7F-4F32-AAFF-0B1298D3FBEC}">
       <formula1>$K$2:$K$34</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B728" xr:uid="{627737C7-25C1-4946-ABD5-35D1B8BC1154}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B940" xr:uid="{627737C7-25C1-4946-ABD5-35D1B8BC1154}">
       <formula1>$K$3:$K$20</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D728" xr:uid="{40D57034-284D-439B-B2DB-D030492C316A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D940" xr:uid="{40D57034-284D-439B-B2DB-D030492C316A}">
       <formula1>$M$3:$M$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C728" xr:uid="{EB02450E-E413-4923-89C3-262676E8D39D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C940" xr:uid="{EB02450E-E413-4923-89C3-262676E8D39D}">
       <formula1>$L$3:$L$36</formula1>
     </dataValidation>
   </dataValidations>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20E960F7-461E-4810-BF01-CE1CCC61A19A}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07F1DA33-48D1-4C83-ABF3-F6D068A9556C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2474" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="303">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1940,20 +1940,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>娯楽費</t>
-    <rPh sb="0" eb="3">
-      <t>ゴラクヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>その他</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プリキュア映画チケ</t>
     <rPh sb="5" eb="7">
       <t>エイガ</t>
@@ -1961,31 +1947,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>服</t>
-    <rPh sb="0" eb="1">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>子供</t>
-    <rPh sb="0" eb="2">
-      <t>コドモ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>医療費</t>
-    <rPh sb="0" eb="3">
-      <t>イリョウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>みなくん耳鼻科</t>
     <rPh sb="4" eb="7">
       <t>ジビカ</t>
@@ -1993,24 +1954,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生活費</t>
-    <rPh sb="0" eb="3">
-      <t>セイカツヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ココス</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>肌着</t>
-    <rPh sb="0" eb="2">
-      <t>ハダギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>アイシャドウ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2023,24 +1970,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>光熱費</t>
-    <rPh sb="0" eb="3">
-      <t>コウネツヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>電気</t>
-    <rPh sb="0" eb="2">
-      <t>デンキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>実績</t>
-    <rPh sb="0" eb="2">
-      <t>ジッセキ</t>
-    </rPh>
+    <t>しーちゃん</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -18339,7 +18269,7 @@
         <v>4</v>
       </c>
       <c r="F585" s="5" t="str">
-        <f t="shared" ref="F585:F723" si="19">B585&amp;C585&amp;E585&amp;D585</f>
+        <f t="shared" ref="F585:F728" si="19">B585&amp;C585&amp;E585&amp;D585</f>
         <v>服りょう4実績</v>
       </c>
       <c r="G585" s="6">
@@ -20258,7 +20188,7 @@
         <v>19</v>
       </c>
       <c r="E656" s="5">
-        <f t="shared" ref="E656:E723" si="23">MONTH(A656)</f>
+        <f t="shared" ref="E656:E728" si="23">MONTH(A656)</f>
         <v>5</v>
       </c>
       <c r="F656" s="5" t="str">
@@ -21851,10 +21781,10 @@
         <v>46204</v>
       </c>
       <c r="B714" s="5" t="s">
-        <v>296</v>
+        <v>90</v>
       </c>
       <c r="C714" s="5" t="s">
-        <v>297</v>
+        <v>11</v>
       </c>
       <c r="D714" s="5" t="s">
         <v>19</v>
@@ -21871,7 +21801,7 @@
         <v>2500</v>
       </c>
       <c r="H714" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="715" spans="1:8" x14ac:dyDescent="0.35">
@@ -21879,10 +21809,10 @@
         <v>46206</v>
       </c>
       <c r="B715" s="5" t="s">
-        <v>299</v>
+        <v>1</v>
       </c>
       <c r="C715" s="5" t="s">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="D715" s="5" t="s">
         <v>19</v>
@@ -21905,10 +21835,10 @@
         <v>46207</v>
       </c>
       <c r="B716" s="5" t="s">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="C716" s="5" t="s">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="D716" s="5" t="s">
         <v>19</v>
@@ -21925,7 +21855,7 @@
         <v>200</v>
       </c>
       <c r="H716" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="717" spans="1:8" x14ac:dyDescent="0.35">
@@ -21933,7 +21863,7 @@
         <v>46207</v>
       </c>
       <c r="B717" s="5" t="s">
-        <v>304</v>
+        <v>3</v>
       </c>
       <c r="C717" s="5" t="s">
         <v>9</v>
@@ -21953,7 +21883,7 @@
         <v>6017</v>
       </c>
       <c r="H717" s="6" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.35">
@@ -21961,10 +21891,10 @@
         <v>46207</v>
       </c>
       <c r="B718" s="5" t="s">
-        <v>299</v>
+        <v>1</v>
       </c>
       <c r="C718" s="5" t="s">
-        <v>300</v>
+        <v>73</v>
       </c>
       <c r="D718" s="5" t="s">
         <v>19</v>
@@ -21981,7 +21911,7 @@
         <v>966</v>
       </c>
       <c r="H718" s="6" t="s">
-        <v>306</v>
+        <v>118</v>
       </c>
     </row>
     <row r="719" spans="1:8" x14ac:dyDescent="0.35">
@@ -22009,7 +21939,7 @@
         <v>7700</v>
       </c>
       <c r="H719" s="6" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="720" spans="1:8" x14ac:dyDescent="0.35">
@@ -22037,7 +21967,7 @@
         <v>7700</v>
       </c>
       <c r="H720" s="6" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.35">
@@ -22065,7 +21995,7 @@
         <v>1870</v>
       </c>
       <c r="H721" s="6" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.35">
@@ -22100,13 +22030,13 @@
         <v>46208</v>
       </c>
       <c r="B723" s="5" t="s">
-        <v>310</v>
+        <v>7</v>
       </c>
       <c r="C723" s="5" t="s">
-        <v>311</v>
+        <v>40</v>
       </c>
       <c r="D723" s="5" t="s">
-        <v>312</v>
+        <v>19</v>
       </c>
       <c r="E723" s="5">
         <f t="shared" si="23"/>
@@ -22122,84 +22052,143 @@
       <c r="H723" s="6"/>
     </row>
     <row r="724" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A724" s="7"/>
-      <c r="B724" s="5"/>
-      <c r="C724" s="5"/>
-      <c r="D724" s="5"/>
+      <c r="A724" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B724" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C724" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D724" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E724" s="5">
-        <f t="shared" ref="E656:E728" si="26">MONTH(A724)</f>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F724" s="5" t="str">
-        <f t="shared" ref="F585:F728" si="27">B724&amp;C724&amp;E724&amp;D724</f>
-        <v>1</v>
-      </c>
-      <c r="G724" s="6"/>
-      <c r="H724" s="6"/>
+        <f t="shared" si="19"/>
+        <v>医療費-7実績</v>
+      </c>
+      <c r="G724" s="6">
+        <v>4240</v>
+      </c>
+      <c r="H724" s="6" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="725" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A725" s="7"/>
-      <c r="B725" s="5"/>
-      <c r="C725" s="5"/>
-      <c r="D725" s="5"/>
+      <c r="A725" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B725" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D725" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E725" s="5">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F725" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G725" s="6"/>
-      <c r="H725" s="6"/>
+        <f t="shared" si="19"/>
+        <v>医療費-7実績</v>
+      </c>
+      <c r="G725" s="6">
+        <v>200</v>
+      </c>
+      <c r="H725" s="6" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A726" s="7"/>
-      <c r="B726" s="5"/>
-      <c r="C726" s="5"/>
-      <c r="D726" s="5"/>
+      <c r="A726" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B726" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D726" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E726" s="5">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F726" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G726" s="6"/>
+        <f t="shared" si="19"/>
+        <v>美容室ゆっこ7実績</v>
+      </c>
+      <c r="G726" s="6">
+        <v>20130</v>
+      </c>
       <c r="H726" s="6"/>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A727" s="7"/>
-      <c r="B727" s="5"/>
-      <c r="C727" s="5"/>
-      <c r="D727" s="5"/>
+      <c r="A727" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B727" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D727" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E727" s="5">
-        <f t="shared" si="26"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F727" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G727" s="6"/>
-      <c r="H727" s="6"/>
+        <f t="shared" si="19"/>
+        <v>服ゆっこ7実績</v>
+      </c>
+      <c r="G727" s="6">
+        <f>1089*2</f>
+        <v>2178</v>
+      </c>
+      <c r="H727" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A728" s="7"/>
-      <c r="B728" s="5"/>
-      <c r="C728" s="5"/>
-      <c r="D728" s="5"/>
+      <c r="A728" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B728" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D728" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E728" s="5">
-        <f t="shared" ref="E728:E791" si="28">MONTH(A728)</f>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F728" s="5" t="str">
-        <f t="shared" ref="F728:F791" si="29">B728&amp;C728&amp;E728&amp;D728</f>
-        <v>1</v>
-      </c>
-      <c r="G728" s="6"/>
-      <c r="H728" s="6"/>
+        <f t="shared" si="19"/>
+        <v>服子供7実績</v>
+      </c>
+      <c r="G728" s="6">
+        <v>2068</v>
+      </c>
+      <c r="H728" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A729" s="7"/>
@@ -22207,11 +22196,11 @@
       <c r="C729" s="5"/>
       <c r="D729" s="5"/>
       <c r="E729" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E728:E791" si="26">MONTH(A729)</f>
         <v>1</v>
       </c>
       <c r="F729" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="F728:F791" si="27">B729&amp;C729&amp;E729&amp;D729</f>
         <v>1</v>
       </c>
       <c r="G729" s="6"/>
@@ -22223,11 +22212,11 @@
       <c r="C730" s="5"/>
       <c r="D730" s="5"/>
       <c r="E730" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F730" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G730" s="6"/>
@@ -22239,11 +22228,11 @@
       <c r="C731" s="5"/>
       <c r="D731" s="5"/>
       <c r="E731" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F731" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G731" s="6"/>
@@ -22255,11 +22244,11 @@
       <c r="C732" s="5"/>
       <c r="D732" s="5"/>
       <c r="E732" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F732" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G732" s="6"/>
@@ -22271,11 +22260,11 @@
       <c r="C733" s="5"/>
       <c r="D733" s="5"/>
       <c r="E733" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F733" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G733" s="6"/>
@@ -22287,11 +22276,11 @@
       <c r="C734" s="5"/>
       <c r="D734" s="5"/>
       <c r="E734" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F734" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G734" s="6"/>
@@ -22303,11 +22292,11 @@
       <c r="C735" s="5"/>
       <c r="D735" s="5"/>
       <c r="E735" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F735" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G735" s="6"/>
@@ -22319,11 +22308,11 @@
       <c r="C736" s="5"/>
       <c r="D736" s="5"/>
       <c r="E736" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F736" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G736" s="6"/>
@@ -22335,11 +22324,11 @@
       <c r="C737" s="5"/>
       <c r="D737" s="5"/>
       <c r="E737" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F737" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G737" s="6"/>
@@ -22351,11 +22340,11 @@
       <c r="C738" s="5"/>
       <c r="D738" s="5"/>
       <c r="E738" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F738" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G738" s="6"/>
@@ -22367,11 +22356,11 @@
       <c r="C739" s="5"/>
       <c r="D739" s="5"/>
       <c r="E739" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F739" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G739" s="6"/>
@@ -22383,11 +22372,11 @@
       <c r="C740" s="5"/>
       <c r="D740" s="5"/>
       <c r="E740" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F740" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G740" s="6"/>
@@ -22399,11 +22388,11 @@
       <c r="C741" s="5"/>
       <c r="D741" s="5"/>
       <c r="E741" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F741" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G741" s="6"/>
@@ -22415,11 +22404,11 @@
       <c r="C742" s="5"/>
       <c r="D742" s="5"/>
       <c r="E742" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F742" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G742" s="6"/>
@@ -22431,11 +22420,11 @@
       <c r="C743" s="5"/>
       <c r="D743" s="5"/>
       <c r="E743" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F743" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G743" s="6"/>
@@ -22447,11 +22436,11 @@
       <c r="C744" s="5"/>
       <c r="D744" s="5"/>
       <c r="E744" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F744" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G744" s="6"/>
@@ -22463,11 +22452,11 @@
       <c r="C745" s="5"/>
       <c r="D745" s="5"/>
       <c r="E745" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F745" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G745" s="6"/>
@@ -22479,11 +22468,11 @@
       <c r="C746" s="5"/>
       <c r="D746" s="5"/>
       <c r="E746" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F746" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G746" s="6"/>
@@ -22495,11 +22484,11 @@
       <c r="C747" s="5"/>
       <c r="D747" s="5"/>
       <c r="E747" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F747" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G747" s="6"/>
@@ -22511,11 +22500,11 @@
       <c r="C748" s="5"/>
       <c r="D748" s="5"/>
       <c r="E748" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F748" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G748" s="6"/>
@@ -22527,11 +22516,11 @@
       <c r="C749" s="5"/>
       <c r="D749" s="5"/>
       <c r="E749" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F749" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G749" s="6"/>
@@ -22543,11 +22532,11 @@
       <c r="C750" s="5"/>
       <c r="D750" s="5"/>
       <c r="E750" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F750" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G750" s="6"/>
@@ -22559,11 +22548,11 @@
       <c r="C751" s="5"/>
       <c r="D751" s="5"/>
       <c r="E751" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F751" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G751" s="6"/>
@@ -22575,11 +22564,11 @@
       <c r="C752" s="5"/>
       <c r="D752" s="5"/>
       <c r="E752" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F752" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G752" s="6"/>
@@ -22591,11 +22580,11 @@
       <c r="C753" s="5"/>
       <c r="D753" s="5"/>
       <c r="E753" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F753" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G753" s="6"/>
@@ -22607,11 +22596,11 @@
       <c r="C754" s="5"/>
       <c r="D754" s="5"/>
       <c r="E754" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F754" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G754" s="6"/>
@@ -22623,11 +22612,11 @@
       <c r="C755" s="5"/>
       <c r="D755" s="5"/>
       <c r="E755" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F755" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G755" s="6"/>
@@ -22639,11 +22628,11 @@
       <c r="C756" s="5"/>
       <c r="D756" s="5"/>
       <c r="E756" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F756" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G756" s="6"/>
@@ -22655,11 +22644,11 @@
       <c r="C757" s="5"/>
       <c r="D757" s="5"/>
       <c r="E757" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F757" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G757" s="6"/>
@@ -22671,11 +22660,11 @@
       <c r="C758" s="5"/>
       <c r="D758" s="5"/>
       <c r="E758" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F758" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G758" s="6"/>
@@ -22687,11 +22676,11 @@
       <c r="C759" s="5"/>
       <c r="D759" s="5"/>
       <c r="E759" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F759" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G759" s="6"/>
@@ -22703,11 +22692,11 @@
       <c r="C760" s="5"/>
       <c r="D760" s="5"/>
       <c r="E760" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F760" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G760" s="6"/>
@@ -22719,11 +22708,11 @@
       <c r="C761" s="5"/>
       <c r="D761" s="5"/>
       <c r="E761" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F761" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G761" s="6"/>
@@ -22735,11 +22724,11 @@
       <c r="C762" s="5"/>
       <c r="D762" s="5"/>
       <c r="E762" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F762" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G762" s="6"/>
@@ -22751,11 +22740,11 @@
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F763" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G763" s="6"/>
@@ -22767,11 +22756,11 @@
       <c r="C764" s="5"/>
       <c r="D764" s="5"/>
       <c r="E764" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F764" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G764" s="6"/>
@@ -22783,11 +22772,11 @@
       <c r="C765" s="5"/>
       <c r="D765" s="5"/>
       <c r="E765" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F765" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G765" s="6"/>
@@ -22799,11 +22788,11 @@
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F766" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G766" s="6"/>
@@ -22815,11 +22804,11 @@
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F767" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G767" s="6"/>
@@ -22831,11 +22820,11 @@
       <c r="C768" s="5"/>
       <c r="D768" s="5"/>
       <c r="E768" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F768" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G768" s="6"/>
@@ -22847,11 +22836,11 @@
       <c r="C769" s="5"/>
       <c r="D769" s="5"/>
       <c r="E769" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F769" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G769" s="6"/>
@@ -22863,11 +22852,11 @@
       <c r="C770" s="5"/>
       <c r="D770" s="5"/>
       <c r="E770" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F770" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G770" s="6"/>
@@ -22879,11 +22868,11 @@
       <c r="C771" s="5"/>
       <c r="D771" s="5"/>
       <c r="E771" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F771" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G771" s="6"/>
@@ -22895,11 +22884,11 @@
       <c r="C772" s="5"/>
       <c r="D772" s="5"/>
       <c r="E772" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F772" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G772" s="6"/>
@@ -22911,11 +22900,11 @@
       <c r="C773" s="5"/>
       <c r="D773" s="5"/>
       <c r="E773" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F773" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G773" s="6"/>
@@ -22927,11 +22916,11 @@
       <c r="C774" s="5"/>
       <c r="D774" s="5"/>
       <c r="E774" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F774" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G774" s="6"/>
@@ -22943,11 +22932,11 @@
       <c r="C775" s="5"/>
       <c r="D775" s="5"/>
       <c r="E775" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F775" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G775" s="6"/>
@@ -22959,11 +22948,11 @@
       <c r="C776" s="5"/>
       <c r="D776" s="5"/>
       <c r="E776" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F776" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G776" s="6"/>
@@ -22975,11 +22964,11 @@
       <c r="C777" s="5"/>
       <c r="D777" s="5"/>
       <c r="E777" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F777" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G777" s="6"/>
@@ -22991,11 +22980,11 @@
       <c r="C778" s="5"/>
       <c r="D778" s="5"/>
       <c r="E778" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F778" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G778" s="6"/>
@@ -23007,11 +22996,11 @@
       <c r="C779" s="5"/>
       <c r="D779" s="5"/>
       <c r="E779" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F779" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G779" s="6"/>
@@ -23023,11 +23012,11 @@
       <c r="C780" s="5"/>
       <c r="D780" s="5"/>
       <c r="E780" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F780" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G780" s="6"/>
@@ -23039,11 +23028,11 @@
       <c r="C781" s="5"/>
       <c r="D781" s="5"/>
       <c r="E781" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F781" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G781" s="6"/>
@@ -23055,11 +23044,11 @@
       <c r="C782" s="5"/>
       <c r="D782" s="5"/>
       <c r="E782" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F782" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G782" s="6"/>
@@ -23071,11 +23060,11 @@
       <c r="C783" s="5"/>
       <c r="D783" s="5"/>
       <c r="E783" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F783" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G783" s="6"/>
@@ -23087,11 +23076,11 @@
       <c r="C784" s="5"/>
       <c r="D784" s="5"/>
       <c r="E784" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F784" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G784" s="6"/>
@@ -23103,11 +23092,11 @@
       <c r="C785" s="5"/>
       <c r="D785" s="5"/>
       <c r="E785" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F785" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G785" s="6"/>
@@ -23119,11 +23108,11 @@
       <c r="C786" s="5"/>
       <c r="D786" s="5"/>
       <c r="E786" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F786" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G786" s="6"/>
@@ -23135,11 +23124,11 @@
       <c r="C787" s="5"/>
       <c r="D787" s="5"/>
       <c r="E787" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F787" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G787" s="6"/>
@@ -23151,11 +23140,11 @@
       <c r="C788" s="5"/>
       <c r="D788" s="5"/>
       <c r="E788" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F788" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G788" s="6"/>
@@ -23167,11 +23156,11 @@
       <c r="C789" s="5"/>
       <c r="D789" s="5"/>
       <c r="E789" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F789" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G789" s="6"/>
@@ -23183,11 +23172,11 @@
       <c r="C790" s="5"/>
       <c r="D790" s="5"/>
       <c r="E790" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F790" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G790" s="6"/>
@@ -23199,11 +23188,11 @@
       <c r="C791" s="5"/>
       <c r="D791" s="5"/>
       <c r="E791" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F791" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G791" s="6"/>
@@ -23215,11 +23204,11 @@
       <c r="C792" s="5"/>
       <c r="D792" s="5"/>
       <c r="E792" s="5">
-        <f t="shared" ref="E792:E855" si="30">MONTH(A792)</f>
+        <f t="shared" ref="E792:E855" si="28">MONTH(A792)</f>
         <v>1</v>
       </c>
       <c r="F792" s="5" t="str">
-        <f t="shared" ref="F792:F855" si="31">B792&amp;C792&amp;E792&amp;D792</f>
+        <f t="shared" ref="F792:F855" si="29">B792&amp;C792&amp;E792&amp;D792</f>
         <v>1</v>
       </c>
       <c r="G792" s="6"/>
@@ -23231,11 +23220,11 @@
       <c r="C793" s="5"/>
       <c r="D793" s="5"/>
       <c r="E793" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F793" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G793" s="6"/>
@@ -23247,11 +23236,11 @@
       <c r="C794" s="5"/>
       <c r="D794" s="5"/>
       <c r="E794" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F794" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G794" s="6"/>
@@ -23263,11 +23252,11 @@
       <c r="C795" s="5"/>
       <c r="D795" s="5"/>
       <c r="E795" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F795" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G795" s="6"/>
@@ -23279,11 +23268,11 @@
       <c r="C796" s="5"/>
       <c r="D796" s="5"/>
       <c r="E796" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F796" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G796" s="6"/>
@@ -23295,11 +23284,11 @@
       <c r="C797" s="5"/>
       <c r="D797" s="5"/>
       <c r="E797" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F797" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G797" s="6"/>
@@ -23311,11 +23300,11 @@
       <c r="C798" s="5"/>
       <c r="D798" s="5"/>
       <c r="E798" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F798" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G798" s="6"/>
@@ -23327,11 +23316,11 @@
       <c r="C799" s="5"/>
       <c r="D799" s="5"/>
       <c r="E799" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F799" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G799" s="6"/>
@@ -23343,11 +23332,11 @@
       <c r="C800" s="5"/>
       <c r="D800" s="5"/>
       <c r="E800" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F800" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G800" s="6"/>
@@ -23359,11 +23348,11 @@
       <c r="C801" s="5"/>
       <c r="D801" s="5"/>
       <c r="E801" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F801" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G801" s="6"/>
@@ -23375,11 +23364,11 @@
       <c r="C802" s="5"/>
       <c r="D802" s="5"/>
       <c r="E802" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F802" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G802" s="6"/>
@@ -23391,11 +23380,11 @@
       <c r="C803" s="5"/>
       <c r="D803" s="5"/>
       <c r="E803" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F803" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G803" s="6"/>
@@ -23407,11 +23396,11 @@
       <c r="C804" s="5"/>
       <c r="D804" s="5"/>
       <c r="E804" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F804" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G804" s="6"/>
@@ -23423,11 +23412,11 @@
       <c r="C805" s="5"/>
       <c r="D805" s="5"/>
       <c r="E805" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F805" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G805" s="6"/>
@@ -23439,11 +23428,11 @@
       <c r="C806" s="5"/>
       <c r="D806" s="5"/>
       <c r="E806" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F806" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G806" s="6"/>
@@ -23455,11 +23444,11 @@
       <c r="C807" s="5"/>
       <c r="D807" s="5"/>
       <c r="E807" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F807" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G807" s="6"/>
@@ -23471,11 +23460,11 @@
       <c r="C808" s="5"/>
       <c r="D808" s="5"/>
       <c r="E808" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F808" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G808" s="6"/>
@@ -23487,11 +23476,11 @@
       <c r="C809" s="5"/>
       <c r="D809" s="5"/>
       <c r="E809" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F809" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G809" s="6"/>
@@ -23503,11 +23492,11 @@
       <c r="C810" s="5"/>
       <c r="D810" s="5"/>
       <c r="E810" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F810" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G810" s="6"/>
@@ -23519,11 +23508,11 @@
       <c r="C811" s="5"/>
       <c r="D811" s="5"/>
       <c r="E811" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F811" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G811" s="6"/>
@@ -23535,11 +23524,11 @@
       <c r="C812" s="5"/>
       <c r="D812" s="5"/>
       <c r="E812" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F812" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G812" s="6"/>
@@ -23551,11 +23540,11 @@
       <c r="C813" s="5"/>
       <c r="D813" s="5"/>
       <c r="E813" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F813" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G813" s="6"/>
@@ -23567,11 +23556,11 @@
       <c r="C814" s="5"/>
       <c r="D814" s="5"/>
       <c r="E814" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F814" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G814" s="6"/>
@@ -23583,11 +23572,11 @@
       <c r="C815" s="5"/>
       <c r="D815" s="5"/>
       <c r="E815" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F815" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G815" s="6"/>
@@ -23599,11 +23588,11 @@
       <c r="C816" s="5"/>
       <c r="D816" s="5"/>
       <c r="E816" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F816" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G816" s="6"/>
@@ -23615,11 +23604,11 @@
       <c r="C817" s="5"/>
       <c r="D817" s="5"/>
       <c r="E817" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F817" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G817" s="6"/>
@@ -23631,11 +23620,11 @@
       <c r="C818" s="5"/>
       <c r="D818" s="5"/>
       <c r="E818" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F818" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G818" s="6"/>
@@ -23647,11 +23636,11 @@
       <c r="C819" s="5"/>
       <c r="D819" s="5"/>
       <c r="E819" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F819" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G819" s="6"/>
@@ -23663,11 +23652,11 @@
       <c r="C820" s="5"/>
       <c r="D820" s="5"/>
       <c r="E820" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F820" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G820" s="6"/>
@@ -23679,11 +23668,11 @@
       <c r="C821" s="5"/>
       <c r="D821" s="5"/>
       <c r="E821" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F821" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G821" s="6"/>
@@ -23695,11 +23684,11 @@
       <c r="C822" s="5"/>
       <c r="D822" s="5"/>
       <c r="E822" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F822" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G822" s="6"/>
@@ -23711,11 +23700,11 @@
       <c r="C823" s="5"/>
       <c r="D823" s="5"/>
       <c r="E823" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F823" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G823" s="6"/>
@@ -23727,11 +23716,11 @@
       <c r="C824" s="5"/>
       <c r="D824" s="5"/>
       <c r="E824" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F824" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G824" s="6"/>
@@ -23743,11 +23732,11 @@
       <c r="C825" s="5"/>
       <c r="D825" s="5"/>
       <c r="E825" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F825" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G825" s="6"/>
@@ -23759,11 +23748,11 @@
       <c r="C826" s="5"/>
       <c r="D826" s="5"/>
       <c r="E826" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F826" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G826" s="6"/>
@@ -23775,11 +23764,11 @@
       <c r="C827" s="5"/>
       <c r="D827" s="5"/>
       <c r="E827" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F827" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G827" s="6"/>
@@ -23791,11 +23780,11 @@
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F828" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G828" s="6"/>
@@ -23807,11 +23796,11 @@
       <c r="C829" s="5"/>
       <c r="D829" s="5"/>
       <c r="E829" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F829" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G829" s="6"/>
@@ -23823,11 +23812,11 @@
       <c r="C830" s="5"/>
       <c r="D830" s="5"/>
       <c r="E830" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F830" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G830" s="6"/>
@@ -23839,11 +23828,11 @@
       <c r="C831" s="5"/>
       <c r="D831" s="5"/>
       <c r="E831" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F831" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G831" s="6"/>
@@ -23855,11 +23844,11 @@
       <c r="C832" s="5"/>
       <c r="D832" s="5"/>
       <c r="E832" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F832" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G832" s="6"/>
@@ -23871,11 +23860,11 @@
       <c r="C833" s="5"/>
       <c r="D833" s="5"/>
       <c r="E833" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F833" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G833" s="6"/>
@@ -23887,11 +23876,11 @@
       <c r="C834" s="5"/>
       <c r="D834" s="5"/>
       <c r="E834" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F834" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G834" s="6"/>
@@ -23903,11 +23892,11 @@
       <c r="C835" s="5"/>
       <c r="D835" s="5"/>
       <c r="E835" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F835" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G835" s="6"/>
@@ -23919,11 +23908,11 @@
       <c r="C836" s="5"/>
       <c r="D836" s="5"/>
       <c r="E836" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F836" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G836" s="6"/>
@@ -23935,11 +23924,11 @@
       <c r="C837" s="5"/>
       <c r="D837" s="5"/>
       <c r="E837" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F837" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G837" s="6"/>
@@ -23951,11 +23940,11 @@
       <c r="C838" s="5"/>
       <c r="D838" s="5"/>
       <c r="E838" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F838" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G838" s="6"/>
@@ -23967,11 +23956,11 @@
       <c r="C839" s="5"/>
       <c r="D839" s="5"/>
       <c r="E839" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F839" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G839" s="6"/>
@@ -23983,11 +23972,11 @@
       <c r="C840" s="5"/>
       <c r="D840" s="5"/>
       <c r="E840" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F840" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G840" s="6"/>
@@ -23999,11 +23988,11 @@
       <c r="C841" s="5"/>
       <c r="D841" s="5"/>
       <c r="E841" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F841" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G841" s="6"/>
@@ -24015,11 +24004,11 @@
       <c r="C842" s="5"/>
       <c r="D842" s="5"/>
       <c r="E842" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F842" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G842" s="6"/>
@@ -24031,11 +24020,11 @@
       <c r="C843" s="5"/>
       <c r="D843" s="5"/>
       <c r="E843" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F843" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G843" s="6"/>
@@ -24047,11 +24036,11 @@
       <c r="C844" s="5"/>
       <c r="D844" s="5"/>
       <c r="E844" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F844" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G844" s="6"/>
@@ -24063,11 +24052,11 @@
       <c r="C845" s="5"/>
       <c r="D845" s="5"/>
       <c r="E845" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F845" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G845" s="6"/>
@@ -24079,11 +24068,11 @@
       <c r="C846" s="5"/>
       <c r="D846" s="5"/>
       <c r="E846" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F846" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G846" s="6"/>
@@ -24095,11 +24084,11 @@
       <c r="C847" s="5"/>
       <c r="D847" s="5"/>
       <c r="E847" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F847" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G847" s="6"/>
@@ -24111,11 +24100,11 @@
       <c r="C848" s="5"/>
       <c r="D848" s="5"/>
       <c r="E848" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F848" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G848" s="6"/>
@@ -24127,11 +24116,11 @@
       <c r="C849" s="5"/>
       <c r="D849" s="5"/>
       <c r="E849" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F849" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G849" s="6"/>
@@ -24143,11 +24132,11 @@
       <c r="C850" s="5"/>
       <c r="D850" s="5"/>
       <c r="E850" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F850" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G850" s="6"/>
@@ -24159,11 +24148,11 @@
       <c r="C851" s="5"/>
       <c r="D851" s="5"/>
       <c r="E851" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F851" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G851" s="6"/>
@@ -24175,11 +24164,11 @@
       <c r="C852" s="5"/>
       <c r="D852" s="5"/>
       <c r="E852" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F852" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G852" s="6"/>
@@ -24191,11 +24180,11 @@
       <c r="C853" s="5"/>
       <c r="D853" s="5"/>
       <c r="E853" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F853" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G853" s="6"/>
@@ -24207,11 +24196,11 @@
       <c r="C854" s="5"/>
       <c r="D854" s="5"/>
       <c r="E854" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F854" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G854" s="6"/>
@@ -24223,11 +24212,11 @@
       <c r="C855" s="5"/>
       <c r="D855" s="5"/>
       <c r="E855" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F855" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G855" s="6"/>
@@ -24239,11 +24228,11 @@
       <c r="C856" s="5"/>
       <c r="D856" s="5"/>
       <c r="E856" s="5">
-        <f t="shared" ref="E856:E919" si="32">MONTH(A856)</f>
+        <f t="shared" ref="E856:E919" si="30">MONTH(A856)</f>
         <v>1</v>
       </c>
       <c r="F856" s="5" t="str">
-        <f t="shared" ref="F856:F919" si="33">B856&amp;C856&amp;E856&amp;D856</f>
+        <f t="shared" ref="F856:F919" si="31">B856&amp;C856&amp;E856&amp;D856</f>
         <v>1</v>
       </c>
       <c r="G856" s="6"/>
@@ -24255,11 +24244,11 @@
       <c r="C857" s="5"/>
       <c r="D857" s="5"/>
       <c r="E857" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F857" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G857" s="6"/>
@@ -24271,11 +24260,11 @@
       <c r="C858" s="5"/>
       <c r="D858" s="5"/>
       <c r="E858" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F858" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G858" s="6"/>
@@ -24287,11 +24276,11 @@
       <c r="C859" s="5"/>
       <c r="D859" s="5"/>
       <c r="E859" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F859" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G859" s="6"/>
@@ -24303,11 +24292,11 @@
       <c r="C860" s="5"/>
       <c r="D860" s="5"/>
       <c r="E860" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F860" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G860" s="6"/>
@@ -24319,11 +24308,11 @@
       <c r="C861" s="5"/>
       <c r="D861" s="5"/>
       <c r="E861" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F861" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G861" s="6"/>
@@ -24335,11 +24324,11 @@
       <c r="C862" s="5"/>
       <c r="D862" s="5"/>
       <c r="E862" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F862" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G862" s="6"/>
@@ -24351,11 +24340,11 @@
       <c r="C863" s="5"/>
       <c r="D863" s="5"/>
       <c r="E863" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F863" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G863" s="6"/>
@@ -24367,11 +24356,11 @@
       <c r="C864" s="5"/>
       <c r="D864" s="5"/>
       <c r="E864" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F864" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G864" s="6"/>
@@ -24383,11 +24372,11 @@
       <c r="C865" s="5"/>
       <c r="D865" s="5"/>
       <c r="E865" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F865" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G865" s="6"/>
@@ -24399,11 +24388,11 @@
       <c r="C866" s="5"/>
       <c r="D866" s="5"/>
       <c r="E866" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F866" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G866" s="6"/>
@@ -24415,11 +24404,11 @@
       <c r="C867" s="5"/>
       <c r="D867" s="5"/>
       <c r="E867" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F867" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G867" s="6"/>
@@ -24431,11 +24420,11 @@
       <c r="C868" s="5"/>
       <c r="D868" s="5"/>
       <c r="E868" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F868" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G868" s="6"/>
@@ -24447,11 +24436,11 @@
       <c r="C869" s="5"/>
       <c r="D869" s="5"/>
       <c r="E869" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F869" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G869" s="6"/>
@@ -24463,11 +24452,11 @@
       <c r="C870" s="5"/>
       <c r="D870" s="5"/>
       <c r="E870" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F870" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G870" s="6"/>
@@ -24479,11 +24468,11 @@
       <c r="C871" s="5"/>
       <c r="D871" s="5"/>
       <c r="E871" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F871" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G871" s="6"/>
@@ -24495,11 +24484,11 @@
       <c r="C872" s="5"/>
       <c r="D872" s="5"/>
       <c r="E872" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F872" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G872" s="6"/>
@@ -24511,11 +24500,11 @@
       <c r="C873" s="5"/>
       <c r="D873" s="5"/>
       <c r="E873" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F873" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G873" s="6"/>
@@ -24527,11 +24516,11 @@
       <c r="C874" s="5"/>
       <c r="D874" s="5"/>
       <c r="E874" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F874" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G874" s="6"/>
@@ -24543,11 +24532,11 @@
       <c r="C875" s="5"/>
       <c r="D875" s="5"/>
       <c r="E875" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F875" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G875" s="6"/>
@@ -24559,11 +24548,11 @@
       <c r="C876" s="5"/>
       <c r="D876" s="5"/>
       <c r="E876" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F876" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G876" s="6"/>
@@ -24575,11 +24564,11 @@
       <c r="C877" s="5"/>
       <c r="D877" s="5"/>
       <c r="E877" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F877" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G877" s="6"/>
@@ -24591,11 +24580,11 @@
       <c r="C878" s="5"/>
       <c r="D878" s="5"/>
       <c r="E878" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F878" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G878" s="6"/>
@@ -24607,11 +24596,11 @@
       <c r="C879" s="5"/>
       <c r="D879" s="5"/>
       <c r="E879" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F879" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G879" s="6"/>
@@ -24623,11 +24612,11 @@
       <c r="C880" s="5"/>
       <c r="D880" s="5"/>
       <c r="E880" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F880" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G880" s="6"/>
@@ -24639,11 +24628,11 @@
       <c r="C881" s="5"/>
       <c r="D881" s="5"/>
       <c r="E881" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F881" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G881" s="6"/>
@@ -24655,11 +24644,11 @@
       <c r="C882" s="5"/>
       <c r="D882" s="5"/>
       <c r="E882" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F882" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G882" s="6"/>
@@ -24671,11 +24660,11 @@
       <c r="C883" s="5"/>
       <c r="D883" s="5"/>
       <c r="E883" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F883" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G883" s="6"/>
@@ -24687,11 +24676,11 @@
       <c r="C884" s="5"/>
       <c r="D884" s="5"/>
       <c r="E884" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F884" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G884" s="6"/>
@@ -24703,11 +24692,11 @@
       <c r="C885" s="5"/>
       <c r="D885" s="5"/>
       <c r="E885" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F885" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G885" s="6"/>
@@ -24719,11 +24708,11 @@
       <c r="C886" s="5"/>
       <c r="D886" s="5"/>
       <c r="E886" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F886" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G886" s="6"/>
@@ -24735,11 +24724,11 @@
       <c r="C887" s="5"/>
       <c r="D887" s="5"/>
       <c r="E887" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F887" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G887" s="6"/>
@@ -24751,11 +24740,11 @@
       <c r="C888" s="5"/>
       <c r="D888" s="5"/>
       <c r="E888" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F888" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G888" s="6"/>
@@ -24767,11 +24756,11 @@
       <c r="C889" s="5"/>
       <c r="D889" s="5"/>
       <c r="E889" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F889" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G889" s="6"/>
@@ -24783,11 +24772,11 @@
       <c r="C890" s="5"/>
       <c r="D890" s="5"/>
       <c r="E890" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F890" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G890" s="6"/>
@@ -24799,11 +24788,11 @@
       <c r="C891" s="5"/>
       <c r="D891" s="5"/>
       <c r="E891" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F891" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G891" s="6"/>
@@ -24815,11 +24804,11 @@
       <c r="C892" s="5"/>
       <c r="D892" s="5"/>
       <c r="E892" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F892" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G892" s="6"/>
@@ -24831,11 +24820,11 @@
       <c r="C893" s="5"/>
       <c r="D893" s="5"/>
       <c r="E893" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F893" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G893" s="6"/>
@@ -24847,11 +24836,11 @@
       <c r="C894" s="5"/>
       <c r="D894" s="5"/>
       <c r="E894" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F894" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G894" s="6"/>
@@ -24863,11 +24852,11 @@
       <c r="C895" s="5"/>
       <c r="D895" s="5"/>
       <c r="E895" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F895" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G895" s="6"/>
@@ -24879,11 +24868,11 @@
       <c r="C896" s="5"/>
       <c r="D896" s="5"/>
       <c r="E896" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F896" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G896" s="6"/>
@@ -24895,11 +24884,11 @@
       <c r="C897" s="5"/>
       <c r="D897" s="5"/>
       <c r="E897" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F897" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G897" s="6"/>
@@ -24911,11 +24900,11 @@
       <c r="C898" s="5"/>
       <c r="D898" s="5"/>
       <c r="E898" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F898" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G898" s="6"/>
@@ -24927,11 +24916,11 @@
       <c r="C899" s="5"/>
       <c r="D899" s="5"/>
       <c r="E899" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F899" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G899" s="6"/>
@@ -24943,11 +24932,11 @@
       <c r="C900" s="5"/>
       <c r="D900" s="5"/>
       <c r="E900" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F900" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G900" s="6"/>
@@ -24959,11 +24948,11 @@
       <c r="C901" s="5"/>
       <c r="D901" s="5"/>
       <c r="E901" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F901" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G901" s="6"/>
@@ -24975,11 +24964,11 @@
       <c r="C902" s="5"/>
       <c r="D902" s="5"/>
       <c r="E902" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F902" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G902" s="6"/>
@@ -24991,11 +24980,11 @@
       <c r="C903" s="5"/>
       <c r="D903" s="5"/>
       <c r="E903" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F903" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G903" s="6"/>
@@ -25007,11 +24996,11 @@
       <c r="C904" s="5"/>
       <c r="D904" s="5"/>
       <c r="E904" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F904" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G904" s="6"/>
@@ -25023,11 +25012,11 @@
       <c r="C905" s="5"/>
       <c r="D905" s="5"/>
       <c r="E905" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F905" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G905" s="6"/>
@@ -25039,11 +25028,11 @@
       <c r="C906" s="5"/>
       <c r="D906" s="5"/>
       <c r="E906" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F906" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G906" s="6"/>
@@ -25055,11 +25044,11 @@
       <c r="C907" s="5"/>
       <c r="D907" s="5"/>
       <c r="E907" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F907" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G907" s="6"/>
@@ -25071,11 +25060,11 @@
       <c r="C908" s="5"/>
       <c r="D908" s="5"/>
       <c r="E908" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F908" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G908" s="6"/>
@@ -25087,11 +25076,11 @@
       <c r="C909" s="5"/>
       <c r="D909" s="5"/>
       <c r="E909" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F909" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G909" s="6"/>
@@ -25103,11 +25092,11 @@
       <c r="C910" s="5"/>
       <c r="D910" s="5"/>
       <c r="E910" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F910" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G910" s="6"/>
@@ -25119,11 +25108,11 @@
       <c r="C911" s="5"/>
       <c r="D911" s="5"/>
       <c r="E911" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F911" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G911" s="6"/>
@@ -25135,11 +25124,11 @@
       <c r="C912" s="5"/>
       <c r="D912" s="5"/>
       <c r="E912" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F912" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G912" s="6"/>
@@ -25151,11 +25140,11 @@
       <c r="C913" s="5"/>
       <c r="D913" s="5"/>
       <c r="E913" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F913" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G913" s="6"/>
@@ -25167,11 +25156,11 @@
       <c r="C914" s="5"/>
       <c r="D914" s="5"/>
       <c r="E914" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F914" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G914" s="6"/>
@@ -25183,11 +25172,11 @@
       <c r="C915" s="5"/>
       <c r="D915" s="5"/>
       <c r="E915" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F915" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G915" s="6"/>
@@ -25199,11 +25188,11 @@
       <c r="C916" s="5"/>
       <c r="D916" s="5"/>
       <c r="E916" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F916" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G916" s="6"/>
@@ -25215,11 +25204,11 @@
       <c r="C917" s="5"/>
       <c r="D917" s="5"/>
       <c r="E917" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F917" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G917" s="6"/>
@@ -25231,11 +25220,11 @@
       <c r="C918" s="5"/>
       <c r="D918" s="5"/>
       <c r="E918" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F918" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G918" s="6"/>
@@ -25247,11 +25236,11 @@
       <c r="C919" s="5"/>
       <c r="D919" s="5"/>
       <c r="E919" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F919" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G919" s="6"/>
@@ -25263,11 +25252,11 @@
       <c r="C920" s="5"/>
       <c r="D920" s="5"/>
       <c r="E920" s="5">
-        <f t="shared" ref="E920:E940" si="34">MONTH(A920)</f>
+        <f t="shared" ref="E920:E940" si="32">MONTH(A920)</f>
         <v>1</v>
       </c>
       <c r="F920" s="5" t="str">
-        <f t="shared" ref="F920:F940" si="35">B920&amp;C920&amp;E920&amp;D920</f>
+        <f t="shared" ref="F920:F940" si="33">B920&amp;C920&amp;E920&amp;D920</f>
         <v>1</v>
       </c>
       <c r="G920" s="6"/>
@@ -25279,11 +25268,11 @@
       <c r="C921" s="5"/>
       <c r="D921" s="5"/>
       <c r="E921" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F921" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G921" s="6"/>
@@ -25295,11 +25284,11 @@
       <c r="C922" s="5"/>
       <c r="D922" s="5"/>
       <c r="E922" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F922" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G922" s="6"/>
@@ -25311,11 +25300,11 @@
       <c r="C923" s="5"/>
       <c r="D923" s="5"/>
       <c r="E923" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F923" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G923" s="6"/>
@@ -25327,11 +25316,11 @@
       <c r="C924" s="5"/>
       <c r="D924" s="5"/>
       <c r="E924" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F924" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G924" s="6"/>
@@ -25343,11 +25332,11 @@
       <c r="C925" s="5"/>
       <c r="D925" s="5"/>
       <c r="E925" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F925" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G925" s="6"/>
@@ -25359,11 +25348,11 @@
       <c r="C926" s="5"/>
       <c r="D926" s="5"/>
       <c r="E926" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F926" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G926" s="6"/>
@@ -25375,11 +25364,11 @@
       <c r="C927" s="5"/>
       <c r="D927" s="5"/>
       <c r="E927" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F927" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G927" s="6"/>
@@ -25391,11 +25380,11 @@
       <c r="C928" s="5"/>
       <c r="D928" s="5"/>
       <c r="E928" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F928" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G928" s="6"/>
@@ -25407,11 +25396,11 @@
       <c r="C929" s="5"/>
       <c r="D929" s="5"/>
       <c r="E929" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F929" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G929" s="6"/>
@@ -25423,11 +25412,11 @@
       <c r="C930" s="5"/>
       <c r="D930" s="5"/>
       <c r="E930" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F930" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G930" s="6"/>
@@ -25439,11 +25428,11 @@
       <c r="C931" s="5"/>
       <c r="D931" s="5"/>
       <c r="E931" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F931" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G931" s="6"/>
@@ -25455,11 +25444,11 @@
       <c r="C932" s="5"/>
       <c r="D932" s="5"/>
       <c r="E932" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F932" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G932" s="6"/>
@@ -25471,11 +25460,11 @@
       <c r="C933" s="5"/>
       <c r="D933" s="5"/>
       <c r="E933" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F933" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G933" s="6"/>
@@ -25487,11 +25476,11 @@
       <c r="C934" s="5"/>
       <c r="D934" s="5"/>
       <c r="E934" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F934" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G934" s="6"/>
@@ -25503,11 +25492,11 @@
       <c r="C935" s="5"/>
       <c r="D935" s="5"/>
       <c r="E935" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F935" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G935" s="6"/>
@@ -25519,11 +25508,11 @@
       <c r="C936" s="5"/>
       <c r="D936" s="5"/>
       <c r="E936" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F936" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G936" s="6"/>
@@ -25535,11 +25524,11 @@
       <c r="C937" s="5"/>
       <c r="D937" s="5"/>
       <c r="E937" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F937" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G937" s="6"/>
@@ -25551,11 +25540,11 @@
       <c r="C938" s="5"/>
       <c r="D938" s="5"/>
       <c r="E938" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F938" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G938" s="6"/>
@@ -25567,11 +25556,11 @@
       <c r="C939" s="5"/>
       <c r="D939" s="5"/>
       <c r="E939" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F939" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G939" s="6"/>
@@ -25583,11 +25572,11 @@
       <c r="C940" s="5"/>
       <c r="D940" s="5"/>
       <c r="E940" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F940" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G940" s="6"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07F1DA33-48D1-4C83-ABF3-F6D068A9556C}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6890129-34A1-4580-8C95-39165ACC958E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="310">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1971,6 +1971,49 @@
   </si>
   <si>
     <t>しーちゃん</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お墓参り</t>
+    <rPh sb="1" eb="3">
+      <t>ハカマイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生活費</t>
+    <rPh sb="0" eb="3">
+      <t>セイカツヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>外食</t>
+    <rPh sb="0" eb="2">
+      <t>ガイショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鮭</t>
+    <rPh sb="0" eb="1">
+      <t>サケ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2163,10 +2206,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11431,7 +11470,7 @@
         <v>9</v>
       </c>
       <c r="F333" s="5" t="str">
-        <f t="shared" ref="F333:F403" si="11">B333&amp;C333&amp;E333&amp;D333</f>
+        <f t="shared" ref="F333:F394" si="11">B333&amp;C333&amp;E333&amp;D333</f>
         <v>ふるさと納税-9予算</v>
       </c>
       <c r="G333" s="6">
@@ -22191,52 +22230,86 @@
       </c>
     </row>
     <row r="729" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A729" s="7"/>
-      <c r="B729" s="5"/>
-      <c r="C729" s="5"/>
-      <c r="D729" s="5"/>
+      <c r="A729" s="7">
+        <v>46214</v>
+      </c>
+      <c r="B729" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D729" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E729" s="5">
-        <f t="shared" ref="E728:E791" si="26">MONTH(A729)</f>
-        <v>1</v>
+        <f t="shared" ref="E729:E731" si="26">MONTH(A729)</f>
+        <v>7</v>
       </c>
       <c r="F729" s="5" t="str">
-        <f t="shared" ref="F728:F791" si="27">B729&amp;C729&amp;E729&amp;D729</f>
-        <v>1</v>
-      </c>
-      <c r="G729" s="6"/>
+        <f t="shared" ref="F729:F731" si="27">B729&amp;C729&amp;E729&amp;D729</f>
+        <v>その他お墓参り7実績</v>
+      </c>
+      <c r="G729" s="6">
+        <v>2565</v>
+      </c>
       <c r="H729" s="6"/>
     </row>
     <row r="730" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A730" s="7"/>
-      <c r="B730" s="5"/>
-      <c r="C730" s="5"/>
-      <c r="D730" s="5"/>
+      <c r="A730" s="7">
+        <v>46214</v>
+      </c>
+      <c r="B730" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D730" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E730" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F730" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G730" s="6"/>
-      <c r="H730" s="6"/>
+        <v>生活費外食7実績</v>
+      </c>
+      <c r="G730" s="6">
+        <v>2814</v>
+      </c>
+      <c r="H730" s="6" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A731" s="7"/>
-      <c r="B731" s="5"/>
-      <c r="C731" s="5"/>
-      <c r="D731" s="5"/>
+      <c r="A731" s="7">
+        <v>46214</v>
+      </c>
+      <c r="B731" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D731" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E731" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F731" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G731" s="6"/>
-      <c r="H731" s="6"/>
+        <v>ふるさと納税-7実績</v>
+      </c>
+      <c r="G731" s="6">
+        <v>13000</v>
+      </c>
+      <c r="H731" s="6" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A732" s="7"/>
@@ -22244,11 +22317,11 @@
       <c r="C732" s="5"/>
       <c r="D732" s="5"/>
       <c r="E732" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="E729:E791" si="28">MONTH(A732)</f>
         <v>1</v>
       </c>
       <c r="F732" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F729:F791" si="29">B732&amp;C732&amp;E732&amp;D732</f>
         <v>1</v>
       </c>
       <c r="G732" s="6"/>
@@ -22260,11 +22333,11 @@
       <c r="C733" s="5"/>
       <c r="D733" s="5"/>
       <c r="E733" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F733" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G733" s="6"/>
@@ -22276,11 +22349,11 @@
       <c r="C734" s="5"/>
       <c r="D734" s="5"/>
       <c r="E734" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F734" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G734" s="6"/>
@@ -22292,11 +22365,11 @@
       <c r="C735" s="5"/>
       <c r="D735" s="5"/>
       <c r="E735" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F735" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G735" s="6"/>
@@ -22308,11 +22381,11 @@
       <c r="C736" s="5"/>
       <c r="D736" s="5"/>
       <c r="E736" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F736" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G736" s="6"/>
@@ -22324,11 +22397,11 @@
       <c r="C737" s="5"/>
       <c r="D737" s="5"/>
       <c r="E737" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F737" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G737" s="6"/>
@@ -22340,11 +22413,11 @@
       <c r="C738" s="5"/>
       <c r="D738" s="5"/>
       <c r="E738" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F738" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G738" s="6"/>
@@ -22356,11 +22429,11 @@
       <c r="C739" s="5"/>
       <c r="D739" s="5"/>
       <c r="E739" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F739" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G739" s="6"/>
@@ -22372,11 +22445,11 @@
       <c r="C740" s="5"/>
       <c r="D740" s="5"/>
       <c r="E740" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F740" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G740" s="6"/>
@@ -22388,11 +22461,11 @@
       <c r="C741" s="5"/>
       <c r="D741" s="5"/>
       <c r="E741" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F741" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G741" s="6"/>
@@ -22404,11 +22477,11 @@
       <c r="C742" s="5"/>
       <c r="D742" s="5"/>
       <c r="E742" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F742" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G742" s="6"/>
@@ -22420,11 +22493,11 @@
       <c r="C743" s="5"/>
       <c r="D743" s="5"/>
       <c r="E743" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F743" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G743" s="6"/>
@@ -22436,11 +22509,11 @@
       <c r="C744" s="5"/>
       <c r="D744" s="5"/>
       <c r="E744" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F744" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G744" s="6"/>
@@ -22452,11 +22525,11 @@
       <c r="C745" s="5"/>
       <c r="D745" s="5"/>
       <c r="E745" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F745" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G745" s="6"/>
@@ -22468,11 +22541,11 @@
       <c r="C746" s="5"/>
       <c r="D746" s="5"/>
       <c r="E746" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F746" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G746" s="6"/>
@@ -22484,11 +22557,11 @@
       <c r="C747" s="5"/>
       <c r="D747" s="5"/>
       <c r="E747" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F747" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G747" s="6"/>
@@ -22500,11 +22573,11 @@
       <c r="C748" s="5"/>
       <c r="D748" s="5"/>
       <c r="E748" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F748" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G748" s="6"/>
@@ -22516,11 +22589,11 @@
       <c r="C749" s="5"/>
       <c r="D749" s="5"/>
       <c r="E749" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F749" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G749" s="6"/>
@@ -22532,11 +22605,11 @@
       <c r="C750" s="5"/>
       <c r="D750" s="5"/>
       <c r="E750" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F750" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G750" s="6"/>
@@ -22548,11 +22621,11 @@
       <c r="C751" s="5"/>
       <c r="D751" s="5"/>
       <c r="E751" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F751" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G751" s="6"/>
@@ -22564,11 +22637,11 @@
       <c r="C752" s="5"/>
       <c r="D752" s="5"/>
       <c r="E752" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F752" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G752" s="6"/>
@@ -22580,11 +22653,11 @@
       <c r="C753" s="5"/>
       <c r="D753" s="5"/>
       <c r="E753" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F753" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G753" s="6"/>
@@ -22596,11 +22669,11 @@
       <c r="C754" s="5"/>
       <c r="D754" s="5"/>
       <c r="E754" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F754" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G754" s="6"/>
@@ -22612,11 +22685,11 @@
       <c r="C755" s="5"/>
       <c r="D755" s="5"/>
       <c r="E755" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F755" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G755" s="6"/>
@@ -22628,11 +22701,11 @@
       <c r="C756" s="5"/>
       <c r="D756" s="5"/>
       <c r="E756" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F756" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G756" s="6"/>
@@ -22644,11 +22717,11 @@
       <c r="C757" s="5"/>
       <c r="D757" s="5"/>
       <c r="E757" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F757" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G757" s="6"/>
@@ -22660,11 +22733,11 @@
       <c r="C758" s="5"/>
       <c r="D758" s="5"/>
       <c r="E758" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F758" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G758" s="6"/>
@@ -22676,11 +22749,11 @@
       <c r="C759" s="5"/>
       <c r="D759" s="5"/>
       <c r="E759" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F759" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G759" s="6"/>
@@ -22692,11 +22765,11 @@
       <c r="C760" s="5"/>
       <c r="D760" s="5"/>
       <c r="E760" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F760" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G760" s="6"/>
@@ -22708,11 +22781,11 @@
       <c r="C761" s="5"/>
       <c r="D761" s="5"/>
       <c r="E761" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F761" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G761" s="6"/>
@@ -22724,11 +22797,11 @@
       <c r="C762" s="5"/>
       <c r="D762" s="5"/>
       <c r="E762" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F762" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G762" s="6"/>
@@ -22740,11 +22813,11 @@
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F763" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G763" s="6"/>
@@ -22756,11 +22829,11 @@
       <c r="C764" s="5"/>
       <c r="D764" s="5"/>
       <c r="E764" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F764" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G764" s="6"/>
@@ -22772,11 +22845,11 @@
       <c r="C765" s="5"/>
       <c r="D765" s="5"/>
       <c r="E765" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F765" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G765" s="6"/>
@@ -22788,11 +22861,11 @@
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F766" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G766" s="6"/>
@@ -22804,11 +22877,11 @@
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F767" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G767" s="6"/>
@@ -22820,11 +22893,11 @@
       <c r="C768" s="5"/>
       <c r="D768" s="5"/>
       <c r="E768" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F768" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G768" s="6"/>
@@ -22836,11 +22909,11 @@
       <c r="C769" s="5"/>
       <c r="D769" s="5"/>
       <c r="E769" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F769" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G769" s="6"/>
@@ -22852,11 +22925,11 @@
       <c r="C770" s="5"/>
       <c r="D770" s="5"/>
       <c r="E770" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F770" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G770" s="6"/>
@@ -22868,11 +22941,11 @@
       <c r="C771" s="5"/>
       <c r="D771" s="5"/>
       <c r="E771" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F771" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G771" s="6"/>
@@ -22884,11 +22957,11 @@
       <c r="C772" s="5"/>
       <c r="D772" s="5"/>
       <c r="E772" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F772" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G772" s="6"/>
@@ -22900,11 +22973,11 @@
       <c r="C773" s="5"/>
       <c r="D773" s="5"/>
       <c r="E773" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F773" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G773" s="6"/>
@@ -22916,11 +22989,11 @@
       <c r="C774" s="5"/>
       <c r="D774" s="5"/>
       <c r="E774" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F774" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G774" s="6"/>
@@ -22932,11 +23005,11 @@
       <c r="C775" s="5"/>
       <c r="D775" s="5"/>
       <c r="E775" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F775" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G775" s="6"/>
@@ -22948,11 +23021,11 @@
       <c r="C776" s="5"/>
       <c r="D776" s="5"/>
       <c r="E776" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F776" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G776" s="6"/>
@@ -22964,11 +23037,11 @@
       <c r="C777" s="5"/>
       <c r="D777" s="5"/>
       <c r="E777" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F777" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G777" s="6"/>
@@ -22980,11 +23053,11 @@
       <c r="C778" s="5"/>
       <c r="D778" s="5"/>
       <c r="E778" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F778" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G778" s="6"/>
@@ -22996,11 +23069,11 @@
       <c r="C779" s="5"/>
       <c r="D779" s="5"/>
       <c r="E779" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F779" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G779" s="6"/>
@@ -23012,11 +23085,11 @@
       <c r="C780" s="5"/>
       <c r="D780" s="5"/>
       <c r="E780" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F780" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G780" s="6"/>
@@ -23028,11 +23101,11 @@
       <c r="C781" s="5"/>
       <c r="D781" s="5"/>
       <c r="E781" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F781" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G781" s="6"/>
@@ -23044,11 +23117,11 @@
       <c r="C782" s="5"/>
       <c r="D782" s="5"/>
       <c r="E782" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F782" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G782" s="6"/>
@@ -23060,11 +23133,11 @@
       <c r="C783" s="5"/>
       <c r="D783" s="5"/>
       <c r="E783" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F783" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G783" s="6"/>
@@ -23076,11 +23149,11 @@
       <c r="C784" s="5"/>
       <c r="D784" s="5"/>
       <c r="E784" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F784" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G784" s="6"/>
@@ -23092,11 +23165,11 @@
       <c r="C785" s="5"/>
       <c r="D785" s="5"/>
       <c r="E785" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F785" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G785" s="6"/>
@@ -23108,11 +23181,11 @@
       <c r="C786" s="5"/>
       <c r="D786" s="5"/>
       <c r="E786" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F786" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G786" s="6"/>
@@ -23124,11 +23197,11 @@
       <c r="C787" s="5"/>
       <c r="D787" s="5"/>
       <c r="E787" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F787" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G787" s="6"/>
@@ -23140,11 +23213,11 @@
       <c r="C788" s="5"/>
       <c r="D788" s="5"/>
       <c r="E788" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F788" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G788" s="6"/>
@@ -23156,11 +23229,11 @@
       <c r="C789" s="5"/>
       <c r="D789" s="5"/>
       <c r="E789" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F789" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G789" s="6"/>
@@ -23172,11 +23245,11 @@
       <c r="C790" s="5"/>
       <c r="D790" s="5"/>
       <c r="E790" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F790" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G790" s="6"/>
@@ -23188,11 +23261,11 @@
       <c r="C791" s="5"/>
       <c r="D791" s="5"/>
       <c r="E791" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F791" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G791" s="6"/>
@@ -23204,11 +23277,11 @@
       <c r="C792" s="5"/>
       <c r="D792" s="5"/>
       <c r="E792" s="5">
-        <f t="shared" ref="E792:E855" si="28">MONTH(A792)</f>
+        <f t="shared" ref="E792:E855" si="30">MONTH(A792)</f>
         <v>1</v>
       </c>
       <c r="F792" s="5" t="str">
-        <f t="shared" ref="F792:F855" si="29">B792&amp;C792&amp;E792&amp;D792</f>
+        <f t="shared" ref="F792:F855" si="31">B792&amp;C792&amp;E792&amp;D792</f>
         <v>1</v>
       </c>
       <c r="G792" s="6"/>
@@ -23220,11 +23293,11 @@
       <c r="C793" s="5"/>
       <c r="D793" s="5"/>
       <c r="E793" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F793" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G793" s="6"/>
@@ -23236,11 +23309,11 @@
       <c r="C794" s="5"/>
       <c r="D794" s="5"/>
       <c r="E794" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F794" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G794" s="6"/>
@@ -23252,11 +23325,11 @@
       <c r="C795" s="5"/>
       <c r="D795" s="5"/>
       <c r="E795" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F795" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G795" s="6"/>
@@ -23268,11 +23341,11 @@
       <c r="C796" s="5"/>
       <c r="D796" s="5"/>
       <c r="E796" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F796" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G796" s="6"/>
@@ -23284,11 +23357,11 @@
       <c r="C797" s="5"/>
       <c r="D797" s="5"/>
       <c r="E797" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F797" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G797" s="6"/>
@@ -23300,11 +23373,11 @@
       <c r="C798" s="5"/>
       <c r="D798" s="5"/>
       <c r="E798" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F798" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G798" s="6"/>
@@ -23316,11 +23389,11 @@
       <c r="C799" s="5"/>
       <c r="D799" s="5"/>
       <c r="E799" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F799" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G799" s="6"/>
@@ -23332,11 +23405,11 @@
       <c r="C800" s="5"/>
       <c r="D800" s="5"/>
       <c r="E800" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F800" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G800" s="6"/>
@@ -23348,11 +23421,11 @@
       <c r="C801" s="5"/>
       <c r="D801" s="5"/>
       <c r="E801" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F801" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G801" s="6"/>
@@ -23364,11 +23437,11 @@
       <c r="C802" s="5"/>
       <c r="D802" s="5"/>
       <c r="E802" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F802" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G802" s="6"/>
@@ -23380,11 +23453,11 @@
       <c r="C803" s="5"/>
       <c r="D803" s="5"/>
       <c r="E803" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F803" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G803" s="6"/>
@@ -23396,11 +23469,11 @@
       <c r="C804" s="5"/>
       <c r="D804" s="5"/>
       <c r="E804" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F804" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G804" s="6"/>
@@ -23412,11 +23485,11 @@
       <c r="C805" s="5"/>
       <c r="D805" s="5"/>
       <c r="E805" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F805" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G805" s="6"/>
@@ -23428,11 +23501,11 @@
       <c r="C806" s="5"/>
       <c r="D806" s="5"/>
       <c r="E806" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F806" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G806" s="6"/>
@@ -23444,11 +23517,11 @@
       <c r="C807" s="5"/>
       <c r="D807" s="5"/>
       <c r="E807" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F807" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G807" s="6"/>
@@ -23460,11 +23533,11 @@
       <c r="C808" s="5"/>
       <c r="D808" s="5"/>
       <c r="E808" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F808" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G808" s="6"/>
@@ -23476,11 +23549,11 @@
       <c r="C809" s="5"/>
       <c r="D809" s="5"/>
       <c r="E809" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F809" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G809" s="6"/>
@@ -23492,11 +23565,11 @@
       <c r="C810" s="5"/>
       <c r="D810" s="5"/>
       <c r="E810" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F810" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G810" s="6"/>
@@ -23508,11 +23581,11 @@
       <c r="C811" s="5"/>
       <c r="D811" s="5"/>
       <c r="E811" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F811" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G811" s="6"/>
@@ -23524,11 +23597,11 @@
       <c r="C812" s="5"/>
       <c r="D812" s="5"/>
       <c r="E812" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F812" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G812" s="6"/>
@@ -23540,11 +23613,11 @@
       <c r="C813" s="5"/>
       <c r="D813" s="5"/>
       <c r="E813" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F813" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G813" s="6"/>
@@ -23556,11 +23629,11 @@
       <c r="C814" s="5"/>
       <c r="D814" s="5"/>
       <c r="E814" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F814" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G814" s="6"/>
@@ -23572,11 +23645,11 @@
       <c r="C815" s="5"/>
       <c r="D815" s="5"/>
       <c r="E815" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F815" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G815" s="6"/>
@@ -23588,11 +23661,11 @@
       <c r="C816" s="5"/>
       <c r="D816" s="5"/>
       <c r="E816" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F816" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G816" s="6"/>
@@ -23604,11 +23677,11 @@
       <c r="C817" s="5"/>
       <c r="D817" s="5"/>
       <c r="E817" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F817" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G817" s="6"/>
@@ -23620,11 +23693,11 @@
       <c r="C818" s="5"/>
       <c r="D818" s="5"/>
       <c r="E818" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F818" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G818" s="6"/>
@@ -23636,11 +23709,11 @@
       <c r="C819" s="5"/>
       <c r="D819" s="5"/>
       <c r="E819" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F819" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G819" s="6"/>
@@ -23652,11 +23725,11 @@
       <c r="C820" s="5"/>
       <c r="D820" s="5"/>
       <c r="E820" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F820" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G820" s="6"/>
@@ -23668,11 +23741,11 @@
       <c r="C821" s="5"/>
       <c r="D821" s="5"/>
       <c r="E821" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F821" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G821" s="6"/>
@@ -23684,11 +23757,11 @@
       <c r="C822" s="5"/>
       <c r="D822" s="5"/>
       <c r="E822" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F822" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G822" s="6"/>
@@ -23700,11 +23773,11 @@
       <c r="C823" s="5"/>
       <c r="D823" s="5"/>
       <c r="E823" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F823" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G823" s="6"/>
@@ -23716,11 +23789,11 @@
       <c r="C824" s="5"/>
       <c r="D824" s="5"/>
       <c r="E824" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F824" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G824" s="6"/>
@@ -23732,11 +23805,11 @@
       <c r="C825" s="5"/>
       <c r="D825" s="5"/>
       <c r="E825" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F825" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G825" s="6"/>
@@ -23748,11 +23821,11 @@
       <c r="C826" s="5"/>
       <c r="D826" s="5"/>
       <c r="E826" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F826" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G826" s="6"/>
@@ -23764,11 +23837,11 @@
       <c r="C827" s="5"/>
       <c r="D827" s="5"/>
       <c r="E827" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F827" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G827" s="6"/>
@@ -23780,11 +23853,11 @@
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F828" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G828" s="6"/>
@@ -23796,11 +23869,11 @@
       <c r="C829" s="5"/>
       <c r="D829" s="5"/>
       <c r="E829" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F829" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G829" s="6"/>
@@ -23812,11 +23885,11 @@
       <c r="C830" s="5"/>
       <c r="D830" s="5"/>
       <c r="E830" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F830" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G830" s="6"/>
@@ -23828,11 +23901,11 @@
       <c r="C831" s="5"/>
       <c r="D831" s="5"/>
       <c r="E831" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F831" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G831" s="6"/>
@@ -23844,11 +23917,11 @@
       <c r="C832" s="5"/>
       <c r="D832" s="5"/>
       <c r="E832" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F832" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G832" s="6"/>
@@ -23860,11 +23933,11 @@
       <c r="C833" s="5"/>
       <c r="D833" s="5"/>
       <c r="E833" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F833" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G833" s="6"/>
@@ -23876,11 +23949,11 @@
       <c r="C834" s="5"/>
       <c r="D834" s="5"/>
       <c r="E834" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F834" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G834" s="6"/>
@@ -23892,11 +23965,11 @@
       <c r="C835" s="5"/>
       <c r="D835" s="5"/>
       <c r="E835" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F835" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G835" s="6"/>
@@ -23908,11 +23981,11 @@
       <c r="C836" s="5"/>
       <c r="D836" s="5"/>
       <c r="E836" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F836" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G836" s="6"/>
@@ -23924,11 +23997,11 @@
       <c r="C837" s="5"/>
       <c r="D837" s="5"/>
       <c r="E837" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F837" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G837" s="6"/>
@@ -23940,11 +24013,11 @@
       <c r="C838" s="5"/>
       <c r="D838" s="5"/>
       <c r="E838" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F838" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G838" s="6"/>
@@ -23956,11 +24029,11 @@
       <c r="C839" s="5"/>
       <c r="D839" s="5"/>
       <c r="E839" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F839" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G839" s="6"/>
@@ -23972,11 +24045,11 @@
       <c r="C840" s="5"/>
       <c r="D840" s="5"/>
       <c r="E840" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F840" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G840" s="6"/>
@@ -23988,11 +24061,11 @@
       <c r="C841" s="5"/>
       <c r="D841" s="5"/>
       <c r="E841" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F841" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G841" s="6"/>
@@ -24004,11 +24077,11 @@
       <c r="C842" s="5"/>
       <c r="D842" s="5"/>
       <c r="E842" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F842" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G842" s="6"/>
@@ -24020,11 +24093,11 @@
       <c r="C843" s="5"/>
       <c r="D843" s="5"/>
       <c r="E843" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F843" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G843" s="6"/>
@@ -24036,11 +24109,11 @@
       <c r="C844" s="5"/>
       <c r="D844" s="5"/>
       <c r="E844" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F844" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G844" s="6"/>
@@ -24052,11 +24125,11 @@
       <c r="C845" s="5"/>
       <c r="D845" s="5"/>
       <c r="E845" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F845" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G845" s="6"/>
@@ -24068,11 +24141,11 @@
       <c r="C846" s="5"/>
       <c r="D846" s="5"/>
       <c r="E846" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F846" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G846" s="6"/>
@@ -24084,11 +24157,11 @@
       <c r="C847" s="5"/>
       <c r="D847" s="5"/>
       <c r="E847" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F847" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G847" s="6"/>
@@ -24100,11 +24173,11 @@
       <c r="C848" s="5"/>
       <c r="D848" s="5"/>
       <c r="E848" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F848" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G848" s="6"/>
@@ -24116,11 +24189,11 @@
       <c r="C849" s="5"/>
       <c r="D849" s="5"/>
       <c r="E849" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F849" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G849" s="6"/>
@@ -24132,11 +24205,11 @@
       <c r="C850" s="5"/>
       <c r="D850" s="5"/>
       <c r="E850" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F850" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G850" s="6"/>
@@ -24148,11 +24221,11 @@
       <c r="C851" s="5"/>
       <c r="D851" s="5"/>
       <c r="E851" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F851" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G851" s="6"/>
@@ -24164,11 +24237,11 @@
       <c r="C852" s="5"/>
       <c r="D852" s="5"/>
       <c r="E852" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F852" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G852" s="6"/>
@@ -24180,11 +24253,11 @@
       <c r="C853" s="5"/>
       <c r="D853" s="5"/>
       <c r="E853" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F853" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G853" s="6"/>
@@ -24196,11 +24269,11 @@
       <c r="C854" s="5"/>
       <c r="D854" s="5"/>
       <c r="E854" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F854" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G854" s="6"/>
@@ -24212,11 +24285,11 @@
       <c r="C855" s="5"/>
       <c r="D855" s="5"/>
       <c r="E855" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F855" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G855" s="6"/>
@@ -24228,11 +24301,11 @@
       <c r="C856" s="5"/>
       <c r="D856" s="5"/>
       <c r="E856" s="5">
-        <f t="shared" ref="E856:E919" si="30">MONTH(A856)</f>
+        <f t="shared" ref="E856:E919" si="32">MONTH(A856)</f>
         <v>1</v>
       </c>
       <c r="F856" s="5" t="str">
-        <f t="shared" ref="F856:F919" si="31">B856&amp;C856&amp;E856&amp;D856</f>
+        <f t="shared" ref="F856:F919" si="33">B856&amp;C856&amp;E856&amp;D856</f>
         <v>1</v>
       </c>
       <c r="G856" s="6"/>
@@ -24244,11 +24317,11 @@
       <c r="C857" s="5"/>
       <c r="D857" s="5"/>
       <c r="E857" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F857" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G857" s="6"/>
@@ -24260,11 +24333,11 @@
       <c r="C858" s="5"/>
       <c r="D858" s="5"/>
       <c r="E858" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F858" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G858" s="6"/>
@@ -24276,11 +24349,11 @@
       <c r="C859" s="5"/>
       <c r="D859" s="5"/>
       <c r="E859" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F859" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G859" s="6"/>
@@ -24292,11 +24365,11 @@
       <c r="C860" s="5"/>
       <c r="D860" s="5"/>
       <c r="E860" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F860" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G860" s="6"/>
@@ -24308,11 +24381,11 @@
       <c r="C861" s="5"/>
       <c r="D861" s="5"/>
       <c r="E861" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F861" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G861" s="6"/>
@@ -24324,11 +24397,11 @@
       <c r="C862" s="5"/>
       <c r="D862" s="5"/>
       <c r="E862" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F862" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G862" s="6"/>
@@ -24340,11 +24413,11 @@
       <c r="C863" s="5"/>
       <c r="D863" s="5"/>
       <c r="E863" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F863" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G863" s="6"/>
@@ -24356,11 +24429,11 @@
       <c r="C864" s="5"/>
       <c r="D864" s="5"/>
       <c r="E864" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F864" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G864" s="6"/>
@@ -24372,11 +24445,11 @@
       <c r="C865" s="5"/>
       <c r="D865" s="5"/>
       <c r="E865" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F865" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G865" s="6"/>
@@ -24388,11 +24461,11 @@
       <c r="C866" s="5"/>
       <c r="D866" s="5"/>
       <c r="E866" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F866" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G866" s="6"/>
@@ -24404,11 +24477,11 @@
       <c r="C867" s="5"/>
       <c r="D867" s="5"/>
       <c r="E867" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F867" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G867" s="6"/>
@@ -24420,11 +24493,11 @@
       <c r="C868" s="5"/>
       <c r="D868" s="5"/>
       <c r="E868" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F868" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G868" s="6"/>
@@ -24436,11 +24509,11 @@
       <c r="C869" s="5"/>
       <c r="D869" s="5"/>
       <c r="E869" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F869" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G869" s="6"/>
@@ -24452,11 +24525,11 @@
       <c r="C870" s="5"/>
       <c r="D870" s="5"/>
       <c r="E870" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F870" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G870" s="6"/>
@@ -24468,11 +24541,11 @@
       <c r="C871" s="5"/>
       <c r="D871" s="5"/>
       <c r="E871" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F871" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G871" s="6"/>
@@ -24484,11 +24557,11 @@
       <c r="C872" s="5"/>
       <c r="D872" s="5"/>
       <c r="E872" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F872" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G872" s="6"/>
@@ -24500,11 +24573,11 @@
       <c r="C873" s="5"/>
       <c r="D873" s="5"/>
       <c r="E873" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F873" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G873" s="6"/>
@@ -24516,11 +24589,11 @@
       <c r="C874" s="5"/>
       <c r="D874" s="5"/>
       <c r="E874" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F874" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G874" s="6"/>
@@ -24532,11 +24605,11 @@
       <c r="C875" s="5"/>
       <c r="D875" s="5"/>
       <c r="E875" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F875" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G875" s="6"/>
@@ -24548,11 +24621,11 @@
       <c r="C876" s="5"/>
       <c r="D876" s="5"/>
       <c r="E876" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F876" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G876" s="6"/>
@@ -24564,11 +24637,11 @@
       <c r="C877" s="5"/>
       <c r="D877" s="5"/>
       <c r="E877" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F877" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G877" s="6"/>
@@ -24580,11 +24653,11 @@
       <c r="C878" s="5"/>
       <c r="D878" s="5"/>
       <c r="E878" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F878" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G878" s="6"/>
@@ -24596,11 +24669,11 @@
       <c r="C879" s="5"/>
       <c r="D879" s="5"/>
       <c r="E879" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F879" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G879" s="6"/>
@@ -24612,11 +24685,11 @@
       <c r="C880" s="5"/>
       <c r="D880" s="5"/>
       <c r="E880" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F880" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G880" s="6"/>
@@ -24628,11 +24701,11 @@
       <c r="C881" s="5"/>
       <c r="D881" s="5"/>
       <c r="E881" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F881" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G881" s="6"/>
@@ -24644,11 +24717,11 @@
       <c r="C882" s="5"/>
       <c r="D882" s="5"/>
       <c r="E882" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F882" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G882" s="6"/>
@@ -24660,11 +24733,11 @@
       <c r="C883" s="5"/>
       <c r="D883" s="5"/>
       <c r="E883" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F883" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G883" s="6"/>
@@ -24676,11 +24749,11 @@
       <c r="C884" s="5"/>
       <c r="D884" s="5"/>
       <c r="E884" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F884" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G884" s="6"/>
@@ -24692,11 +24765,11 @@
       <c r="C885" s="5"/>
       <c r="D885" s="5"/>
       <c r="E885" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F885" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G885" s="6"/>
@@ -24708,11 +24781,11 @@
       <c r="C886" s="5"/>
       <c r="D886" s="5"/>
       <c r="E886" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F886" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G886" s="6"/>
@@ -24724,11 +24797,11 @@
       <c r="C887" s="5"/>
       <c r="D887" s="5"/>
       <c r="E887" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F887" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G887" s="6"/>
@@ -24740,11 +24813,11 @@
       <c r="C888" s="5"/>
       <c r="D888" s="5"/>
       <c r="E888" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F888" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G888" s="6"/>
@@ -24756,11 +24829,11 @@
       <c r="C889" s="5"/>
       <c r="D889" s="5"/>
       <c r="E889" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F889" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G889" s="6"/>
@@ -24772,11 +24845,11 @@
       <c r="C890" s="5"/>
       <c r="D890" s="5"/>
       <c r="E890" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F890" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G890" s="6"/>
@@ -24788,11 +24861,11 @@
       <c r="C891" s="5"/>
       <c r="D891" s="5"/>
       <c r="E891" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F891" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G891" s="6"/>
@@ -24804,11 +24877,11 @@
       <c r="C892" s="5"/>
       <c r="D892" s="5"/>
       <c r="E892" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F892" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G892" s="6"/>
@@ -24820,11 +24893,11 @@
       <c r="C893" s="5"/>
       <c r="D893" s="5"/>
       <c r="E893" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F893" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G893" s="6"/>
@@ -24836,11 +24909,11 @@
       <c r="C894" s="5"/>
       <c r="D894" s="5"/>
       <c r="E894" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F894" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G894" s="6"/>
@@ -24852,11 +24925,11 @@
       <c r="C895" s="5"/>
       <c r="D895" s="5"/>
       <c r="E895" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F895" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G895" s="6"/>
@@ -24868,11 +24941,11 @@
       <c r="C896" s="5"/>
       <c r="D896" s="5"/>
       <c r="E896" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F896" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G896" s="6"/>
@@ -24884,11 +24957,11 @@
       <c r="C897" s="5"/>
       <c r="D897" s="5"/>
       <c r="E897" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F897" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G897" s="6"/>
@@ -24900,11 +24973,11 @@
       <c r="C898" s="5"/>
       <c r="D898" s="5"/>
       <c r="E898" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F898" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G898" s="6"/>
@@ -24916,11 +24989,11 @@
       <c r="C899" s="5"/>
       <c r="D899" s="5"/>
       <c r="E899" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F899" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G899" s="6"/>
@@ -24932,11 +25005,11 @@
       <c r="C900" s="5"/>
       <c r="D900" s="5"/>
       <c r="E900" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F900" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G900" s="6"/>
@@ -24948,11 +25021,11 @@
       <c r="C901" s="5"/>
       <c r="D901" s="5"/>
       <c r="E901" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F901" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G901" s="6"/>
@@ -24964,11 +25037,11 @@
       <c r="C902" s="5"/>
       <c r="D902" s="5"/>
       <c r="E902" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F902" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G902" s="6"/>
@@ -24980,11 +25053,11 @@
       <c r="C903" s="5"/>
       <c r="D903" s="5"/>
       <c r="E903" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F903" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G903" s="6"/>
@@ -24996,11 +25069,11 @@
       <c r="C904" s="5"/>
       <c r="D904" s="5"/>
       <c r="E904" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F904" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G904" s="6"/>
@@ -25012,11 +25085,11 @@
       <c r="C905" s="5"/>
       <c r="D905" s="5"/>
       <c r="E905" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F905" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G905" s="6"/>
@@ -25028,11 +25101,11 @@
       <c r="C906" s="5"/>
       <c r="D906" s="5"/>
       <c r="E906" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F906" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G906" s="6"/>
@@ -25044,11 +25117,11 @@
       <c r="C907" s="5"/>
       <c r="D907" s="5"/>
       <c r="E907" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F907" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G907" s="6"/>
@@ -25060,11 +25133,11 @@
       <c r="C908" s="5"/>
       <c r="D908" s="5"/>
       <c r="E908" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F908" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G908" s="6"/>
@@ -25076,11 +25149,11 @@
       <c r="C909" s="5"/>
       <c r="D909" s="5"/>
       <c r="E909" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F909" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G909" s="6"/>
@@ -25092,11 +25165,11 @@
       <c r="C910" s="5"/>
       <c r="D910" s="5"/>
       <c r="E910" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F910" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G910" s="6"/>
@@ -25108,11 +25181,11 @@
       <c r="C911" s="5"/>
       <c r="D911" s="5"/>
       <c r="E911" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F911" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G911" s="6"/>
@@ -25124,11 +25197,11 @@
       <c r="C912" s="5"/>
       <c r="D912" s="5"/>
       <c r="E912" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F912" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G912" s="6"/>
@@ -25140,11 +25213,11 @@
       <c r="C913" s="5"/>
       <c r="D913" s="5"/>
       <c r="E913" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F913" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G913" s="6"/>
@@ -25156,11 +25229,11 @@
       <c r="C914" s="5"/>
       <c r="D914" s="5"/>
       <c r="E914" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F914" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G914" s="6"/>
@@ -25172,11 +25245,11 @@
       <c r="C915" s="5"/>
       <c r="D915" s="5"/>
       <c r="E915" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F915" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G915" s="6"/>
@@ -25188,11 +25261,11 @@
       <c r="C916" s="5"/>
       <c r="D916" s="5"/>
       <c r="E916" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F916" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G916" s="6"/>
@@ -25204,11 +25277,11 @@
       <c r="C917" s="5"/>
       <c r="D917" s="5"/>
       <c r="E917" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F917" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G917" s="6"/>
@@ -25220,11 +25293,11 @@
       <c r="C918" s="5"/>
       <c r="D918" s="5"/>
       <c r="E918" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F918" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G918" s="6"/>
@@ -25236,11 +25309,11 @@
       <c r="C919" s="5"/>
       <c r="D919" s="5"/>
       <c r="E919" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F919" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G919" s="6"/>
@@ -25252,11 +25325,11 @@
       <c r="C920" s="5"/>
       <c r="D920" s="5"/>
       <c r="E920" s="5">
-        <f t="shared" ref="E920:E940" si="32">MONTH(A920)</f>
+        <f t="shared" ref="E920:E940" si="34">MONTH(A920)</f>
         <v>1</v>
       </c>
       <c r="F920" s="5" t="str">
-        <f t="shared" ref="F920:F940" si="33">B920&amp;C920&amp;E920&amp;D920</f>
+        <f t="shared" ref="F920:F940" si="35">B920&amp;C920&amp;E920&amp;D920</f>
         <v>1</v>
       </c>
       <c r="G920" s="6"/>
@@ -25268,11 +25341,11 @@
       <c r="C921" s="5"/>
       <c r="D921" s="5"/>
       <c r="E921" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F921" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G921" s="6"/>
@@ -25284,11 +25357,11 @@
       <c r="C922" s="5"/>
       <c r="D922" s="5"/>
       <c r="E922" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F922" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G922" s="6"/>
@@ -25300,11 +25373,11 @@
       <c r="C923" s="5"/>
       <c r="D923" s="5"/>
       <c r="E923" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F923" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G923" s="6"/>
@@ -25316,11 +25389,11 @@
       <c r="C924" s="5"/>
       <c r="D924" s="5"/>
       <c r="E924" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F924" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G924" s="6"/>
@@ -25332,11 +25405,11 @@
       <c r="C925" s="5"/>
       <c r="D925" s="5"/>
       <c r="E925" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F925" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G925" s="6"/>
@@ -25348,11 +25421,11 @@
       <c r="C926" s="5"/>
       <c r="D926" s="5"/>
       <c r="E926" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F926" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G926" s="6"/>
@@ -25364,11 +25437,11 @@
       <c r="C927" s="5"/>
       <c r="D927" s="5"/>
       <c r="E927" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F927" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G927" s="6"/>
@@ -25380,11 +25453,11 @@
       <c r="C928" s="5"/>
       <c r="D928" s="5"/>
       <c r="E928" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F928" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G928" s="6"/>
@@ -25396,11 +25469,11 @@
       <c r="C929" s="5"/>
       <c r="D929" s="5"/>
       <c r="E929" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F929" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G929" s="6"/>
@@ -25412,11 +25485,11 @@
       <c r="C930" s="5"/>
       <c r="D930" s="5"/>
       <c r="E930" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F930" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G930" s="6"/>
@@ -25428,11 +25501,11 @@
       <c r="C931" s="5"/>
       <c r="D931" s="5"/>
       <c r="E931" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F931" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G931" s="6"/>
@@ -25444,11 +25517,11 @@
       <c r="C932" s="5"/>
       <c r="D932" s="5"/>
       <c r="E932" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F932" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G932" s="6"/>
@@ -25460,11 +25533,11 @@
       <c r="C933" s="5"/>
       <c r="D933" s="5"/>
       <c r="E933" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F933" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G933" s="6"/>
@@ -25476,11 +25549,11 @@
       <c r="C934" s="5"/>
       <c r="D934" s="5"/>
       <c r="E934" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F934" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G934" s="6"/>
@@ -25492,11 +25565,11 @@
       <c r="C935" s="5"/>
       <c r="D935" s="5"/>
       <c r="E935" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F935" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G935" s="6"/>
@@ -25508,11 +25581,11 @@
       <c r="C936" s="5"/>
       <c r="D936" s="5"/>
       <c r="E936" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F936" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G936" s="6"/>
@@ -25524,11 +25597,11 @@
       <c r="C937" s="5"/>
       <c r="D937" s="5"/>
       <c r="E937" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F937" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G937" s="6"/>
@@ -25540,11 +25613,11 @@
       <c r="C938" s="5"/>
       <c r="D938" s="5"/>
       <c r="E938" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F938" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G938" s="6"/>
@@ -25556,11 +25629,11 @@
       <c r="C939" s="5"/>
       <c r="D939" s="5"/>
       <c r="E939" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F939" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G939" s="6"/>
@@ -25572,11 +25645,11 @@
       <c r="C940" s="5"/>
       <c r="D940" s="5"/>
       <c r="E940" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="F940" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="G940" s="6"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6890129-34A1-4580-8C95-39165ACC958E}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88A56635-64A0-4F3B-99E7-E306275029D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="303">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -1971,49 +1971,6 @@
   </si>
   <si>
     <t>しーちゃん</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>その他</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お墓参り</t>
-    <rPh sb="1" eb="3">
-      <t>ハカマイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>生活費</t>
-    <rPh sb="0" eb="3">
-      <t>セイカツヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>外食</t>
-    <rPh sb="0" eb="2">
-      <t>ガイショク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>マック</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>鮭</t>
-    <rPh sb="0" eb="1">
-      <t>サケ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11470,7 +11427,7 @@
         <v>9</v>
       </c>
       <c r="F333" s="5" t="str">
-        <f t="shared" ref="F333:F394" si="11">B333&amp;C333&amp;E333&amp;D333</f>
+        <f t="shared" ref="F333:F403" si="11">B333&amp;C333&amp;E333&amp;D333</f>
         <v>ふるさと納税-9予算</v>
       </c>
       <c r="G333" s="6">
@@ -18308,7 +18265,7 @@
         <v>4</v>
       </c>
       <c r="F585" s="5" t="str">
-        <f t="shared" ref="F585:F728" si="19">B585&amp;C585&amp;E585&amp;D585</f>
+        <f t="shared" ref="F585:F735" si="19">B585&amp;C585&amp;E585&amp;D585</f>
         <v>服りょう4実績</v>
       </c>
       <c r="G585" s="6">
@@ -20227,7 +20184,7 @@
         <v>19</v>
       </c>
       <c r="E656" s="5">
-        <f t="shared" ref="E656:E728" si="23">MONTH(A656)</f>
+        <f t="shared" ref="E656:E735" si="23">MONTH(A656)</f>
         <v>5</v>
       </c>
       <c r="F656" s="5" t="str">
@@ -22234,20 +22191,20 @@
         <v>46214</v>
       </c>
       <c r="B729" s="5" t="s">
-        <v>303</v>
+        <v>11</v>
       </c>
       <c r="C729" s="5" t="s">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="D729" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E729" s="5">
-        <f t="shared" ref="E729:E731" si="26">MONTH(A729)</f>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="F729" s="5" t="str">
-        <f t="shared" ref="F729:F731" si="27">B729&amp;C729&amp;E729&amp;D729</f>
+        <f t="shared" si="19"/>
         <v>その他お墓参り7実績</v>
       </c>
       <c r="G729" s="6">
@@ -22260,27 +22217,27 @@
         <v>46214</v>
       </c>
       <c r="B730" s="5" t="s">
-        <v>305</v>
+        <v>3</v>
       </c>
       <c r="C730" s="5" t="s">
-        <v>306</v>
+        <v>9</v>
       </c>
       <c r="D730" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E730" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="F730" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="19"/>
         <v>生活費外食7実績</v>
       </c>
       <c r="G730" s="6">
         <v>2814</v>
       </c>
       <c r="H730" s="6" t="s">
-        <v>307</v>
+        <v>108</v>
       </c>
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.35">
@@ -22291,89 +22248,127 @@
         <v>29</v>
       </c>
       <c r="C731" s="5" t="s">
-        <v>308</v>
+        <v>20</v>
       </c>
       <c r="D731" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E731" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>7</v>
       </c>
       <c r="F731" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="19"/>
         <v>ふるさと納税-7実績</v>
       </c>
       <c r="G731" s="6">
         <v>13000</v>
       </c>
       <c r="H731" s="6" t="s">
-        <v>309</v>
+        <v>169</v>
       </c>
     </row>
     <row r="732" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A732" s="7"/>
-      <c r="B732" s="5"/>
+      <c r="A732" s="7">
+        <v>46215</v>
+      </c>
+      <c r="B732" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C732" s="5"/>
-      <c r="D732" s="5"/>
+      <c r="D732" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E732" s="5">
-        <f t="shared" ref="E729:E791" si="28">MONTH(A732)</f>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F732" s="5" t="str">
-        <f t="shared" ref="F729:F791" si="29">B732&amp;C732&amp;E732&amp;D732</f>
-        <v>1</v>
-      </c>
-      <c r="G732" s="6"/>
+        <f t="shared" si="19"/>
+        <v>美容室7実績</v>
+      </c>
+      <c r="G732" s="6">
+        <v>1400</v>
+      </c>
       <c r="H732" s="6"/>
     </row>
     <row r="733" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A733" s="7"/>
-      <c r="B733" s="5"/>
+      <c r="A733" s="7">
+        <v>46215</v>
+      </c>
+      <c r="B733" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C733" s="5"/>
-      <c r="D733" s="5"/>
+      <c r="D733" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E733" s="5">
-        <f t="shared" si="28"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F733" s="5" t="str">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="G733" s="6"/>
+        <f t="shared" si="19"/>
+        <v>美容室7実績</v>
+      </c>
+      <c r="G733" s="6">
+        <v>1400</v>
+      </c>
       <c r="H733" s="6"/>
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A734" s="7"/>
-      <c r="B734" s="5"/>
-      <c r="C734" s="5"/>
-      <c r="D734" s="5"/>
+      <c r="A734" s="7">
+        <v>46215</v>
+      </c>
+      <c r="B734" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C734" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D734" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E734" s="5">
-        <f t="shared" si="28"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F734" s="5" t="str">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="G734" s="6"/>
+        <f t="shared" si="19"/>
+        <v>服ゆっこ7実績</v>
+      </c>
+      <c r="G734" s="6">
+        <v>23100</v>
+      </c>
       <c r="H734" s="6"/>
     </row>
     <row r="735" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A735" s="7"/>
-      <c r="B735" s="5"/>
-      <c r="C735" s="5"/>
-      <c r="D735" s="5"/>
+      <c r="A735" s="7">
+        <v>46215</v>
+      </c>
+      <c r="B735" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D735" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E735" s="5">
-        <f t="shared" si="28"/>
-        <v>1</v>
+        <f t="shared" si="23"/>
+        <v>7</v>
       </c>
       <c r="F735" s="5" t="str">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="G735" s="6"/>
-      <c r="H735" s="6"/>
+        <f t="shared" si="19"/>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G735" s="6">
+        <v>5918</v>
+      </c>
+      <c r="H735" s="6" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A736" s="7"/>
@@ -22381,11 +22376,11 @@
       <c r="C736" s="5"/>
       <c r="D736" s="5"/>
       <c r="E736" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E732:E791" si="26">MONTH(A736)</f>
         <v>1</v>
       </c>
       <c r="F736" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="F732:F791" si="27">B736&amp;C736&amp;E736&amp;D736</f>
         <v>1</v>
       </c>
       <c r="G736" s="6"/>
@@ -22397,11 +22392,11 @@
       <c r="C737" s="5"/>
       <c r="D737" s="5"/>
       <c r="E737" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F737" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G737" s="6"/>
@@ -22413,11 +22408,11 @@
       <c r="C738" s="5"/>
       <c r="D738" s="5"/>
       <c r="E738" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F738" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G738" s="6"/>
@@ -22429,11 +22424,11 @@
       <c r="C739" s="5"/>
       <c r="D739" s="5"/>
       <c r="E739" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F739" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G739" s="6"/>
@@ -22445,11 +22440,11 @@
       <c r="C740" s="5"/>
       <c r="D740" s="5"/>
       <c r="E740" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F740" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G740" s="6"/>
@@ -22461,11 +22456,11 @@
       <c r="C741" s="5"/>
       <c r="D741" s="5"/>
       <c r="E741" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F741" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G741" s="6"/>
@@ -22477,11 +22472,11 @@
       <c r="C742" s="5"/>
       <c r="D742" s="5"/>
       <c r="E742" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F742" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G742" s="6"/>
@@ -22493,11 +22488,11 @@
       <c r="C743" s="5"/>
       <c r="D743" s="5"/>
       <c r="E743" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F743" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G743" s="6"/>
@@ -22509,11 +22504,11 @@
       <c r="C744" s="5"/>
       <c r="D744" s="5"/>
       <c r="E744" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F744" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G744" s="6"/>
@@ -22525,11 +22520,11 @@
       <c r="C745" s="5"/>
       <c r="D745" s="5"/>
       <c r="E745" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F745" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G745" s="6"/>
@@ -22541,11 +22536,11 @@
       <c r="C746" s="5"/>
       <c r="D746" s="5"/>
       <c r="E746" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F746" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G746" s="6"/>
@@ -22557,11 +22552,11 @@
       <c r="C747" s="5"/>
       <c r="D747" s="5"/>
       <c r="E747" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F747" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G747" s="6"/>
@@ -22573,11 +22568,11 @@
       <c r="C748" s="5"/>
       <c r="D748" s="5"/>
       <c r="E748" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F748" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G748" s="6"/>
@@ -22589,11 +22584,11 @@
       <c r="C749" s="5"/>
       <c r="D749" s="5"/>
       <c r="E749" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F749" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G749" s="6"/>
@@ -22605,11 +22600,11 @@
       <c r="C750" s="5"/>
       <c r="D750" s="5"/>
       <c r="E750" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F750" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G750" s="6"/>
@@ -22621,11 +22616,11 @@
       <c r="C751" s="5"/>
       <c r="D751" s="5"/>
       <c r="E751" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F751" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G751" s="6"/>
@@ -22637,11 +22632,11 @@
       <c r="C752" s="5"/>
       <c r="D752" s="5"/>
       <c r="E752" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F752" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G752" s="6"/>
@@ -22653,11 +22648,11 @@
       <c r="C753" s="5"/>
       <c r="D753" s="5"/>
       <c r="E753" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F753" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G753" s="6"/>
@@ -22669,11 +22664,11 @@
       <c r="C754" s="5"/>
       <c r="D754" s="5"/>
       <c r="E754" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F754" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G754" s="6"/>
@@ -22685,11 +22680,11 @@
       <c r="C755" s="5"/>
       <c r="D755" s="5"/>
       <c r="E755" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F755" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G755" s="6"/>
@@ -22701,11 +22696,11 @@
       <c r="C756" s="5"/>
       <c r="D756" s="5"/>
       <c r="E756" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F756" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G756" s="6"/>
@@ -22717,11 +22712,11 @@
       <c r="C757" s="5"/>
       <c r="D757" s="5"/>
       <c r="E757" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F757" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G757" s="6"/>
@@ -22733,11 +22728,11 @@
       <c r="C758" s="5"/>
       <c r="D758" s="5"/>
       <c r="E758" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F758" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G758" s="6"/>
@@ -22749,11 +22744,11 @@
       <c r="C759" s="5"/>
       <c r="D759" s="5"/>
       <c r="E759" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F759" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G759" s="6"/>
@@ -22765,11 +22760,11 @@
       <c r="C760" s="5"/>
       <c r="D760" s="5"/>
       <c r="E760" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F760" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G760" s="6"/>
@@ -22781,11 +22776,11 @@
       <c r="C761" s="5"/>
       <c r="D761" s="5"/>
       <c r="E761" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F761" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G761" s="6"/>
@@ -22797,11 +22792,11 @@
       <c r="C762" s="5"/>
       <c r="D762" s="5"/>
       <c r="E762" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F762" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G762" s="6"/>
@@ -22813,11 +22808,11 @@
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F763" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G763" s="6"/>
@@ -22829,11 +22824,11 @@
       <c r="C764" s="5"/>
       <c r="D764" s="5"/>
       <c r="E764" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F764" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G764" s="6"/>
@@ -22845,11 +22840,11 @@
       <c r="C765" s="5"/>
       <c r="D765" s="5"/>
       <c r="E765" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F765" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G765" s="6"/>
@@ -22861,11 +22856,11 @@
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F766" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G766" s="6"/>
@@ -22877,11 +22872,11 @@
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F767" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G767" s="6"/>
@@ -22893,11 +22888,11 @@
       <c r="C768" s="5"/>
       <c r="D768" s="5"/>
       <c r="E768" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F768" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G768" s="6"/>
@@ -22909,11 +22904,11 @@
       <c r="C769" s="5"/>
       <c r="D769" s="5"/>
       <c r="E769" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F769" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G769" s="6"/>
@@ -22925,11 +22920,11 @@
       <c r="C770" s="5"/>
       <c r="D770" s="5"/>
       <c r="E770" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F770" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G770" s="6"/>
@@ -22941,11 +22936,11 @@
       <c r="C771" s="5"/>
       <c r="D771" s="5"/>
       <c r="E771" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F771" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G771" s="6"/>
@@ -22957,11 +22952,11 @@
       <c r="C772" s="5"/>
       <c r="D772" s="5"/>
       <c r="E772" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F772" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G772" s="6"/>
@@ -22973,11 +22968,11 @@
       <c r="C773" s="5"/>
       <c r="D773" s="5"/>
       <c r="E773" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F773" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G773" s="6"/>
@@ -22989,11 +22984,11 @@
       <c r="C774" s="5"/>
       <c r="D774" s="5"/>
       <c r="E774" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F774" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G774" s="6"/>
@@ -23005,11 +23000,11 @@
       <c r="C775" s="5"/>
       <c r="D775" s="5"/>
       <c r="E775" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F775" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G775" s="6"/>
@@ -23021,11 +23016,11 @@
       <c r="C776" s="5"/>
       <c r="D776" s="5"/>
       <c r="E776" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F776" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G776" s="6"/>
@@ -23037,11 +23032,11 @@
       <c r="C777" s="5"/>
       <c r="D777" s="5"/>
       <c r="E777" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F777" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G777" s="6"/>
@@ -23053,11 +23048,11 @@
       <c r="C778" s="5"/>
       <c r="D778" s="5"/>
       <c r="E778" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F778" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G778" s="6"/>
@@ -23069,11 +23064,11 @@
       <c r="C779" s="5"/>
       <c r="D779" s="5"/>
       <c r="E779" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F779" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G779" s="6"/>
@@ -23085,11 +23080,11 @@
       <c r="C780" s="5"/>
       <c r="D780" s="5"/>
       <c r="E780" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F780" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G780" s="6"/>
@@ -23101,11 +23096,11 @@
       <c r="C781" s="5"/>
       <c r="D781" s="5"/>
       <c r="E781" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F781" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G781" s="6"/>
@@ -23117,11 +23112,11 @@
       <c r="C782" s="5"/>
       <c r="D782" s="5"/>
       <c r="E782" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F782" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G782" s="6"/>
@@ -23133,11 +23128,11 @@
       <c r="C783" s="5"/>
       <c r="D783" s="5"/>
       <c r="E783" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F783" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G783" s="6"/>
@@ -23149,11 +23144,11 @@
       <c r="C784" s="5"/>
       <c r="D784" s="5"/>
       <c r="E784" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F784" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G784" s="6"/>
@@ -23165,11 +23160,11 @@
       <c r="C785" s="5"/>
       <c r="D785" s="5"/>
       <c r="E785" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F785" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G785" s="6"/>
@@ -23181,11 +23176,11 @@
       <c r="C786" s="5"/>
       <c r="D786" s="5"/>
       <c r="E786" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F786" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G786" s="6"/>
@@ -23197,11 +23192,11 @@
       <c r="C787" s="5"/>
       <c r="D787" s="5"/>
       <c r="E787" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F787" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G787" s="6"/>
@@ -23213,11 +23208,11 @@
       <c r="C788" s="5"/>
       <c r="D788" s="5"/>
       <c r="E788" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F788" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G788" s="6"/>
@@ -23229,11 +23224,11 @@
       <c r="C789" s="5"/>
       <c r="D789" s="5"/>
       <c r="E789" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F789" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G789" s="6"/>
@@ -23245,11 +23240,11 @@
       <c r="C790" s="5"/>
       <c r="D790" s="5"/>
       <c r="E790" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F790" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G790" s="6"/>
@@ -23261,11 +23256,11 @@
       <c r="C791" s="5"/>
       <c r="D791" s="5"/>
       <c r="E791" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="F791" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="G791" s="6"/>
@@ -23277,11 +23272,11 @@
       <c r="C792" s="5"/>
       <c r="D792" s="5"/>
       <c r="E792" s="5">
-        <f t="shared" ref="E792:E855" si="30">MONTH(A792)</f>
+        <f t="shared" ref="E792:E855" si="28">MONTH(A792)</f>
         <v>1</v>
       </c>
       <c r="F792" s="5" t="str">
-        <f t="shared" ref="F792:F855" si="31">B792&amp;C792&amp;E792&amp;D792</f>
+        <f t="shared" ref="F792:F855" si="29">B792&amp;C792&amp;E792&amp;D792</f>
         <v>1</v>
       </c>
       <c r="G792" s="6"/>
@@ -23293,11 +23288,11 @@
       <c r="C793" s="5"/>
       <c r="D793" s="5"/>
       <c r="E793" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F793" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G793" s="6"/>
@@ -23309,11 +23304,11 @@
       <c r="C794" s="5"/>
       <c r="D794" s="5"/>
       <c r="E794" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F794" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G794" s="6"/>
@@ -23325,11 +23320,11 @@
       <c r="C795" s="5"/>
       <c r="D795" s="5"/>
       <c r="E795" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F795" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G795" s="6"/>
@@ -23341,11 +23336,11 @@
       <c r="C796" s="5"/>
       <c r="D796" s="5"/>
       <c r="E796" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F796" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G796" s="6"/>
@@ -23357,11 +23352,11 @@
       <c r="C797" s="5"/>
       <c r="D797" s="5"/>
       <c r="E797" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F797" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G797" s="6"/>
@@ -23373,11 +23368,11 @@
       <c r="C798" s="5"/>
       <c r="D798" s="5"/>
       <c r="E798" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F798" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G798" s="6"/>
@@ -23389,11 +23384,11 @@
       <c r="C799" s="5"/>
       <c r="D799" s="5"/>
       <c r="E799" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F799" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G799" s="6"/>
@@ -23405,11 +23400,11 @@
       <c r="C800" s="5"/>
       <c r="D800" s="5"/>
       <c r="E800" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F800" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G800" s="6"/>
@@ -23421,11 +23416,11 @@
       <c r="C801" s="5"/>
       <c r="D801" s="5"/>
       <c r="E801" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F801" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G801" s="6"/>
@@ -23437,11 +23432,11 @@
       <c r="C802" s="5"/>
       <c r="D802" s="5"/>
       <c r="E802" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F802" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G802" s="6"/>
@@ -23453,11 +23448,11 @@
       <c r="C803" s="5"/>
       <c r="D803" s="5"/>
       <c r="E803" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F803" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G803" s="6"/>
@@ -23469,11 +23464,11 @@
       <c r="C804" s="5"/>
       <c r="D804" s="5"/>
       <c r="E804" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F804" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G804" s="6"/>
@@ -23485,11 +23480,11 @@
       <c r="C805" s="5"/>
       <c r="D805" s="5"/>
       <c r="E805" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F805" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G805" s="6"/>
@@ -23501,11 +23496,11 @@
       <c r="C806" s="5"/>
       <c r="D806" s="5"/>
       <c r="E806" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F806" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G806" s="6"/>
@@ -23517,11 +23512,11 @@
       <c r="C807" s="5"/>
       <c r="D807" s="5"/>
       <c r="E807" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F807" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G807" s="6"/>
@@ -23533,11 +23528,11 @@
       <c r="C808" s="5"/>
       <c r="D808" s="5"/>
       <c r="E808" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F808" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G808" s="6"/>
@@ -23549,11 +23544,11 @@
       <c r="C809" s="5"/>
       <c r="D809" s="5"/>
       <c r="E809" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F809" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G809" s="6"/>
@@ -23565,11 +23560,11 @@
       <c r="C810" s="5"/>
       <c r="D810" s="5"/>
       <c r="E810" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F810" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G810" s="6"/>
@@ -23581,11 +23576,11 @@
       <c r="C811" s="5"/>
       <c r="D811" s="5"/>
       <c r="E811" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F811" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G811" s="6"/>
@@ -23597,11 +23592,11 @@
       <c r="C812" s="5"/>
       <c r="D812" s="5"/>
       <c r="E812" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F812" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G812" s="6"/>
@@ -23613,11 +23608,11 @@
       <c r="C813" s="5"/>
       <c r="D813" s="5"/>
       <c r="E813" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F813" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G813" s="6"/>
@@ -23629,11 +23624,11 @@
       <c r="C814" s="5"/>
       <c r="D814" s="5"/>
       <c r="E814" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F814" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G814" s="6"/>
@@ -23645,11 +23640,11 @@
       <c r="C815" s="5"/>
       <c r="D815" s="5"/>
       <c r="E815" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F815" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G815" s="6"/>
@@ -23661,11 +23656,11 @@
       <c r="C816" s="5"/>
       <c r="D816" s="5"/>
       <c r="E816" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F816" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G816" s="6"/>
@@ -23677,11 +23672,11 @@
       <c r="C817" s="5"/>
       <c r="D817" s="5"/>
       <c r="E817" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F817" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G817" s="6"/>
@@ -23693,11 +23688,11 @@
       <c r="C818" s="5"/>
       <c r="D818" s="5"/>
       <c r="E818" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F818" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G818" s="6"/>
@@ -23709,11 +23704,11 @@
       <c r="C819" s="5"/>
       <c r="D819" s="5"/>
       <c r="E819" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F819" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G819" s="6"/>
@@ -23725,11 +23720,11 @@
       <c r="C820" s="5"/>
       <c r="D820" s="5"/>
       <c r="E820" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F820" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G820" s="6"/>
@@ -23741,11 +23736,11 @@
       <c r="C821" s="5"/>
       <c r="D821" s="5"/>
       <c r="E821" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F821" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G821" s="6"/>
@@ -23757,11 +23752,11 @@
       <c r="C822" s="5"/>
       <c r="D822" s="5"/>
       <c r="E822" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F822" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G822" s="6"/>
@@ -23773,11 +23768,11 @@
       <c r="C823" s="5"/>
       <c r="D823" s="5"/>
       <c r="E823" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F823" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G823" s="6"/>
@@ -23789,11 +23784,11 @@
       <c r="C824" s="5"/>
       <c r="D824" s="5"/>
       <c r="E824" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F824" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G824" s="6"/>
@@ -23805,11 +23800,11 @@
       <c r="C825" s="5"/>
       <c r="D825" s="5"/>
       <c r="E825" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F825" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G825" s="6"/>
@@ -23821,11 +23816,11 @@
       <c r="C826" s="5"/>
       <c r="D826" s="5"/>
       <c r="E826" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F826" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G826" s="6"/>
@@ -23837,11 +23832,11 @@
       <c r="C827" s="5"/>
       <c r="D827" s="5"/>
       <c r="E827" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F827" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G827" s="6"/>
@@ -23853,11 +23848,11 @@
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F828" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G828" s="6"/>
@@ -23869,11 +23864,11 @@
       <c r="C829" s="5"/>
       <c r="D829" s="5"/>
       <c r="E829" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F829" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G829" s="6"/>
@@ -23885,11 +23880,11 @@
       <c r="C830" s="5"/>
       <c r="D830" s="5"/>
       <c r="E830" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F830" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G830" s="6"/>
@@ -23901,11 +23896,11 @@
       <c r="C831" s="5"/>
       <c r="D831" s="5"/>
       <c r="E831" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F831" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G831" s="6"/>
@@ -23917,11 +23912,11 @@
       <c r="C832" s="5"/>
       <c r="D832" s="5"/>
       <c r="E832" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F832" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G832" s="6"/>
@@ -23933,11 +23928,11 @@
       <c r="C833" s="5"/>
       <c r="D833" s="5"/>
       <c r="E833" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F833" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G833" s="6"/>
@@ -23949,11 +23944,11 @@
       <c r="C834" s="5"/>
       <c r="D834" s="5"/>
       <c r="E834" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F834" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G834" s="6"/>
@@ -23965,11 +23960,11 @@
       <c r="C835" s="5"/>
       <c r="D835" s="5"/>
       <c r="E835" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F835" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G835" s="6"/>
@@ -23981,11 +23976,11 @@
       <c r="C836" s="5"/>
       <c r="D836" s="5"/>
       <c r="E836" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F836" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G836" s="6"/>
@@ -23997,11 +23992,11 @@
       <c r="C837" s="5"/>
       <c r="D837" s="5"/>
       <c r="E837" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F837" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G837" s="6"/>
@@ -24013,11 +24008,11 @@
       <c r="C838" s="5"/>
       <c r="D838" s="5"/>
       <c r="E838" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F838" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G838" s="6"/>
@@ -24029,11 +24024,11 @@
       <c r="C839" s="5"/>
       <c r="D839" s="5"/>
       <c r="E839" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F839" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G839" s="6"/>
@@ -24045,11 +24040,11 @@
       <c r="C840" s="5"/>
       <c r="D840" s="5"/>
       <c r="E840" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F840" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G840" s="6"/>
@@ -24061,11 +24056,11 @@
       <c r="C841" s="5"/>
       <c r="D841" s="5"/>
       <c r="E841" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F841" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G841" s="6"/>
@@ -24077,11 +24072,11 @@
       <c r="C842" s="5"/>
       <c r="D842" s="5"/>
       <c r="E842" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F842" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G842" s="6"/>
@@ -24093,11 +24088,11 @@
       <c r="C843" s="5"/>
       <c r="D843" s="5"/>
       <c r="E843" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F843" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G843" s="6"/>
@@ -24109,11 +24104,11 @@
       <c r="C844" s="5"/>
       <c r="D844" s="5"/>
       <c r="E844" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F844" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G844" s="6"/>
@@ -24125,11 +24120,11 @@
       <c r="C845" s="5"/>
       <c r="D845" s="5"/>
       <c r="E845" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F845" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G845" s="6"/>
@@ -24141,11 +24136,11 @@
       <c r="C846" s="5"/>
       <c r="D846" s="5"/>
       <c r="E846" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F846" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G846" s="6"/>
@@ -24157,11 +24152,11 @@
       <c r="C847" s="5"/>
       <c r="D847" s="5"/>
       <c r="E847" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F847" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G847" s="6"/>
@@ -24173,11 +24168,11 @@
       <c r="C848" s="5"/>
       <c r="D848" s="5"/>
       <c r="E848" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F848" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G848" s="6"/>
@@ -24189,11 +24184,11 @@
       <c r="C849" s="5"/>
       <c r="D849" s="5"/>
       <c r="E849" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F849" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G849" s="6"/>
@@ -24205,11 +24200,11 @@
       <c r="C850" s="5"/>
       <c r="D850" s="5"/>
       <c r="E850" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F850" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G850" s="6"/>
@@ -24221,11 +24216,11 @@
       <c r="C851" s="5"/>
       <c r="D851" s="5"/>
       <c r="E851" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F851" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G851" s="6"/>
@@ -24237,11 +24232,11 @@
       <c r="C852" s="5"/>
       <c r="D852" s="5"/>
       <c r="E852" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F852" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G852" s="6"/>
@@ -24253,11 +24248,11 @@
       <c r="C853" s="5"/>
       <c r="D853" s="5"/>
       <c r="E853" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F853" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G853" s="6"/>
@@ -24269,11 +24264,11 @@
       <c r="C854" s="5"/>
       <c r="D854" s="5"/>
       <c r="E854" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F854" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G854" s="6"/>
@@ -24285,11 +24280,11 @@
       <c r="C855" s="5"/>
       <c r="D855" s="5"/>
       <c r="E855" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="F855" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="G855" s="6"/>
@@ -24301,11 +24296,11 @@
       <c r="C856" s="5"/>
       <c r="D856" s="5"/>
       <c r="E856" s="5">
-        <f t="shared" ref="E856:E919" si="32">MONTH(A856)</f>
+        <f t="shared" ref="E856:E919" si="30">MONTH(A856)</f>
         <v>1</v>
       </c>
       <c r="F856" s="5" t="str">
-        <f t="shared" ref="F856:F919" si="33">B856&amp;C856&amp;E856&amp;D856</f>
+        <f t="shared" ref="F856:F919" si="31">B856&amp;C856&amp;E856&amp;D856</f>
         <v>1</v>
       </c>
       <c r="G856" s="6"/>
@@ -24317,11 +24312,11 @@
       <c r="C857" s="5"/>
       <c r="D857" s="5"/>
       <c r="E857" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F857" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G857" s="6"/>
@@ -24333,11 +24328,11 @@
       <c r="C858" s="5"/>
       <c r="D858" s="5"/>
       <c r="E858" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F858" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G858" s="6"/>
@@ -24349,11 +24344,11 @@
       <c r="C859" s="5"/>
       <c r="D859" s="5"/>
       <c r="E859" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F859" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G859" s="6"/>
@@ -24365,11 +24360,11 @@
       <c r="C860" s="5"/>
       <c r="D860" s="5"/>
       <c r="E860" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F860" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G860" s="6"/>
@@ -24381,11 +24376,11 @@
       <c r="C861" s="5"/>
       <c r="D861" s="5"/>
       <c r="E861" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F861" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G861" s="6"/>
@@ -24397,11 +24392,11 @@
       <c r="C862" s="5"/>
       <c r="D862" s="5"/>
       <c r="E862" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F862" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G862" s="6"/>
@@ -24413,11 +24408,11 @@
       <c r="C863" s="5"/>
       <c r="D863" s="5"/>
       <c r="E863" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F863" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G863" s="6"/>
@@ -24429,11 +24424,11 @@
       <c r="C864" s="5"/>
       <c r="D864" s="5"/>
       <c r="E864" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F864" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G864" s="6"/>
@@ -24445,11 +24440,11 @@
       <c r="C865" s="5"/>
       <c r="D865" s="5"/>
       <c r="E865" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F865" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G865" s="6"/>
@@ -24461,11 +24456,11 @@
       <c r="C866" s="5"/>
       <c r="D866" s="5"/>
       <c r="E866" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F866" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G866" s="6"/>
@@ -24477,11 +24472,11 @@
       <c r="C867" s="5"/>
       <c r="D867" s="5"/>
       <c r="E867" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F867" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G867" s="6"/>
@@ -24493,11 +24488,11 @@
       <c r="C868" s="5"/>
       <c r="D868" s="5"/>
       <c r="E868" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F868" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G868" s="6"/>
@@ -24509,11 +24504,11 @@
       <c r="C869" s="5"/>
       <c r="D869" s="5"/>
       <c r="E869" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F869" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G869" s="6"/>
@@ -24525,11 +24520,11 @@
       <c r="C870" s="5"/>
       <c r="D870" s="5"/>
       <c r="E870" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F870" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G870" s="6"/>
@@ -24541,11 +24536,11 @@
       <c r="C871" s="5"/>
       <c r="D871" s="5"/>
       <c r="E871" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F871" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G871" s="6"/>
@@ -24557,11 +24552,11 @@
       <c r="C872" s="5"/>
       <c r="D872" s="5"/>
       <c r="E872" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F872" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G872" s="6"/>
@@ -24573,11 +24568,11 @@
       <c r="C873" s="5"/>
       <c r="D873" s="5"/>
       <c r="E873" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F873" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G873" s="6"/>
@@ -24589,11 +24584,11 @@
       <c r="C874" s="5"/>
       <c r="D874" s="5"/>
       <c r="E874" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F874" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G874" s="6"/>
@@ -24605,11 +24600,11 @@
       <c r="C875" s="5"/>
       <c r="D875" s="5"/>
       <c r="E875" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F875" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G875" s="6"/>
@@ -24621,11 +24616,11 @@
       <c r="C876" s="5"/>
       <c r="D876" s="5"/>
       <c r="E876" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F876" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G876" s="6"/>
@@ -24637,11 +24632,11 @@
       <c r="C877" s="5"/>
       <c r="D877" s="5"/>
       <c r="E877" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F877" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G877" s="6"/>
@@ -24653,11 +24648,11 @@
       <c r="C878" s="5"/>
       <c r="D878" s="5"/>
       <c r="E878" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F878" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G878" s="6"/>
@@ -24669,11 +24664,11 @@
       <c r="C879" s="5"/>
       <c r="D879" s="5"/>
       <c r="E879" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F879" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G879" s="6"/>
@@ -24685,11 +24680,11 @@
       <c r="C880" s="5"/>
       <c r="D880" s="5"/>
       <c r="E880" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F880" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G880" s="6"/>
@@ -24701,11 +24696,11 @@
       <c r="C881" s="5"/>
       <c r="D881" s="5"/>
       <c r="E881" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F881" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G881" s="6"/>
@@ -24717,11 +24712,11 @@
       <c r="C882" s="5"/>
       <c r="D882" s="5"/>
       <c r="E882" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F882" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G882" s="6"/>
@@ -24733,11 +24728,11 @@
       <c r="C883" s="5"/>
       <c r="D883" s="5"/>
       <c r="E883" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F883" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G883" s="6"/>
@@ -24749,11 +24744,11 @@
       <c r="C884" s="5"/>
       <c r="D884" s="5"/>
       <c r="E884" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F884" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G884" s="6"/>
@@ -24765,11 +24760,11 @@
       <c r="C885" s="5"/>
       <c r="D885" s="5"/>
       <c r="E885" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F885" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G885" s="6"/>
@@ -24781,11 +24776,11 @@
       <c r="C886" s="5"/>
       <c r="D886" s="5"/>
       <c r="E886" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F886" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G886" s="6"/>
@@ -24797,11 +24792,11 @@
       <c r="C887" s="5"/>
       <c r="D887" s="5"/>
       <c r="E887" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F887" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G887" s="6"/>
@@ -24813,11 +24808,11 @@
       <c r="C888" s="5"/>
       <c r="D888" s="5"/>
       <c r="E888" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F888" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G888" s="6"/>
@@ -24829,11 +24824,11 @@
       <c r="C889" s="5"/>
       <c r="D889" s="5"/>
       <c r="E889" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F889" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G889" s="6"/>
@@ -24845,11 +24840,11 @@
       <c r="C890" s="5"/>
       <c r="D890" s="5"/>
       <c r="E890" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F890" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G890" s="6"/>
@@ -24861,11 +24856,11 @@
       <c r="C891" s="5"/>
       <c r="D891" s="5"/>
       <c r="E891" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F891" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G891" s="6"/>
@@ -24877,11 +24872,11 @@
       <c r="C892" s="5"/>
       <c r="D892" s="5"/>
       <c r="E892" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F892" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G892" s="6"/>
@@ -24893,11 +24888,11 @@
       <c r="C893" s="5"/>
       <c r="D893" s="5"/>
       <c r="E893" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F893" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G893" s="6"/>
@@ -24909,11 +24904,11 @@
       <c r="C894" s="5"/>
       <c r="D894" s="5"/>
       <c r="E894" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F894" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G894" s="6"/>
@@ -24925,11 +24920,11 @@
       <c r="C895" s="5"/>
       <c r="D895" s="5"/>
       <c r="E895" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F895" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G895" s="6"/>
@@ -24941,11 +24936,11 @@
       <c r="C896" s="5"/>
       <c r="D896" s="5"/>
       <c r="E896" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F896" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G896" s="6"/>
@@ -24957,11 +24952,11 @@
       <c r="C897" s="5"/>
       <c r="D897" s="5"/>
       <c r="E897" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F897" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G897" s="6"/>
@@ -24973,11 +24968,11 @@
       <c r="C898" s="5"/>
       <c r="D898" s="5"/>
       <c r="E898" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F898" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G898" s="6"/>
@@ -24989,11 +24984,11 @@
       <c r="C899" s="5"/>
       <c r="D899" s="5"/>
       <c r="E899" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F899" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G899" s="6"/>
@@ -25005,11 +25000,11 @@
       <c r="C900" s="5"/>
       <c r="D900" s="5"/>
       <c r="E900" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F900" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G900" s="6"/>
@@ -25021,11 +25016,11 @@
       <c r="C901" s="5"/>
       <c r="D901" s="5"/>
       <c r="E901" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F901" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G901" s="6"/>
@@ -25037,11 +25032,11 @@
       <c r="C902" s="5"/>
       <c r="D902" s="5"/>
       <c r="E902" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F902" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G902" s="6"/>
@@ -25053,11 +25048,11 @@
       <c r="C903" s="5"/>
       <c r="D903" s="5"/>
       <c r="E903" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F903" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G903" s="6"/>
@@ -25069,11 +25064,11 @@
       <c r="C904" s="5"/>
       <c r="D904" s="5"/>
       <c r="E904" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F904" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G904" s="6"/>
@@ -25085,11 +25080,11 @@
       <c r="C905" s="5"/>
       <c r="D905" s="5"/>
       <c r="E905" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F905" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G905" s="6"/>
@@ -25101,11 +25096,11 @@
       <c r="C906" s="5"/>
       <c r="D906" s="5"/>
       <c r="E906" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F906" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G906" s="6"/>
@@ -25117,11 +25112,11 @@
       <c r="C907" s="5"/>
       <c r="D907" s="5"/>
       <c r="E907" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F907" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G907" s="6"/>
@@ -25133,11 +25128,11 @@
       <c r="C908" s="5"/>
       <c r="D908" s="5"/>
       <c r="E908" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F908" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G908" s="6"/>
@@ -25149,11 +25144,11 @@
       <c r="C909" s="5"/>
       <c r="D909" s="5"/>
       <c r="E909" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F909" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G909" s="6"/>
@@ -25165,11 +25160,11 @@
       <c r="C910" s="5"/>
       <c r="D910" s="5"/>
       <c r="E910" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F910" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G910" s="6"/>
@@ -25181,11 +25176,11 @@
       <c r="C911" s="5"/>
       <c r="D911" s="5"/>
       <c r="E911" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F911" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G911" s="6"/>
@@ -25197,11 +25192,11 @@
       <c r="C912" s="5"/>
       <c r="D912" s="5"/>
       <c r="E912" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F912" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G912" s="6"/>
@@ -25213,11 +25208,11 @@
       <c r="C913" s="5"/>
       <c r="D913" s="5"/>
       <c r="E913" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F913" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G913" s="6"/>
@@ -25229,11 +25224,11 @@
       <c r="C914" s="5"/>
       <c r="D914" s="5"/>
       <c r="E914" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F914" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G914" s="6"/>
@@ -25245,11 +25240,11 @@
       <c r="C915" s="5"/>
       <c r="D915" s="5"/>
       <c r="E915" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F915" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G915" s="6"/>
@@ -25261,11 +25256,11 @@
       <c r="C916" s="5"/>
       <c r="D916" s="5"/>
       <c r="E916" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F916" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G916" s="6"/>
@@ -25277,11 +25272,11 @@
       <c r="C917" s="5"/>
       <c r="D917" s="5"/>
       <c r="E917" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F917" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G917" s="6"/>
@@ -25293,11 +25288,11 @@
       <c r="C918" s="5"/>
       <c r="D918" s="5"/>
       <c r="E918" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F918" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G918" s="6"/>
@@ -25309,11 +25304,11 @@
       <c r="C919" s="5"/>
       <c r="D919" s="5"/>
       <c r="E919" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="F919" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="G919" s="6"/>
@@ -25325,11 +25320,11 @@
       <c r="C920" s="5"/>
       <c r="D920" s="5"/>
       <c r="E920" s="5">
-        <f t="shared" ref="E920:E940" si="34">MONTH(A920)</f>
+        <f t="shared" ref="E920:E940" si="32">MONTH(A920)</f>
         <v>1</v>
       </c>
       <c r="F920" s="5" t="str">
-        <f t="shared" ref="F920:F940" si="35">B920&amp;C920&amp;E920&amp;D920</f>
+        <f t="shared" ref="F920:F940" si="33">B920&amp;C920&amp;E920&amp;D920</f>
         <v>1</v>
       </c>
       <c r="G920" s="6"/>
@@ -25341,11 +25336,11 @@
       <c r="C921" s="5"/>
       <c r="D921" s="5"/>
       <c r="E921" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F921" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G921" s="6"/>
@@ -25357,11 +25352,11 @@
       <c r="C922" s="5"/>
       <c r="D922" s="5"/>
       <c r="E922" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F922" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G922" s="6"/>
@@ -25373,11 +25368,11 @@
       <c r="C923" s="5"/>
       <c r="D923" s="5"/>
       <c r="E923" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F923" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G923" s="6"/>
@@ -25389,11 +25384,11 @@
       <c r="C924" s="5"/>
       <c r="D924" s="5"/>
       <c r="E924" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F924" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G924" s="6"/>
@@ -25405,11 +25400,11 @@
       <c r="C925" s="5"/>
       <c r="D925" s="5"/>
       <c r="E925" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F925" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G925" s="6"/>
@@ -25421,11 +25416,11 @@
       <c r="C926" s="5"/>
       <c r="D926" s="5"/>
       <c r="E926" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F926" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G926" s="6"/>
@@ -25437,11 +25432,11 @@
       <c r="C927" s="5"/>
       <c r="D927" s="5"/>
       <c r="E927" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F927" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G927" s="6"/>
@@ -25453,11 +25448,11 @@
       <c r="C928" s="5"/>
       <c r="D928" s="5"/>
       <c r="E928" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F928" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G928" s="6"/>
@@ -25469,11 +25464,11 @@
       <c r="C929" s="5"/>
       <c r="D929" s="5"/>
       <c r="E929" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F929" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G929" s="6"/>
@@ -25485,11 +25480,11 @@
       <c r="C930" s="5"/>
       <c r="D930" s="5"/>
       <c r="E930" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F930" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G930" s="6"/>
@@ -25501,11 +25496,11 @@
       <c r="C931" s="5"/>
       <c r="D931" s="5"/>
       <c r="E931" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F931" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G931" s="6"/>
@@ -25517,11 +25512,11 @@
       <c r="C932" s="5"/>
       <c r="D932" s="5"/>
       <c r="E932" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F932" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G932" s="6"/>
@@ -25533,11 +25528,11 @@
       <c r="C933" s="5"/>
       <c r="D933" s="5"/>
       <c r="E933" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F933" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G933" s="6"/>
@@ -25549,11 +25544,11 @@
       <c r="C934" s="5"/>
       <c r="D934" s="5"/>
       <c r="E934" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F934" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G934" s="6"/>
@@ -25565,11 +25560,11 @@
       <c r="C935" s="5"/>
       <c r="D935" s="5"/>
       <c r="E935" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F935" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G935" s="6"/>
@@ -25581,11 +25576,11 @@
       <c r="C936" s="5"/>
       <c r="D936" s="5"/>
       <c r="E936" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F936" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G936" s="6"/>
@@ -25597,11 +25592,11 @@
       <c r="C937" s="5"/>
       <c r="D937" s="5"/>
       <c r="E937" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F937" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G937" s="6"/>
@@ -25613,11 +25608,11 @@
       <c r="C938" s="5"/>
       <c r="D938" s="5"/>
       <c r="E938" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F938" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G938" s="6"/>
@@ -25629,11 +25624,11 @@
       <c r="C939" s="5"/>
       <c r="D939" s="5"/>
       <c r="E939" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F939" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G939" s="6"/>
@@ -25645,11 +25640,11 @@
       <c r="C940" s="5"/>
       <c r="D940" s="5"/>
       <c r="E940" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="F940" s="5" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="G940" s="6"/>

--- a/cost_managemant.xlsx
+++ b/cost_managemant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8585bf5f6caa8491/Desktop/Python_dir/money_managemant/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88A56635-64A0-4F3B-99E7-E306275029D3}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{B01D6116-F4DB-46BB-862F-A034B8FD710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB441E08-1B73-4F2D-A83A-4D6D45006CC9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6E378B90-8636-4C18-97D1-3FA81C22362A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2515" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2579" uniqueCount="303">
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
@@ -2000,12 +2000,18 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2040,7 +2046,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2072,6 +2078,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2163,6 +2172,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11427,7 +11440,7 @@
         <v>9</v>
       </c>
       <c r="F333" s="5" t="str">
-        <f t="shared" ref="F333:F403" si="11">B333&amp;C333&amp;E333&amp;D333</f>
+        <f t="shared" ref="F333:F394" si="11">B333&amp;C333&amp;E333&amp;D333</f>
         <v>ふるさと納税-9予算</v>
       </c>
       <c r="G333" s="6">
@@ -22371,339 +22384,549 @@
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A736" s="7"/>
-      <c r="B736" s="5"/>
-      <c r="C736" s="5"/>
-      <c r="D736" s="5"/>
+      <c r="A736" s="7">
+        <v>46216</v>
+      </c>
+      <c r="B736" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C736" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D736" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E736" s="5">
-        <f t="shared" ref="E732:E791" si="26">MONTH(A736)</f>
-        <v>1</v>
+        <f t="shared" ref="E736:E759" si="26">MONTH(A736)</f>
+        <v>7</v>
       </c>
       <c r="F736" s="5" t="str">
-        <f t="shared" ref="F732:F791" si="27">B736&amp;C736&amp;E736&amp;D736</f>
-        <v>1</v>
-      </c>
-      <c r="G736" s="6"/>
+        <f t="shared" ref="F736:F759" si="27">B736&amp;C736&amp;E736&amp;D736</f>
+        <v>化粧品-7実績</v>
+      </c>
+      <c r="G736" s="6">
+        <v>1760</v>
+      </c>
       <c r="H736" s="6"/>
     </row>
     <row r="737" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A737" s="7"/>
-      <c r="B737" s="5"/>
-      <c r="C737" s="5"/>
-      <c r="D737" s="5"/>
+      <c r="A737" s="7">
+        <v>46217</v>
+      </c>
+      <c r="B737" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C737" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D737" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E737" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F737" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G737" s="6"/>
+        <v>医療費-7実績</v>
+      </c>
+      <c r="G737" s="6">
+        <v>200</v>
+      </c>
       <c r="H737" s="6"/>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A738" s="7"/>
-      <c r="B738" s="5"/>
-      <c r="C738" s="5"/>
-      <c r="D738" s="5"/>
+      <c r="A738" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B738" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C738" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D738" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E738" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F738" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G738" s="6"/>
+        <v>その他予備費7実績</v>
+      </c>
+      <c r="G738" s="6">
+        <v>11608</v>
+      </c>
       <c r="H738" s="6"/>
     </row>
     <row r="739" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A739" s="7"/>
-      <c r="B739" s="5"/>
-      <c r="C739" s="5"/>
-      <c r="D739" s="5"/>
+      <c r="A739" s="7">
+        <v>46221</v>
+      </c>
+      <c r="B739" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D739" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E739" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F739" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G739" s="6"/>
+        <v>医療費-7実績</v>
+      </c>
+      <c r="G739" s="6">
+        <v>400</v>
+      </c>
       <c r="H739" s="6"/>
     </row>
     <row r="740" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A740" s="7"/>
-      <c r="B740" s="5"/>
-      <c r="C740" s="5"/>
-      <c r="D740" s="5"/>
+      <c r="A740" s="7">
+        <v>46221</v>
+      </c>
+      <c r="B740" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C740" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D740" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E740" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F740" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G740" s="6"/>
-      <c r="H740" s="6"/>
+        <v>生活費外食7実績</v>
+      </c>
+      <c r="G740" s="6">
+        <v>1850</v>
+      </c>
+      <c r="H740" s="6" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A741" s="7"/>
-      <c r="B741" s="5"/>
-      <c r="C741" s="5"/>
-      <c r="D741" s="5"/>
+      <c r="A741" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B741" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D741" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E741" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F741" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G741" s="6"/>
+        <v>家賃-7実績</v>
+      </c>
+      <c r="G741" s="6">
+        <v>120829</v>
+      </c>
       <c r="H741" s="6"/>
     </row>
     <row r="742" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A742" s="7"/>
-      <c r="B742" s="5"/>
-      <c r="C742" s="5"/>
-      <c r="D742" s="5"/>
+      <c r="A742" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B742" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C742" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D742" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E742" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F742" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G742" s="6"/>
+        <v>生活費-7実績</v>
+      </c>
+      <c r="G742" s="11">
+        <v>108000</v>
+      </c>
       <c r="H742" s="6"/>
     </row>
     <row r="743" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A743" s="7"/>
-      <c r="B743" s="5"/>
-      <c r="C743" s="5"/>
-      <c r="D743" s="5"/>
+      <c r="A743" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B743" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D743" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E743" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F743" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G743" s="6"/>
+        <v>通信料ゆっこ7実績</v>
+      </c>
+      <c r="G743" s="11">
+        <v>2500</v>
+      </c>
       <c r="H743" s="6"/>
     </row>
     <row r="744" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A744" s="7"/>
-      <c r="B744" s="5"/>
-      <c r="C744" s="5"/>
-      <c r="D744" s="5"/>
+      <c r="A744" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B744" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C744" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D744" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E744" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F744" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G744" s="6"/>
+        <v>通信料りょう7実績</v>
+      </c>
+      <c r="G744" s="11">
+        <v>3500</v>
+      </c>
       <c r="H744" s="6"/>
     </row>
     <row r="745" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A745" s="7"/>
-      <c r="B745" s="5"/>
-      <c r="C745" s="5"/>
-      <c r="D745" s="5"/>
+      <c r="A745" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B745" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D745" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E745" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F745" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G745" s="6"/>
+        <v>サブスクiCloud7実績</v>
+      </c>
+      <c r="G745" s="6">
+        <v>450</v>
+      </c>
       <c r="H745" s="6"/>
     </row>
     <row r="746" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A746" s="7"/>
-      <c r="B746" s="5"/>
-      <c r="C746" s="5"/>
-      <c r="D746" s="5"/>
+      <c r="A746" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B746" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C746" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D746" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E746" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F746" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G746" s="6"/>
+        <v>習い事バレエ7実績</v>
+      </c>
+      <c r="G746" s="6">
+        <v>9020</v>
+      </c>
       <c r="H746" s="6"/>
     </row>
     <row r="747" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A747" s="7"/>
-      <c r="B747" s="5"/>
-      <c r="C747" s="5"/>
-      <c r="D747" s="5"/>
+      <c r="A747" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B747" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D747" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E747" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F747" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G747" s="6"/>
+        <v>習い事公文7実績</v>
+      </c>
+      <c r="G747" s="6">
+        <v>14960</v>
+      </c>
       <c r="H747" s="6"/>
     </row>
     <row r="748" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A748" s="7"/>
-      <c r="B748" s="5"/>
-      <c r="C748" s="5"/>
-      <c r="D748" s="5"/>
+      <c r="A748" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B748" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C748" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D748" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E748" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F748" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G748" s="6"/>
+        <v>その他NISA積み立て7実績</v>
+      </c>
+      <c r="G748" s="6">
+        <v>40000</v>
+      </c>
       <c r="H748" s="6"/>
     </row>
     <row r="749" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A749" s="7"/>
-      <c r="B749" s="5"/>
-      <c r="C749" s="5"/>
-      <c r="D749" s="5"/>
+      <c r="A749" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B749" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C749" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D749" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E749" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F749" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G749" s="6"/>
+        <v>保険ゆっこ医療7実績</v>
+      </c>
+      <c r="G749" s="6">
+        <v>2924</v>
+      </c>
       <c r="H749" s="6"/>
     </row>
     <row r="750" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A750" s="7"/>
-      <c r="B750" s="5"/>
-      <c r="C750" s="5"/>
-      <c r="D750" s="5"/>
+      <c r="A750" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B750" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C750" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D750" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E750" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F750" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G750" s="6"/>
+        <v>保険りょう死亡7実績</v>
+      </c>
+      <c r="G750" s="6">
+        <v>1780</v>
+      </c>
       <c r="H750" s="6"/>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A751" s="7"/>
-      <c r="B751" s="5"/>
-      <c r="C751" s="5"/>
-      <c r="D751" s="5"/>
+      <c r="A751" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B751" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D751" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E751" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F751" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G751" s="6"/>
+        <v>保険りょう医療7実績</v>
+      </c>
+      <c r="G751" s="6">
+        <v>2572</v>
+      </c>
       <c r="H751" s="6"/>
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A752" s="7"/>
-      <c r="B752" s="5"/>
-      <c r="C752" s="5"/>
-      <c r="D752" s="5"/>
+      <c r="A752" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B752" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C752" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D752" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E752" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F752" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G752" s="6"/>
+        <f>B752&amp;C752&amp;E752&amp;D752</f>
+        <v>こずかいゆっこ7実績</v>
+      </c>
+      <c r="G752" s="6">
+        <v>25000</v>
+      </c>
       <c r="H752" s="6"/>
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A753" s="7"/>
-      <c r="B753" s="5"/>
-      <c r="C753" s="5"/>
-      <c r="D753" s="5"/>
+      <c r="A753" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B753" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C753" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D753" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E753" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F753" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G753" s="6"/>
+        <f t="shared" ref="F753:F754" si="28">B753&amp;C753&amp;E753&amp;D753</f>
+        <v>こずかいりょう7実績</v>
+      </c>
+      <c r="G753" s="6">
+        <v>25000</v>
+      </c>
       <c r="H753" s="6"/>
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A754" s="7"/>
-      <c r="B754" s="5"/>
-      <c r="C754" s="5"/>
-      <c r="D754" s="5"/>
+      <c r="A754" s="7">
+        <v>46234</v>
+      </c>
+      <c r="B754" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C754" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D754" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E754" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F754" s="5" t="str">
-        <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G754" s="6"/>
+        <f t="shared" si="28"/>
+        <v>奨学金-7実績</v>
+      </c>
+      <c r="G754" s="6">
+        <v>10125</v>
+      </c>
       <c r="H754" s="6"/>
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A755" s="7"/>
-      <c r="B755" s="5"/>
-      <c r="C755" s="5"/>
-      <c r="D755" s="5"/>
+      <c r="A755" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B755" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C755" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D755" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E755" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F755" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G755" s="6"/>
+        <v>生活費外食7実績</v>
+      </c>
+      <c r="G755" s="11"/>
       <c r="H755" s="6"/>
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A756" s="7"/>
-      <c r="B756" s="5"/>
-      <c r="C756" s="5"/>
-      <c r="D756" s="5"/>
+      <c r="A756" s="7">
+        <v>46221</v>
+      </c>
+      <c r="B756" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C756" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D756" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="E756" s="5">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F756" s="5" t="str">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="G756" s="6"/>
+        <v>服ゆっこ7実績</v>
+      </c>
+      <c r="G756" s="6">
+        <v>20472</v>
+      </c>
       <c r="H756" s="6"/>
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.35">
@@ -22760,11 +22983,11 @@
       <c r="C760" s="5"/>
       <c r="D760" s="5"/>
       <c r="E760" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="E736:E791" si="29">MONTH(A760)</f>
         <v>1</v>
       </c>
       <c r="F760" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="F736:F791" si="30">B760&amp;C760&amp;E760&amp;D760</f>
         <v>1</v>
       </c>
       <c r="G760" s="6"/>
@@ -22776,11 +22999,11 @@
       <c r="C761" s="5"/>
       <c r="D761" s="5"/>
       <c r="E761" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F761" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G761" s="6"/>
@@ -22792,11 +23015,11 @@
       <c r="C762" s="5"/>
       <c r="D762" s="5"/>
       <c r="E762" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F762" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G762" s="6"/>
@@ -22808,11 +23031,11 @@
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F763" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G763" s="6"/>
@@ -22824,11 +23047,11 @@
       <c r="C764" s="5"/>
       <c r="D764" s="5"/>
       <c r="E764" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F764" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G764" s="6"/>
@@ -22840,11 +23063,11 @@
       <c r="C765" s="5"/>
       <c r="D765" s="5"/>
       <c r="E765" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F765" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G765" s="6"/>
@@ -22856,11 +23079,11 @@
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F766" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G766" s="6"/>
@@ -22872,11 +23095,11 @@
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F767" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G767" s="6"/>
@@ -22888,11 +23111,11 @@
       <c r="C768" s="5"/>
       <c r="D768" s="5"/>
       <c r="E768" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F768" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G768" s="6"/>
@@ -22904,11 +23127,11 @@
       <c r="C769" s="5"/>
       <c r="D769" s="5"/>
       <c r="E769" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F769" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G769" s="6"/>
@@ -22920,11 +23143,11 @@
       <c r="C770" s="5"/>
       <c r="D770" s="5"/>
       <c r="E770" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F770" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G770" s="6"/>
@@ -22936,11 +23159,11 @@
       <c r="C771" s="5"/>
       <c r="D771" s="5"/>
       <c r="E771" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F771" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G771" s="6"/>
@@ -22952,11 +23175,11 @@
       <c r="C772" s="5"/>
       <c r="D772" s="5"/>
       <c r="E772" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F772" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G772" s="6"/>
@@ -22968,11 +23191,11 @@
       <c r="C773" s="5"/>
       <c r="D773" s="5"/>
       <c r="E773" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F773" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G773" s="6"/>
@@ -22984,11 +23207,11 @@
       <c r="C774" s="5"/>
       <c r="D774" s="5"/>
       <c r="E774" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F774" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G774" s="6"/>
@@ -23000,11 +23223,11 @@
       <c r="C775" s="5"/>
       <c r="D775" s="5"/>
       <c r="E775" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F775" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G775" s="6"/>
@@ -23016,11 +23239,11 @@
       <c r="C776" s="5"/>
       <c r="D776" s="5"/>
       <c r="E776" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F776" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G776" s="6"/>
@@ -23032,11 +23255,11 @@
       <c r="C777" s="5"/>
       <c r="D777" s="5"/>
       <c r="E777" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F777" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G777" s="6"/>
@@ -23048,11 +23271,11 @@
       <c r="C778" s="5"/>
       <c r="D778" s="5"/>
       <c r="E778" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F778" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G778" s="6"/>
@@ -23064,11 +23287,11 @@
       <c r="C779" s="5"/>
       <c r="D779" s="5"/>
       <c r="E779" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F779" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G779" s="6"/>
@@ -23080,11 +23303,11 @@
       <c r="C780" s="5"/>
       <c r="D780" s="5"/>
       <c r="E780" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F780" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G780" s="6"/>
@@ -23096,11 +23319,11 @@
       <c r="C781" s="5"/>
       <c r="D781" s="5"/>
       <c r="E781" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F781" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G781" s="6"/>
@@ -23112,11 +23335,11 @@
       <c r="C782" s="5"/>
       <c r="D782" s="5"/>
       <c r="E782" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F782" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G782" s="6"/>
@@ -23128,11 +23351,11 @@
       <c r="C783" s="5"/>
       <c r="D783" s="5"/>
       <c r="E783" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F783" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G783" s="6"/>
@@ -23144,11 +23367,11 @@
       <c r="C784" s="5"/>
       <c r="D784" s="5"/>
       <c r="E784" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F784" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G784" s="6"/>
@@ -23160,11 +23383,11 @@
       <c r="C785" s="5"/>
       <c r="D785" s="5"/>
       <c r="E785" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F785" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G785" s="6"/>
@@ -23176,11 +23399,11 @@
       <c r="C786" s="5"/>
       <c r="D786" s="5"/>
       <c r="E786" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F786" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G786" s="6"/>
@@ -23192,11 +23415,11 @@
       <c r="C787" s="5"/>
       <c r="D787" s="5"/>
       <c r="E787" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F787" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G787" s="6"/>
@@ -23208,11 +23431,11 @@
       <c r="C788" s="5"/>
       <c r="D788" s="5"/>
       <c r="E788" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F788" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G788" s="6"/>
@@ -23224,11 +23447,11 @@
       <c r="C789" s="5"/>
       <c r="D789" s="5"/>
       <c r="E789" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F789" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G789" s="6"/>
@@ -23240,11 +23463,11 @@
       <c r="C790" s="5"/>
       <c r="D790" s="5"/>
       <c r="E790" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F790" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G790" s="6"/>
@@ -23256,11 +23479,11 @@
       <c r="C791" s="5"/>
       <c r="D791" s="5"/>
       <c r="E791" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="F791" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="G791" s="6"/>
@@ -23272,11 +23495,11 @@
       <c r="C792" s="5"/>
       <c r="D792" s="5"/>
       <c r="E792" s="5">
-        <f t="shared" ref="E792:E855" si="28">MONTH(A792)</f>
+        <f t="shared" ref="E792:E855" si="31">MONTH(A792)</f>
         <v>1</v>
       </c>
       <c r="F792" s="5" t="str">
-        <f t="shared" ref="F792:F855" si="29">B792&amp;C792&amp;E792&amp;D792</f>
+        <f t="shared" ref="F792:F855" si="32">B792&amp;C792&amp;E792&amp;D792</f>
         <v>1</v>
       </c>
       <c r="G792" s="6"/>
@@ -23288,11 +23511,11 @@
       <c r="C793" s="5"/>
       <c r="D793" s="5"/>
       <c r="E793" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F793" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G793" s="6"/>
@@ -23304,11 +23527,11 @@
       <c r="C794" s="5"/>
       <c r="D794" s="5"/>
       <c r="E794" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F794" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G794" s="6"/>
@@ -23320,11 +23543,11 @@
       <c r="C795" s="5"/>
       <c r="D795" s="5"/>
       <c r="E795" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F795" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G795" s="6"/>
@@ -23336,11 +23559,11 @@
       <c r="C796" s="5"/>
       <c r="D796" s="5"/>
       <c r="E796" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F796" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G796" s="6"/>
@@ -23352,11 +23575,11 @@
       <c r="C797" s="5"/>
       <c r="D797" s="5"/>
       <c r="E797" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F797" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G797" s="6"/>
@@ -23368,11 +23591,11 @@
       <c r="C798" s="5"/>
       <c r="D798" s="5"/>
       <c r="E798" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F798" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G798" s="6"/>
@@ -23384,11 +23607,11 @@
       <c r="C799" s="5"/>
       <c r="D799" s="5"/>
       <c r="E799" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F799" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G799" s="6"/>
@@ -23400,11 +23623,11 @@
       <c r="C800" s="5"/>
       <c r="D800" s="5"/>
       <c r="E800" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F800" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G800" s="6"/>
@@ -23416,11 +23639,11 @@
       <c r="C801" s="5"/>
       <c r="D801" s="5"/>
       <c r="E801" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F801" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G801" s="6"/>
@@ -23432,11 +23655,11 @@
       <c r="C802" s="5"/>
       <c r="D802" s="5"/>
       <c r="E802" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F802" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G802" s="6"/>
@@ -23448,11 +23671,11 @@
       <c r="C803" s="5"/>
       <c r="D803" s="5"/>
       <c r="E803" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F803" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G803" s="6"/>
@@ -23464,11 +23687,11 @@
       <c r="C804" s="5"/>
       <c r="D804" s="5"/>
       <c r="E804" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F804" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G804" s="6"/>
@@ -23480,11 +23703,11 @@
       <c r="C805" s="5"/>
       <c r="D805" s="5"/>
       <c r="E805" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F805" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G805" s="6"/>
@@ -23496,11 +23719,11 @@
       <c r="C806" s="5"/>
       <c r="D806" s="5"/>
       <c r="E806" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F806" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G806" s="6"/>
@@ -23512,11 +23735,11 @@
       <c r="C807" s="5"/>
       <c r="D807" s="5"/>
       <c r="E807" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F807" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G807" s="6"/>
@@ -23528,11 +23751,11 @@
       <c r="C808" s="5"/>
       <c r="D808" s="5"/>
       <c r="E808" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F808" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G808" s="6"/>
@@ -23544,11 +23767,11 @@
       <c r="C809" s="5"/>
       <c r="D809" s="5"/>
       <c r="E809" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F809" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G809" s="6"/>
@@ -23560,11 +23783,11 @@
       <c r="C810" s="5"/>
       <c r="D810" s="5"/>
       <c r="E810" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F810" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G810" s="6"/>
@@ -23576,11 +23799,11 @@
       <c r="C811" s="5"/>
       <c r="D811" s="5"/>
       <c r="E811" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F811" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G811" s="6"/>
@@ -23592,11 +23815,11 @@
       <c r="C812" s="5"/>
       <c r="D812" s="5"/>
       <c r="E812" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F812" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G812" s="6"/>
@@ -23608,11 +23831,11 @@
       <c r="C813" s="5"/>
       <c r="D813" s="5"/>
       <c r="E813" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F813" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G813" s="6"/>
@@ -23624,11 +23847,11 @@
       <c r="C814" s="5"/>
       <c r="D814" s="5"/>
       <c r="E814" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F814" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G814" s="6"/>
@@ -23640,11 +23863,11 @@
       <c r="C815" s="5"/>
       <c r="D815" s="5"/>
       <c r="E815" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F815" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G815" s="6"/>
@@ -23656,11 +23879,11 @@
       <c r="C816" s="5"/>
       <c r="D816" s="5"/>
       <c r="E816" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F816" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G816" s="6"/>
@@ -23672,11 +23895,11 @@
       <c r="C817" s="5"/>
       <c r="D817" s="5"/>
       <c r="E817" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F817" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G817" s="6"/>
@@ -23688,11 +23911,11 @@
       <c r="C818" s="5"/>
       <c r="D818" s="5"/>
       <c r="E818" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F818" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G818" s="6"/>
@@ -23704,11 +23927,11 @@
       <c r="C819" s="5"/>
       <c r="D819" s="5"/>
       <c r="E819" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F819" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G819" s="6"/>
@@ -23720,11 +23943,11 @@
       <c r="C820" s="5"/>
       <c r="D820" s="5"/>
       <c r="E820" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F820" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G820" s="6"/>
@@ -23736,11 +23959,11 @@
       <c r="C821" s="5"/>
       <c r="D821" s="5"/>
       <c r="E821" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F821" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G821" s="6"/>
@@ -23752,11 +23975,11 @@
       <c r="C822" s="5"/>
       <c r="D822" s="5"/>
       <c r="E822" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F822" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G822" s="6"/>
@@ -23768,11 +23991,11 @@
       <c r="C823" s="5"/>
       <c r="D823" s="5"/>
       <c r="E823" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F823" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G823" s="6"/>
@@ -23784,11 +24007,11 @@
       <c r="C824" s="5"/>
       <c r="D824" s="5"/>
       <c r="E824" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F824" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G824" s="6"/>
@@ -23800,11 +24023,11 @@
       <c r="C825" s="5"/>
       <c r="D825" s="5"/>
       <c r="E825" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F825" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G825" s="6"/>
@@ -23816,11 +24039,11 @@
       <c r="C826" s="5"/>
       <c r="D826" s="5"/>
       <c r="E826" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F826" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G826" s="6"/>
@@ -23832,11 +24055,11 @@
       <c r="C827" s="5"/>
       <c r="D827" s="5"/>
       <c r="E827" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F827" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G827" s="6"/>
@@ -23848,11 +24071,11 @@
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F828" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G828" s="6"/>
@@ -23864,11 +24087,11 @@
       <c r="C829" s="5"/>
       <c r="D829" s="5"/>
       <c r="E829" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F829" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G829" s="6"/>
@@ -23880,11 +24103,11 @@
       <c r="C830" s="5"/>
       <c r="D830" s="5"/>
       <c r="E830" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F830" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G830" s="6"/>
@@ -23896,11 +24119,11 @@
       <c r="C831" s="5"/>
       <c r="D831" s="5"/>
       <c r="E831" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F831" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G831" s="6"/>
@@ -23912,11 +24135,11 @@
       <c r="C832" s="5"/>
       <c r="D832" s="5"/>
       <c r="E832" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F832" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G832" s="6"/>
@@ -23928,11 +24151,11 @@
       <c r="C833" s="5"/>
       <c r="D833" s="5"/>
       <c r="E833" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F833" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G833" s="6"/>
@@ -23944,11 +24167,11 @@
       <c r="C834" s="5"/>
       <c r="D834" s="5"/>
       <c r="E834" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F834" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G834" s="6"/>
@@ -23960,11 +24183,11 @@
       <c r="C835" s="5"/>
       <c r="D835" s="5"/>
       <c r="E835" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F835" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G835" s="6"/>
@@ -23976,11 +24199,11 @@
       <c r="C836" s="5"/>
       <c r="D836" s="5"/>
       <c r="E836" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F836" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G836" s="6"/>
@@ -23992,11 +24215,11 @@
       <c r="C837" s="5"/>
       <c r="D837" s="5"/>
       <c r="E837" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F837" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G837" s="6"/>
@@ -24008,11 +24231,11 @@
       <c r="C838" s="5"/>
       <c r="D838" s="5"/>
       <c r="E838" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F838" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G838" s="6"/>
@@ -24024,11 +24247,11 @@
       <c r="C839" s="5"/>
       <c r="D839" s="5"/>
       <c r="E839" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F839" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G839" s="6"/>
@@ -24040,11 +24263,11 @@
       <c r="C840" s="5"/>
       <c r="D840" s="5"/>
       <c r="E840" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F840" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G840" s="6"/>
@@ -24056,11 +24279,11 @@
       <c r="C841" s="5"/>
       <c r="D841" s="5"/>
       <c r="E841" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F841" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G841" s="6"/>
@@ -24072,11 +24295,11 @@
       <c r="C842" s="5"/>
       <c r="D842" s="5"/>
       <c r="E842" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F842" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G842" s="6"/>
@@ -24088,11 +24311,11 @@
       <c r="C843" s="5"/>
       <c r="D843" s="5"/>
       <c r="E843" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F843" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G843" s="6"/>
@@ -24104,11 +24327,11 @@
       <c r="C844" s="5"/>
       <c r="D844" s="5"/>
       <c r="E844" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F844" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G844" s="6"/>
@@ -24120,11 +24343,11 @@
       <c r="C845" s="5"/>
       <c r="D845" s="5"/>
       <c r="E845" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F845" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G845" s="6"/>
@@ -24136,11 +24359,11 @@
       <c r="C846" s="5"/>
       <c r="D846" s="5"/>
       <c r="E846" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F846" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G846" s="6"/>
@@ -24152,11 +24375,11 @@
       <c r="C847" s="5"/>
       <c r="D847" s="5"/>
       <c r="E847" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F847" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G847" s="6"/>
@@ -24168,11 +24391,11 @@
       <c r="C848" s="5"/>
       <c r="D848" s="5"/>
       <c r="E848" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F848" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G848" s="6"/>
@@ -24184,11 +24407,11 @@
       <c r="C849" s="5"/>
       <c r="D849" s="5"/>
       <c r="E849" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F849" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G849" s="6"/>
@@ -24200,11 +24423,11 @@
       <c r="C850" s="5"/>
       <c r="D850" s="5"/>
       <c r="E850" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F850" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G850" s="6"/>
@@ -24216,11 +24439,11 @@
       <c r="C851" s="5"/>
       <c r="D851" s="5"/>
       <c r="E851" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F851" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G851" s="6"/>
@@ -24232,11 +24455,11 @@
       <c r="C852" s="5"/>
       <c r="D852" s="5"/>
       <c r="E852" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F852" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G852" s="6"/>
@@ -24248,11 +24471,11 @@
       <c r="C853" s="5"/>
       <c r="D853" s="5"/>
       <c r="E853" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F853" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G853" s="6"/>
@@ -24264,11 +24487,11 @@
       <c r="C854" s="5"/>
       <c r="D854" s="5"/>
       <c r="E854" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F854" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G854" s="6"/>
@@ -24280,11 +24503,11 @@
       <c r="C855" s="5"/>
       <c r="D855" s="5"/>
       <c r="E855" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
       <c r="F855" s="5" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="G855" s="6"/>
@@ -24296,11 +24519,11 @@
       <c r="C856" s="5"/>
       <c r="D856" s="5"/>
       <c r="E856" s="5">
-        <f t="shared" ref="E856:E919" si="30">MONTH(A856)</f>
+        <f t="shared" ref="E856:E919" si="33">MONTH(A856)</f>
         <v>1</v>
       </c>
       <c r="F856" s="5" t="str">
-        <f t="shared" ref="F856:F919" si="31">B856&amp;C856&amp;E856&amp;D856</f>
+        <f t="shared" ref="F856:F919" si="34">B856&amp;C856&amp;E856&amp;D856</f>
         <v>1</v>
       </c>
       <c r="G856" s="6"/>
@@ -24312,11 +24535,11 @@
       <c r="C857" s="5"/>
       <c r="D857" s="5"/>
       <c r="E857" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F857" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G857" s="6"/>
@@ -24328,11 +24551,11 @@
       <c r="C858" s="5"/>
       <c r="D858" s="5"/>
       <c r="E858" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F858" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G858" s="6"/>
@@ -24344,11 +24567,11 @@
       <c r="C859" s="5"/>
       <c r="D859" s="5"/>
       <c r="E859" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F859" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G859" s="6"/>
@@ -24360,11 +24583,11 @@
       <c r="C860" s="5"/>
       <c r="D860" s="5"/>
       <c r="E860" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F860" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G860" s="6"/>
@@ -24376,11 +24599,11 @@
       <c r="C861" s="5"/>
       <c r="D861" s="5"/>
       <c r="E861" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F861" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G861" s="6"/>
@@ -24392,11 +24615,11 @@
       <c r="C862" s="5"/>
       <c r="D862" s="5"/>
       <c r="E862" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F862" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G862" s="6"/>
@@ -24408,11 +24631,11 @@
       <c r="C863" s="5"/>
       <c r="D863" s="5"/>
       <c r="E863" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F863" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G863" s="6"/>
@@ -24424,11 +24647,11 @@
       <c r="C864" s="5"/>
       <c r="D864" s="5"/>
       <c r="E864" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F864" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G864" s="6"/>
@@ -24440,11 +24663,11 @@
       <c r="C865" s="5"/>
       <c r="D865" s="5"/>
       <c r="E865" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F865" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G865" s="6"/>
@@ -24456,11 +24679,11 @@
       <c r="C866" s="5"/>
       <c r="D866" s="5"/>
       <c r="E866" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F866" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G866" s="6"/>
@@ -24472,11 +24695,11 @@
       <c r="C867" s="5"/>
       <c r="D867" s="5"/>
       <c r="E867" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F867" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G867" s="6"/>
@@ -24488,11 +24711,11 @@
       <c r="C868" s="5"/>
       <c r="D868" s="5"/>
       <c r="E868" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F868" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G868" s="6"/>
@@ -24504,11 +24727,11 @@
       <c r="C869" s="5"/>
       <c r="D869" s="5"/>
       <c r="E869" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F869" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G869" s="6"/>
@@ -24520,11 +24743,11 @@
       <c r="C870" s="5"/>
       <c r="D870" s="5"/>
       <c r="E870" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F870" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G870" s="6"/>
@@ -24536,11 +24759,11 @@
       <c r="C871" s="5"/>
       <c r="D871" s="5"/>
       <c r="E871" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F871" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G871" s="6"/>
@@ -24552,11 +24775,11 @@
       <c r="C872" s="5"/>
       <c r="D872" s="5"/>
       <c r="E872" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F872" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G872" s="6"/>
@@ -24568,11 +24791,11 @@
       <c r="C873" s="5"/>
       <c r="D873" s="5"/>
       <c r="E873" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F873" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G873" s="6"/>
@@ -24584,11 +24807,11 @@
       <c r="C874" s="5"/>
       <c r="D874" s="5"/>
       <c r="E874" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F874" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G874" s="6"/>
@@ -24600,11 +24823,11 @@
       <c r="C875" s="5"/>
       <c r="D875" s="5"/>
       <c r="E875" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F875" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G875" s="6"/>
@@ -24616,11 +24839,11 @@
       <c r="C876" s="5"/>
       <c r="D876" s="5"/>
       <c r="E876" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F876" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G876" s="6"/>
@@ -24632,11 +24855,11 @@
       <c r="C877" s="5"/>
       <c r="D877" s="5"/>
       <c r="E877" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F877" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G877" s="6"/>
@@ -24648,11 +24871,11 @@
       <c r="C878" s="5"/>
       <c r="D878" s="5"/>
       <c r="E878" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F878" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G878" s="6"/>
@@ -24664,11 +24887,11 @@
       <c r="C879" s="5"/>
       <c r="D879" s="5"/>
       <c r="E879" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F879" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G879" s="6"/>
@@ -24680,11 +24903,11 @@
       <c r="C880" s="5"/>
       <c r="D880" s="5"/>
       <c r="E880" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F880" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G880" s="6"/>
@@ -24696,11 +24919,11 @@
       <c r="C881" s="5"/>
       <c r="D881" s="5"/>
       <c r="E881" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F881" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G881" s="6"/>
@@ -24712,11 +24935,11 @@
       <c r="C882" s="5"/>
       <c r="D882" s="5"/>
       <c r="E882" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F882" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G882" s="6"/>
@@ -24728,11 +24951,11 @@
       <c r="C883" s="5"/>
       <c r="D883" s="5"/>
       <c r="E883" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F883" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G883" s="6"/>
@@ -24744,11 +24967,11 @@
       <c r="C884" s="5"/>
       <c r="D884" s="5"/>
       <c r="E884" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F884" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G884" s="6"/>
@@ -24760,11 +24983,11 @@
       <c r="C885" s="5"/>
       <c r="D885" s="5"/>
       <c r="E885" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F885" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G885" s="6"/>
@@ -24776,11 +24999,11 @@
       <c r="C886" s="5"/>
       <c r="D886" s="5"/>
       <c r="E886" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F886" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G886" s="6"/>
@@ -24792,11 +25015,11 @@
       <c r="C887" s="5"/>
       <c r="D887" s="5"/>
       <c r="E887" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F887" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G887" s="6"/>
@@ -24808,11 +25031,11 @@
       <c r="C888" s="5"/>
       <c r="D888" s="5"/>
       <c r="E888" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F888" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G888" s="6"/>
@@ -24824,11 +25047,11 @@
       <c r="C889" s="5"/>
       <c r="D889" s="5"/>
       <c r="E889" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F889" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G889" s="6"/>
@@ -24840,11 +25063,11 @@
       <c r="C890" s="5"/>
       <c r="D890" s="5"/>
       <c r="E890" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F890" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G890" s="6"/>
@@ -24856,11 +25079,11 @@
       <c r="C891" s="5"/>
       <c r="D891" s="5"/>
       <c r="E891" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F891" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G891" s="6"/>
@@ -24872,11 +25095,11 @@
       <c r="C892" s="5"/>
       <c r="D892" s="5"/>
       <c r="E892" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F892" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G892" s="6"/>
@@ -24888,11 +25111,11 @@
       <c r="C893" s="5"/>
       <c r="D893" s="5"/>
       <c r="E893" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F893" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G893" s="6"/>
@@ -24904,11 +25127,11 @@
       <c r="C894" s="5"/>
       <c r="D894" s="5"/>
       <c r="E894" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F894" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G894" s="6"/>
@@ -24920,11 +25143,11 @@
       <c r="C895" s="5"/>
       <c r="D895" s="5"/>
       <c r="E895" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F895" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G895" s="6"/>
@@ -24936,11 +25159,11 @@
       <c r="C896" s="5"/>
       <c r="D896" s="5"/>
       <c r="E896" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F896" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G896" s="6"/>
@@ -24952,11 +25175,11 @@
       <c r="C897" s="5"/>
       <c r="D897" s="5"/>
       <c r="E897" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F897" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G897" s="6"/>
@@ -24968,11 +25191,11 @@
       <c r="C898" s="5"/>
       <c r="D898" s="5"/>
       <c r="E898" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F898" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G898" s="6"/>
@@ -24984,11 +25207,11 @@
       <c r="C899" s="5"/>
       <c r="D899" s="5"/>
       <c r="E899" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F899" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G899" s="6"/>
@@ -25000,11 +25223,11 @@
       <c r="C900" s="5"/>
       <c r="D900" s="5"/>
       <c r="E900" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F900" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G900" s="6"/>
@@ -25016,11 +25239,11 @@
       <c r="C901" s="5"/>
       <c r="D901" s="5"/>
       <c r="E901" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F901" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G901" s="6"/>
@@ -25032,11 +25255,11 @@
       <c r="C902" s="5"/>
       <c r="D902" s="5"/>
       <c r="E902" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F902" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G902" s="6"/>
@@ -25048,11 +25271,11 @@
       <c r="C903" s="5"/>
       <c r="D903" s="5"/>
       <c r="E903" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F903" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G903" s="6"/>
@@ -25064,11 +25287,11 @@
       <c r="C904" s="5"/>
       <c r="D904" s="5"/>
       <c r="E904" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F904" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G904" s="6"/>
@@ -25080,11 +25303,11 @@
       <c r="C905" s="5"/>
       <c r="D905" s="5"/>
       <c r="E905" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F905" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G905" s="6"/>
@@ -25096,11 +25319,11 @@
       <c r="C906" s="5"/>
       <c r="D906" s="5"/>
       <c r="E906" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F906" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G906" s="6"/>
@@ -25112,11 +25335,11 @@
       <c r="C907" s="5"/>
       <c r="D907" s="5"/>
       <c r="E907" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F907" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G907" s="6"/>
@@ -25128,11 +25351,11 @@
       <c r="C908" s="5"/>
       <c r="D908" s="5"/>
       <c r="E908" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F908" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G908" s="6"/>
@@ -25144,11 +25367,11 @@
       <c r="C909" s="5"/>
       <c r="D909" s="5"/>
       <c r="E909" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F909" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G909" s="6"/>
@@ -25160,11 +25383,11 @@
       <c r="C910" s="5"/>
       <c r="D910" s="5"/>
       <c r="E910" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F910" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G910" s="6"/>
@@ -25176,11 +25399,11 @@
       <c r="C911" s="5"/>
       <c r="D911" s="5"/>
       <c r="E911" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F911" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G911" s="6"/>
@@ -25192,11 +25415,11 @@
       <c r="C912" s="5"/>
       <c r="D912" s="5"/>
       <c r="E912" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F912" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G912" s="6"/>
@@ -25208,11 +25431,11 @@
       <c r="C913" s="5"/>
       <c r="D913" s="5"/>
       <c r="E913" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F913" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G913" s="6"/>
@@ -25224,11 +25447,11 @@
       <c r="C914" s="5"/>
       <c r="D914" s="5"/>
       <c r="E914" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F914" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G914" s="6"/>
@@ -25240,11 +25463,11 @@
       <c r="C915" s="5"/>
       <c r="D915" s="5"/>
       <c r="E915" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F915" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G915" s="6"/>
@@ -25256,11 +25479,11 @@
       <c r="C916" s="5"/>
       <c r="D916" s="5"/>
       <c r="E916" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F916" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G916" s="6"/>
@@ -25272,11 +25495,11 @@
       <c r="C917" s="5"/>
       <c r="D917" s="5"/>
       <c r="E917" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F917" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G917" s="6"/>
@@ -25288,11 +25511,11 @@
       <c r="C918" s="5"/>
       <c r="D918" s="5"/>
       <c r="E918" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F918" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G918" s="6"/>
@@ -25304,11 +25527,11 @@
       <c r="C919" s="5"/>
       <c r="D919" s="5"/>
       <c r="E919" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="F919" s="5" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="G919" s="6"/>
@@ -25320,11 +25543,11 @@
       <c r="C920" s="5"/>
       <c r="D920" s="5"/>
       <c r="E920" s="5">
-        <f t="shared" ref="E920:E940" si="32">MONTH(A920)</f>
+        <f t="shared" ref="E920:E940" si="35">MONTH(A920)</f>
         <v>1</v>
       </c>
       <c r="F920" s="5" t="str">
-        <f t="shared" ref="F920:F940" si="33">B920&amp;C920&amp;E920&amp;D920</f>
+        <f t="shared" ref="F920:F940" si="36">B920&amp;C920&amp;E920&amp;D920</f>
         <v>1</v>
       </c>
       <c r="G920" s="6"/>
@@ -25336,11 +25559,11 @@
       <c r="C921" s="5"/>
       <c r="D921" s="5"/>
       <c r="E921" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F921" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G921" s="6"/>
@@ -25352,11 +25575,11 @@
       <c r="C922" s="5"/>
       <c r="D922" s="5"/>
       <c r="E922" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F922" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G922" s="6"/>
@@ -25368,11 +25591,11 @@
       <c r="C923" s="5"/>
       <c r="D923" s="5"/>
       <c r="E923" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F923" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G923" s="6"/>
@@ -25384,11 +25607,11 @@
       <c r="C924" s="5"/>
       <c r="D924" s="5"/>
       <c r="E924" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F924" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G924" s="6"/>
@@ -25400,11 +25623,11 @@
       <c r="C925" s="5"/>
       <c r="D925" s="5"/>
       <c r="E925" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F925" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G925" s="6"/>
@@ -25416,11 +25639,11 @@
       <c r="C926" s="5"/>
       <c r="D926" s="5"/>
       <c r="E926" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F926" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G926" s="6"/>
@@ -25432,11 +25655,11 @@
       <c r="C927" s="5"/>
       <c r="D927" s="5"/>
       <c r="E927" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F927" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G927" s="6"/>
@@ -25448,11 +25671,11 @@
       <c r="C928" s="5"/>
       <c r="D928" s="5"/>
       <c r="E928" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F928" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G928" s="6"/>
@@ -25464,11 +25687,11 @@
       <c r="C929" s="5"/>
       <c r="D929" s="5"/>
       <c r="E929" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F929" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G929" s="6"/>
@@ -25480,11 +25703,11 @@
       <c r="C930" s="5"/>
       <c r="D930" s="5"/>
       <c r="E930" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F930" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G930" s="6"/>
@@ -25496,11 +25719,11 @@
       <c r="C931" s="5"/>
       <c r="D931" s="5"/>
       <c r="E931" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F931" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G931" s="6"/>
@@ -25512,11 +25735,11 @@
       <c r="C932" s="5"/>
       <c r="D932" s="5"/>
       <c r="E932" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F932" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G932" s="6"/>
@@ -25528,11 +25751,11 @@
       <c r="C933" s="5"/>
       <c r="D933" s="5"/>
       <c r="E933" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F933" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G933" s="6"/>
@@ -25544,11 +25767,11 @@
       <c r="C934" s="5"/>
       <c r="D934" s="5"/>
       <c r="E934" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F934" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G934" s="6"/>
@@ -25560,11 +25783,11 @@
       <c r="C935" s="5"/>
       <c r="D935" s="5"/>
       <c r="E935" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F935" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G935" s="6"/>
@@ -25576,11 +25799,11 @@
       <c r="C936" s="5"/>
       <c r="D936" s="5"/>
       <c r="E936" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F936" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G936" s="6"/>
@@ -25592,11 +25815,11 @@
       <c r="C937" s="5"/>
       <c r="D937" s="5"/>
       <c r="E937" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F937" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G937" s="6"/>
@@ -25608,11 +25831,11 @@
       <c r="C938" s="5"/>
       <c r="D938" s="5"/>
       <c r="E938" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F938" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G938" s="6"/>
@@ -25624,11 +25847,11 @@
       <c r="C939" s="5"/>
       <c r="D939" s="5"/>
       <c r="E939" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F939" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G939" s="6"/>
@@ -25640,11 +25863,11 @@
       <c r="C940" s="5"/>
       <c r="D940" s="5"/>
       <c r="E940" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="F940" s="5" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="G940" s="6"/>
